--- a/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30678C82-A27B-4E2F-BBCC-34F5F4A83B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFF5F0-9AF8-4ED4-B943-FD306474D47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="2" r:id="rId1"/>
-    <sheet name="modeldata" sheetId="1" r:id="rId2"/>
-    <sheet name="BATS 2023" sheetId="3" r:id="rId3"/>
+    <sheet name="constants" sheetId="4" r:id="rId2"/>
+    <sheet name="modeldata" sheetId="1" r:id="rId3"/>
+    <sheet name="BATS 2023" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="88">
   <si>
     <t>Source:</t>
   </si>
@@ -231,6 +254,81 @@
   <si>
     <t>4+ out 4+ ret</t>
   </si>
+  <si>
+    <t>Alt1</t>
+  </si>
+  <si>
+    <t>Alt2</t>
+  </si>
+  <si>
+    <t>Alt3</t>
+  </si>
+  <si>
+    <t>Alt4</t>
+  </si>
+  <si>
+    <t>Alt5</t>
+  </si>
+  <si>
+    <t>Alt6</t>
+  </si>
+  <si>
+    <t>Alt7</t>
+  </si>
+  <si>
+    <t>Alt8</t>
+  </si>
+  <si>
+    <t>Alt9</t>
+  </si>
+  <si>
+    <t>Alt10</t>
+  </si>
+  <si>
+    <t>Alt11</t>
+  </si>
+  <si>
+    <t>Alt12</t>
+  </si>
+  <si>
+    <t>Alt13</t>
+  </si>
+  <si>
+    <t>Alt14</t>
+  </si>
+  <si>
+    <t>Alt15</t>
+  </si>
+  <si>
+    <t>Alt16</t>
+  </si>
+  <si>
+    <t>4 Stops</t>
+  </si>
+  <si>
+    <t>5 Stops</t>
+  </si>
+  <si>
+    <t>2 out</t>
+  </si>
+  <si>
+    <t>Return Stops</t>
+  </si>
+  <si>
+    <t>Total Number of Stops</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Exisiting</t>
+  </si>
+  <si>
+    <t>New Constants</t>
+  </si>
+  <si>
+    <t>Outbound Stops</t>
+  </si>
 </sst>
 </file>
 
@@ -241,7 +339,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +377,14 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -413,7 +519,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -493,13 +599,27 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -6404,7 +6524,7 @@
       </c>
       <c r="C48" s="11"/>
     </row>
-    <row r="50" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>51</v>
       </c>
@@ -6415,7 +6535,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>1</v>
       </c>
@@ -6516,21 +6636,57 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
       <c r="B52" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="18"/>
+      <c r="C52" s="16" cm="1">
+        <f t="array" ref="C52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="17" cm="1">
+        <f t="array" ref="D52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="17" cm="1">
+        <f t="array" ref="E52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="17" cm="1">
+        <f t="array" ref="F52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="17" cm="1">
+        <f t="array" ref="G52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="17" cm="1">
+        <f t="array" ref="H52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="17" cm="1">
+        <f t="array" ref="I52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="17" cm="1">
+        <f t="array" ref="J52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="17" cm="1">
+        <f t="array" ref="K52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="17" cm="1">
+        <f t="array" ref="L52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="18" cm="1">
+        <f t="array" ref="M52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
       <c r="O52" s="15" t="s">
         <v>33</v>
       </c>
@@ -6593,21 +6749,57 @@
       <c r="AL52" s="17"/>
       <c r="AM52" s="18"/>
     </row>
-    <row r="53" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>87</v>
+      </c>
       <c r="B53" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C53" s="19"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="20"/>
+      <c r="C53" s="19" cm="1">
+        <f t="array" ref="C53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="15" cm="1">
+        <f t="array" ref="D53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="15" cm="1">
+        <f t="array" ref="E53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="15" cm="1">
+        <f t="array" ref="F53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" cm="1">
+        <f t="array" ref="G53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="15" cm="1">
+        <f t="array" ref="H53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="15" cm="1">
+        <f t="array" ref="I53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="15" cm="1">
+        <f t="array" ref="J53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="15" cm="1">
+        <f t="array" ref="K53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="15" cm="1">
+        <f t="array" ref="L53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="20" cm="1">
+        <f t="array" ref="M53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
       <c r="O53" s="15" t="s">
         <v>34</v>
       </c>
@@ -6703,21 +6895,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="54" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>87</v>
+      </c>
       <c r="B54" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="20"/>
+      <c r="C54" s="19" cm="1">
+        <f t="array" ref="C54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="15" cm="1">
+        <f t="array" ref="D54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="15" cm="1">
+        <f t="array" ref="E54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="15" cm="1">
+        <f t="array" ref="F54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="15" cm="1">
+        <f t="array" ref="G54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="15" cm="1">
+        <f t="array" ref="H54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="15" cm="1">
+        <f t="array" ref="I54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="15" cm="1">
+        <f t="array" ref="J54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="15" cm="1">
+        <f t="array" ref="K54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="15" cm="1">
+        <f t="array" ref="L54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="20" cm="1">
+        <f t="array" ref="M54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
       <c r="O54" s="15" t="s">
         <v>35</v>
       </c>
@@ -6813,21 +7041,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="55" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>87</v>
+      </c>
       <c r="B55" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C55" s="21"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="23"/>
+      <c r="C55" s="21" cm="1">
+        <f t="array" ref="C55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="22" cm="1">
+        <f t="array" ref="D55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="22" cm="1">
+        <f t="array" ref="E55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="22" cm="1">
+        <f t="array" ref="F55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="22" cm="1">
+        <f t="array" ref="G55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="22" cm="1">
+        <f t="array" ref="H55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="22" cm="1">
+        <f t="array" ref="I55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="22" cm="1">
+        <f t="array" ref="J55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="22" cm="1">
+        <f t="array" ref="K55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L55" s="22" cm="1">
+        <f t="array" ref="L55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="23" cm="1">
+        <f t="array" ref="M55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
+        <v>0</v>
+      </c>
       <c r="O55" s="15" t="s">
         <v>36</v>
       </c>
@@ -6923,21 +7187,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>82</v>
+      </c>
       <c r="B56" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C56" s="24"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="25"/>
-      <c r="L56" s="25"/>
-      <c r="M56" s="26"/>
+      <c r="C56" s="24" cm="1">
+        <f t="array" ref="C56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="25" cm="1">
+        <f t="array" ref="D56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="25" cm="1">
+        <f t="array" ref="E56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="25" cm="1">
+        <f t="array" ref="F56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="25" cm="1">
+        <f t="array" ref="G56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="25" cm="1">
+        <f t="array" ref="H56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="25" cm="1">
+        <f t="array" ref="I56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="25" cm="1">
+        <f t="array" ref="J56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="25" cm="1">
+        <f t="array" ref="K56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="25" cm="1">
+        <f t="array" ref="L56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="26" cm="1">
+        <f t="array" ref="M56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
       <c r="O56" s="13" t="s">
         <v>29</v>
       </c>
@@ -7000,21 +7300,57 @@
       <c r="AL56" s="25"/>
       <c r="AM56" s="26"/>
     </row>
-    <row r="57" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>82</v>
+      </c>
       <c r="B57" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C57" s="27"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
-      <c r="M57" s="28"/>
+      <c r="C57" s="27" cm="1">
+        <f t="array" ref="C57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="13" cm="1">
+        <f t="array" ref="D57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="13" cm="1">
+        <f t="array" ref="E57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="13" cm="1">
+        <f t="array" ref="F57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="13" cm="1">
+        <f t="array" ref="G57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="13" cm="1">
+        <f t="array" ref="H57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="13" cm="1">
+        <f t="array" ref="I57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="13" cm="1">
+        <f t="array" ref="J57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="13" cm="1">
+        <f t="array" ref="K57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="13" cm="1">
+        <f t="array" ref="L57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="28" cm="1">
+        <f t="array" ref="M57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
       <c r="O57" s="13" t="s">
         <v>30</v>
       </c>
@@ -7110,21 +7446,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="58" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>82</v>
+      </c>
       <c r="B58" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
-      <c r="M58" s="28"/>
+      <c r="C58" s="27" cm="1">
+        <f t="array" ref="C58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="13" cm="1">
+        <f t="array" ref="D58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="13" cm="1">
+        <f t="array" ref="E58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="13" cm="1">
+        <f t="array" ref="F58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="13" cm="1">
+        <f t="array" ref="G58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="13" cm="1">
+        <f t="array" ref="H58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="13" cm="1">
+        <f t="array" ref="I58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="13" cm="1">
+        <f t="array" ref="J58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="13" cm="1">
+        <f t="array" ref="K58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="13" cm="1">
+        <f t="array" ref="L58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="28" cm="1">
+        <f t="array" ref="M58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
       <c r="O58" s="13" t="s">
         <v>31</v>
       </c>
@@ -7220,21 +7592,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
       <c r="B59" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C59" s="29"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="31"/>
+      <c r="C59" s="29" cm="1">
+        <f t="array" ref="C59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="30" cm="1">
+        <f t="array" ref="D59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="30" cm="1">
+        <f t="array" ref="E59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="30" cm="1">
+        <f t="array" ref="F59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="30" cm="1">
+        <f t="array" ref="G59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="30" cm="1">
+        <f t="array" ref="H59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="30" cm="1">
+        <f t="array" ref="I59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="30" cm="1">
+        <f t="array" ref="J59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="30" cm="1">
+        <f t="array" ref="K59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L59" s="30" cm="1">
+        <f t="array" ref="L59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="31" cm="1">
+        <f t="array" ref="M59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
+        <v>0</v>
+      </c>
       <c r="O59" s="13" t="s">
         <v>32</v>
       </c>
@@ -7330,21 +7738,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>83</v>
+      </c>
       <c r="B60" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="33"/>
-      <c r="M60" s="34"/>
+      <c r="C60" s="32" cm="1">
+        <f t="array" ref="C60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="33" cm="1">
+        <f t="array" ref="D60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="33" cm="1">
+        <f t="array" ref="E60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="33" cm="1">
+        <f t="array" ref="F60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="33" cm="1">
+        <f t="array" ref="G60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="33" cm="1">
+        <f t="array" ref="H60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="33" cm="1">
+        <f t="array" ref="I60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="33" cm="1">
+        <f t="array" ref="J60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="33" cm="1">
+        <f t="array" ref="K60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="33" cm="1">
+        <f t="array" ref="L60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="34" cm="1">
+        <f t="array" ref="M60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
       <c r="O60" s="14" t="s">
         <v>43</v>
       </c>
@@ -7407,21 +7851,57 @@
       <c r="AL60" s="33"/>
       <c r="AM60" s="34"/>
     </row>
-    <row r="61" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>83</v>
+      </c>
       <c r="B61" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="35"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="36"/>
+      <c r="C61" s="35" cm="1">
+        <f t="array" ref="C61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="14" cm="1">
+        <f t="array" ref="D61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="14" cm="1">
+        <f t="array" ref="E61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="14" cm="1">
+        <f t="array" ref="F61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="14" cm="1">
+        <f t="array" ref="G61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="14" cm="1">
+        <f t="array" ref="H61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="14" cm="1">
+        <f t="array" ref="I61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="14" cm="1">
+        <f t="array" ref="J61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="14" cm="1">
+        <f t="array" ref="K61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="14" cm="1">
+        <f t="array" ref="L61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="36" cm="1">
+        <f t="array" ref="M61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
       <c r="O61" s="14" t="s">
         <v>37</v>
       </c>
@@ -7484,21 +7964,57 @@
       <c r="AL61" s="14"/>
       <c r="AM61" s="36"/>
     </row>
-    <row r="62" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
       <c r="B62" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C62" s="35"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="36"/>
+      <c r="C62" s="35" cm="1">
+        <f t="array" ref="C62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="14" cm="1">
+        <f t="array" ref="D62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="14" cm="1">
+        <f t="array" ref="E62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="14" cm="1">
+        <f t="array" ref="F62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="14" cm="1">
+        <f t="array" ref="G62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H62" s="14" cm="1">
+        <f t="array" ref="H62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="14" cm="1">
+        <f t="array" ref="I62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="14" cm="1">
+        <f t="array" ref="J62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="14" cm="1">
+        <f t="array" ref="K62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="14" cm="1">
+        <f t="array" ref="L62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="36" cm="1">
+        <f t="array" ref="M62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
       <c r="O62" s="14" t="s">
         <v>38</v>
       </c>
@@ -7594,21 +8110,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="63" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>83</v>
+      </c>
       <c r="B63" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="35"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="36"/>
+      <c r="C63" s="35" cm="1">
+        <f t="array" ref="C63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="14" cm="1">
+        <f t="array" ref="D63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="14" cm="1">
+        <f t="array" ref="E63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="14" cm="1">
+        <f t="array" ref="F63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="14" cm="1">
+        <f t="array" ref="G63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H63" s="14" cm="1">
+        <f t="array" ref="H63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="14" cm="1">
+        <f t="array" ref="I63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="14" cm="1">
+        <f t="array" ref="J63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="14" cm="1">
+        <f t="array" ref="K63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="14" cm="1">
+        <f t="array" ref="L63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="36" cm="1">
+        <f t="array" ref="M63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
       <c r="O63" s="14" t="s">
         <v>39</v>
       </c>
@@ -7704,21 +8256,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="64" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>83</v>
+      </c>
       <c r="B64" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="36"/>
+        <v>79</v>
+      </c>
+      <c r="C64" s="35" cm="1">
+        <f t="array" ref="C64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="14" cm="1">
+        <f t="array" ref="D64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="14" cm="1">
+        <f t="array" ref="E64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="14" cm="1">
+        <f t="array" ref="F64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="14" cm="1">
+        <f t="array" ref="G64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="14" cm="1">
+        <f t="array" ref="H64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="14" cm="1">
+        <f t="array" ref="I64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="14" cm="1">
+        <f t="array" ref="J64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K64" s="14" cm="1">
+        <f t="array" ref="K64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L64" s="14" cm="1">
+        <f t="array" ref="L64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="36" cm="1">
+        <f t="array" ref="M64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
       <c r="O64" s="14" t="s">
         <v>44</v>
       </c>
@@ -7767,7 +8355,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB64" s="14" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="AC64" s="35" t="e">
         <f t="shared" si="185"/>
@@ -7814,21 +8402,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>83</v>
+      </c>
       <c r="B65" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C65" s="35"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="36"/>
+        <v>80</v>
+      </c>
+      <c r="C65" s="35" cm="1">
+        <f t="array" ref="C65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="14" cm="1">
+        <f t="array" ref="D65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="14" cm="1">
+        <f t="array" ref="E65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F65" s="14" cm="1">
+        <f t="array" ref="F65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="14" cm="1">
+        <f t="array" ref="G65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="14" cm="1">
+        <f t="array" ref="H65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="14" cm="1">
+        <f t="array" ref="I65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="14" cm="1">
+        <f t="array" ref="J65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="14" cm="1">
+        <f t="array" ref="K65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L65" s="14" cm="1">
+        <f t="array" ref="L65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="36" cm="1">
+        <f t="array" ref="M65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
       <c r="O65" s="14" t="s">
         <v>45</v>
       </c>
@@ -7877,7 +8501,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB65" s="14" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="AC65" s="35" t="e">
         <f t="shared" si="185"/>
@@ -7924,21 +8548,57 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
       <c r="B66" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
-      <c r="L66" s="38"/>
-      <c r="M66" s="39"/>
+      <c r="C66" s="37" cm="1">
+        <f t="array" ref="C66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="38" cm="1">
+        <f t="array" ref="D66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!D$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="38" cm="1">
+        <f t="array" ref="E66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!E$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="38" cm="1">
+        <f t="array" ref="F66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!F$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G66" s="38" cm="1">
+        <f t="array" ref="G66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!G$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="38" cm="1">
+        <f t="array" ref="H66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!H$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="38" cm="1">
+        <f t="array" ref="I66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!I$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="38" cm="1">
+        <f t="array" ref="J66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!J$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="38" cm="1">
+        <f t="array" ref="K66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!K$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L66" s="38" cm="1">
+        <f t="array" ref="L66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!L$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="39" cm="1">
+        <f t="array" ref="M66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!M$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
+        <v>0</v>
+      </c>
       <c r="O66" s="14" t="s">
         <v>40</v>
       </c>
@@ -8031,6 +8691,2836 @@
       </c>
       <c r="AM66" s="39" t="e">
         <f t="shared" si="195"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="AC27:AM45">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>ABS(AC27) &gt; 10%</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F41A67D-DB7F-48D1-AFB6-344D1665DF25}">
+  <dimension ref="A1:AH38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C1" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="S1" s="73" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>77</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L4" t="s">
+        <v>81</v>
+      </c>
+      <c r="M4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" t="s">
+        <v>33</v>
+      </c>
+      <c r="U4" t="s">
+        <v>33</v>
+      </c>
+      <c r="V4" t="s">
+        <v>33</v>
+      </c>
+      <c r="W4" t="s">
+        <v>34</v>
+      </c>
+      <c r="X4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A5" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" s="7"/>
+      <c r="S6">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH6" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A6,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R7" s="7"/>
+      <c r="S7">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W7">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA7">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE7">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH7" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A7,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8" s="7"/>
+      <c r="S8">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W8">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH8" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A8,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="R9" s="7"/>
+      <c r="S9">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH9" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A9,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="R10" s="7"/>
+      <c r="S10">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W10">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA10">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE10">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH10" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A10,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11" s="7"/>
+      <c r="S11">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W11">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH11" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A11,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="R12" s="7"/>
+      <c r="S12">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH12" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A12,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="R13" s="7"/>
+      <c r="S13">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W13">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA13">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE13">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH13" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A13,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="R14" s="7"/>
+      <c r="S14">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W14">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH14" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A14,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="R15" s="7"/>
+      <c r="S15">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH15" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A15,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="R16" s="7"/>
+      <c r="S16">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W16">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA16">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE16">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH16" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A16,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="R17" s="7"/>
+      <c r="S17">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W17">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH17" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A17,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="R18" s="7"/>
+      <c r="S18">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH18" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A18,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="R19" s="7"/>
+      <c r="S19">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W19">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA19">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE19">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH19" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A19,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="R20" s="7"/>
+      <c r="S20">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W20">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH20" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A20,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="R21" s="7"/>
+      <c r="S21">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH21" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A21,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="R22" s="7"/>
+      <c r="S22">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W22">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA22">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE22">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH22" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A22,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="R23" s="7"/>
+      <c r="S23">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W23">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH23" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A23,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="R24" s="7"/>
+      <c r="S24">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH24" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A24,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="R25" s="7"/>
+      <c r="S25">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W25">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA25">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE25">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH25" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A25,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="R26" s="7"/>
+      <c r="S26">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W26">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH26" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A26,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="R27" s="7"/>
+      <c r="S27">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH27" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A27,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="R28" s="7"/>
+      <c r="S28">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W28">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA28">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE28">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH28" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A28,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="R29" s="7"/>
+      <c r="S29">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W29">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH29" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A29,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="R30" s="7"/>
+      <c r="S30">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH30" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A30,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+      <c r="R31" s="7"/>
+      <c r="S31">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W31">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA31">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE31">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH31" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A31,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="R32" s="7"/>
+      <c r="S32">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W32">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH32" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A32,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="R33" s="7"/>
+      <c r="S33">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH33" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A33,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>82</v>
+      </c>
+      <c r="R34" s="7"/>
+      <c r="S34">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W34">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA34">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE34">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH34" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A34,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>83</v>
+      </c>
+      <c r="R35" s="7"/>
+      <c r="S35">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W35">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH35" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A35,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="R36" s="7"/>
+      <c r="S36">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!S$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!T$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!U$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!V$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="W36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!W$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!X$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Y$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!Z$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AA$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AB$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AC$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AD$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AE$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AF$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AG$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH36" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(constants!AH$4,calibration!$AB$52:$AB$66,0),MATCH(constants!$A36,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+      <c r="R37" s="7"/>
+      <c r="S37">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W37">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA37">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE37">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AF37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH37" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$5,calibration!$AB$52:$AB$66,0),MATCH(constants!$A37,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="R38" s="7"/>
+      <c r="S38">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(S$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(T$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(U$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(V$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W38">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(W$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(X$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Y$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(Z$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AA$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AB$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AC$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AD$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AE$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AF$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AG$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH38" t="e">
+        <f>INDEX(calibration!$AC$52:$AM$66,MATCH(AH$3,calibration!$AB$52:$AB$66,0),MATCH(constants!$A38,calibration!$P$51:$Z$51,0))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -8039,7 +11529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADE016D-553D-4789-A918-6381BA0F9838}">
   <sheetPr>
     <tabColor rgb="FF9BBB59"/>
@@ -8191,7 +11681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEE3413-48B7-4B37-B389-374873CCA87C}">
   <sheetPr>
     <tabColor theme="3" tint="0.499984740745262"/>

--- a/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFF5F0-9AF8-4ED4-B943-FD306474D47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DECCF4F-D169-4FA8-9A53-E82CC1C9364E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="2" r:id="rId1"/>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>3 out 3 ret</t>
-  </si>
-  <si>
-    <t>Source</t>
   </si>
   <si>
     <t>0 Ret</t>
@@ -328,6 +325,9 @@
   </si>
   <si>
     <t>Outbound Stops</t>
+  </si>
+  <si>
+    <t>Source: M:\Development\Travel Model One\Calibration\Version 1.7\2023_BATS_Summaries\pipeline_mt_20260821_NoMon_rmo\ctramp_2023\BATS_Summaries\BATS2023_stop_frequency.xlsx</t>
   </si>
 </sst>
 </file>
@@ -606,13 +606,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <strike val="0"/>
@@ -971,7 +965,7 @@
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
@@ -985,7 +979,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P2" s="12"/>
       <c r="Q2" s="12"/>
@@ -1000,7 +994,7 @@
       <c r="Z2" s="12"/>
       <c r="AA2" s="12"/>
       <c r="AB2" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC2" s="12"/>
       <c r="AD2" s="12"/>
@@ -1117,7 +1111,7 @@
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="43">
         <f>SUM('BATS 2023'!P4:P7)</f>
@@ -1164,7 +1158,7 @@
         <v>856344.68628552498</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P4" s="43">
         <f>SUM(modeldata!C4:C7)</f>
@@ -1211,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC4" s="3">
         <f>P4-C4</f>
@@ -1260,7 +1254,7 @@
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="46">
         <f>SUM('BATS 2023'!P8:P11)</f>
@@ -1307,7 +1301,7 @@
         <v>84280.883866961944</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P5" s="46">
         <f>SUM(modeldata!C8:C11)</f>
@@ -1354,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AB5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC5" s="6">
         <f>P5-C5</f>
@@ -1403,7 +1397,7 @@
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="46">
         <f>SUM('BATS 2023'!P12:P15)</f>
@@ -1450,7 +1444,7 @@
         <v>37720.411891635027</v>
       </c>
       <c r="O6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P6" s="46">
         <f>SUM(modeldata!C12:C15)</f>
@@ -1497,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC6" s="6">
         <f t="shared" ref="AC6:AC8" si="1">P6-C6</f>
@@ -1546,7 +1540,7 @@
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="49">
         <f>SUM('BATS 2023'!P16:P19)</f>
@@ -1593,7 +1587,7 @@
         <v>7901.9660427044219</v>
       </c>
       <c r="O7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P7" s="49">
         <f>SUM(modeldata!C16:C19)</f>
@@ -1640,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="AB7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC7" s="8">
         <f t="shared" si="1"/>
@@ -1689,7 +1683,7 @@
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="52">
         <f>SUM(C4:C7)</f>
@@ -1736,7 +1730,7 @@
         <v>986247.94808682636</v>
       </c>
       <c r="O8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P8" s="52">
         <f>SUM(P4:P7)</f>
@@ -1783,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC8">
         <f t="shared" si="1"/>
@@ -1845,7 +1839,7 @@
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="43">
         <f>SUM('BATS 2023'!P4,'BATS 2023'!P8,'BATS 2023'!P12,'BATS 2023'!P16)</f>
@@ -1892,7 +1886,7 @@
         <v>773789.05495939124</v>
       </c>
       <c r="O10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P10" s="43">
         <f>modeldata!C4+modeldata!C8+modeldata!C12+modeldata!C16</f>
@@ -1939,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC10" s="3">
         <f>P10-C10</f>
@@ -1988,7 +1982,7 @@
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="46">
         <f>SUM('BATS 2023'!P5,'BATS 2023'!P9,'BATS 2023'!P13,'BATS 2023'!P17)</f>
@@ -2035,7 +2029,7 @@
         <v>138952.67010878486</v>
       </c>
       <c r="O11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" s="46">
         <f>modeldata!C5+modeldata!C9+modeldata!C13+modeldata!C17</f>
@@ -2082,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC11" s="6">
         <f>P11-C11</f>
@@ -2131,7 +2125,7 @@
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="46">
         <f>SUM('BATS 2023'!P6,'BATS 2023'!P10,'BATS 2023'!P14,'BATS 2023'!P18)</f>
@@ -2178,7 +2172,7 @@
         <v>50928.770542269362</v>
       </c>
       <c r="O12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P12" s="46">
         <f>modeldata!C6+modeldata!C10+modeldata!C14+modeldata!C18</f>
@@ -2225,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AB12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AC12" s="6">
         <f t="shared" ref="AC12:AC14" si="33">P12-C12</f>
@@ -2274,7 +2268,7 @@
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="49">
         <f>SUM('BATS 2023'!P7,'BATS 2023'!P11,'BATS 2023'!P15,'BATS 2023'!P19)</f>
@@ -2321,7 +2315,7 @@
         <v>22577.452476380953</v>
       </c>
       <c r="O13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P13" s="49">
         <f>modeldata!C7+modeldata!C11+modeldata!C15+modeldata!C19</f>
@@ -2368,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="AB13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC13" s="8">
         <f t="shared" si="33"/>
@@ -2417,7 +2411,7 @@
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="52">
         <f>SUM(C10:C13)</f>
@@ -2464,7 +2458,7 @@
         <v>986247.94808682648</v>
       </c>
       <c r="O14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P14" s="52">
         <f>SUM(P10:P13)</f>
@@ -2511,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="AB14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC14">
         <f t="shared" si="33"/>
@@ -2584,7 +2578,7 @@
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="43">
         <f>'BATS 2023'!P4</f>
@@ -2631,7 +2625,7 @@
         <v>675881.93703013682</v>
       </c>
       <c r="O16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P16" s="43">
         <f>modeldata!C4</f>
@@ -2678,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="AB16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC16" s="3">
         <f>P16-C16</f>
@@ -2727,7 +2721,7 @@
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="46">
         <f>'BATS 2023'!P5+'BATS 2023'!P8</f>
@@ -2774,7 +2768,7 @@
         <v>186753.41224701353</v>
       </c>
       <c r="O17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P17" s="46">
         <f>modeldata!C5+modeldata!C8</f>
@@ -2821,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="AB17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC17" s="6">
         <f>P17-C17</f>
@@ -2870,7 +2864,7 @@
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="46">
         <f>SUM('BATS 2023'!P6,'BATS 2023'!P12,'BATS 2023'!P9)</f>
@@ -2917,7 +2911,7 @@
         <v>72312.696812277689</v>
       </c>
       <c r="O18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P18" s="46">
         <f>modeldata!C6+modeldata!C9+modeldata!C12</f>
@@ -2964,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="AB18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC18" s="6">
         <f t="shared" ref="AC18:AC20" si="55">P18-C18</f>
@@ -3013,7 +3007,7 @@
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="46">
         <f>SUM('BATS 2023'!P7,'BATS 2023'!P10,'BATS 2023'!P13,'BATS 2023'!P16)</f>
@@ -3060,7 +3054,7 @@
         <v>47050.923678754792</v>
       </c>
       <c r="O19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P19" s="46">
         <f>modeldata!C7+modeldata!C10+modeldata!C13+modeldata!C16</f>
@@ -3107,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="AB19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="55"/>
@@ -3156,7 +3150,7 @@
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="46">
         <f>SUM('BATS 2023'!P11,'BATS 2023'!P14,'BATS 2023'!P17)</f>
@@ -3203,7 +3197,7 @@
         <v>1806.2941002392156</v>
       </c>
       <c r="O20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P20" s="46">
         <f>modeldata!C11+modeldata!C14+modeldata!C17</f>
@@ -3250,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="AB20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="55"/>
@@ -3299,7 +3293,7 @@
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="46">
         <f>SUM('BATS 2023'!P15,'BATS 2023'!P18)</f>
@@ -3346,7 +3340,7 @@
         <v>2442.6842184043094</v>
       </c>
       <c r="O21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P21" s="46">
         <f>modeldata!C15+modeldata!C18</f>
@@ -3393,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="AB21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC21" s="6">
         <f>P21-C21</f>
@@ -3442,7 +3436,7 @@
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="49">
         <f>'BATS 2023'!P19</f>
@@ -3489,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P22" s="49">
         <f>modeldata!C19</f>
@@ -3536,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="AB22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC22" s="8">
         <f>P22-C22</f>
@@ -3585,7 +3579,7 @@
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="52">
         <f>SUM(C16:C22)</f>
@@ -3632,7 +3626,7 @@
         <v>986247.94808682636</v>
       </c>
       <c r="O23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P23" s="52">
         <f>SUM(P16:P22)</f>
@@ -3679,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC23">
         <f t="shared" ref="AC23" si="77">P23-C23</f>
@@ -3729,7 +3723,7 @@
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -3744,7 +3738,7 @@
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P25" s="12"/>
       <c r="Q25" s="12"/>
@@ -3759,7 +3753,7 @@
       <c r="Z25" s="12"/>
       <c r="AA25" s="12"/>
       <c r="AB25" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC25" s="12"/>
       <c r="AD25" s="12"/>
@@ -3876,7 +3870,7 @@
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="53">
         <f t="shared" ref="C27:M27" si="78">C4/C$8</f>
@@ -3923,7 +3917,7 @@
         <v>0.8682853920727599</v>
       </c>
       <c r="O27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P27" s="64" t="e">
         <f>P4/P$8</f>
@@ -3970,7 +3964,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC27" s="64" t="e">
         <f>P27-C27</f>
@@ -4019,7 +4013,7 @@
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="56">
         <f t="shared" ref="C28:M28" si="90">C5/C$8</f>
@@ -4066,7 +4060,7 @@
         <v>8.5456080319816399E-2</v>
       </c>
       <c r="O28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P28" s="67" t="e">
         <f t="shared" ref="P28:P30" si="91">P5/P$8</f>
@@ -4113,7 +4107,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC28" s="67" t="e">
         <f>P28-C28</f>
@@ -4162,7 +4156,7 @@
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="56">
         <f t="shared" ref="C29:M29" si="93">C6/C$8</f>
@@ -4209,7 +4203,7 @@
         <v>3.824637806832145E-2</v>
       </c>
       <c r="O29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P29" s="67" t="e">
         <f t="shared" si="91"/>
@@ -4256,7 +4250,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC29" s="67" t="e">
         <f t="shared" ref="AC29:AC31" si="95">P29-C29</f>
@@ -4305,7 +4299,7 @@
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="59">
         <f t="shared" ref="C30:M30" si="96">C7/C$8</f>
@@ -4352,7 +4346,7 @@
         <v>8.012149539102266E-3</v>
       </c>
       <c r="O30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P30" s="70" t="e">
         <f t="shared" si="91"/>
@@ -4399,7 +4393,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC30" s="70" t="e">
         <f t="shared" si="95"/>
@@ -4448,7 +4442,7 @@
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="62">
         <f t="shared" ref="C31:M31" si="98">C8/C$8</f>
@@ -4495,7 +4489,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P31" s="68" t="e">
         <f>P8/P$8</f>
@@ -4542,7 +4536,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC31" s="68" t="e">
         <f t="shared" si="95"/>
@@ -4626,7 +4620,7 @@
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33" s="53">
         <f t="shared" ref="C33:M33" si="100">C10/C$14</f>
@@ -4673,7 +4667,7 @@
         <v>0.78457862088375063</v>
       </c>
       <c r="O33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P33" s="64" t="e">
         <f>P10/P$14</f>
@@ -4720,7 +4714,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC33" s="64" t="e">
         <f>P33-C33</f>
@@ -4769,7 +4763,7 @@
     </row>
     <row r="34" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" s="56">
         <f t="shared" ref="C34:M34" si="112">C11/C$14</f>
@@ -4816,7 +4810,7 @@
         <v>0.14089019944561837</v>
       </c>
       <c r="O34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P34" s="67" t="e">
         <f t="shared" ref="P34:P36" si="113">P11/P$14</f>
@@ -4863,7 +4857,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC34" s="67" t="e">
         <f>P34-C34</f>
@@ -4912,7 +4906,7 @@
     </row>
     <row r="35" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" s="56">
         <f t="shared" ref="C35:M35" si="115">C12/C$14</f>
@@ -4959,7 +4953,7 @@
         <v>5.1638911534430627E-2</v>
       </c>
       <c r="O35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P35" s="67" t="e">
         <f t="shared" si="113"/>
@@ -5006,7 +5000,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AC35" s="67" t="e">
         <f t="shared" ref="AC35:AC37" si="117">P35-C35</f>
@@ -5055,7 +5049,7 @@
     </row>
     <row r="36" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="59">
         <f t="shared" ref="C36:M36" si="118">C13/C$14</f>
@@ -5102,7 +5096,7 @@
         <v>2.2892268136200267E-2</v>
       </c>
       <c r="O36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P36" s="70" t="e">
         <f t="shared" si="113"/>
@@ -5149,7 +5143,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC36" s="70" t="e">
         <f t="shared" si="117"/>
@@ -5198,7 +5192,7 @@
     </row>
     <row r="37" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="62">
         <f t="shared" ref="C37:M37" si="120">C14/C$14</f>
@@ -5245,7 +5239,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P37" s="68" t="e">
         <f>P14/P$14</f>
@@ -5292,7 +5286,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC37" s="68" t="e">
         <f t="shared" si="117"/>
@@ -5376,7 +5370,7 @@
     </row>
     <row r="39" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="53">
         <f t="shared" ref="C39:M39" si="122">C16/C$23</f>
@@ -5423,7 +5417,7 @@
         <v>0.68530630491170785</v>
       </c>
       <c r="O39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P39" s="64" t="e">
         <f>P16/P$23</f>
@@ -5470,7 +5464,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC39" s="64" t="e">
         <f>P39-C39</f>
@@ -5519,7 +5513,7 @@
     </row>
     <row r="40" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="56">
         <f t="shared" ref="C40:M40" si="134">C17/C$23</f>
@@ -5566,7 +5560,7 @@
         <v>0.18935746594888966</v>
       </c>
       <c r="O40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P40" s="67" t="e">
         <f t="shared" ref="P40:P45" si="135">P17/P$23</f>
@@ -5613,7 +5607,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC40" s="67" t="e">
         <f>P40-C40</f>
@@ -5662,7 +5656,7 @@
     </row>
     <row r="41" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="56">
         <f t="shared" ref="C41:M41" si="137">C18/C$23</f>
@@ -5709,7 +5703,7 @@
         <v>7.3321011164133226E-2</v>
       </c>
       <c r="O41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P41" s="67" t="e">
         <f t="shared" si="135"/>
@@ -5756,7 +5750,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC41" s="67" t="e">
         <f t="shared" ref="AC41:AC43" si="139">P41-C41</f>
@@ -5805,7 +5799,7 @@
     </row>
     <row r="42" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="56">
         <f t="shared" ref="C42:M42" si="140">C19/C$23</f>
@@ -5852,7 +5846,7 @@
         <v>4.7706992719251336E-2</v>
       </c>
       <c r="O42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P42" s="67" t="e">
         <f t="shared" si="135"/>
@@ -5899,7 +5893,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC42" s="67" t="e">
         <f t="shared" si="139"/>
@@ -5948,7 +5942,7 @@
     </row>
     <row r="43" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="56">
         <f t="shared" ref="C43:M43" si="142">C20/C$23</f>
@@ -5995,7 +5989,7 @@
         <v>1.8314807181532354E-3</v>
       </c>
       <c r="O43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P43" s="67" t="e">
         <f t="shared" si="135"/>
@@ -6042,7 +6036,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC43" s="67" t="e">
         <f t="shared" si="139"/>
@@ -6091,7 +6085,7 @@
     </row>
     <row r="44" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="56">
         <f t="shared" ref="C44:M44" si="144">C21/C$23</f>
@@ -6138,7 +6132,7 @@
         <v>2.4767445378646941E-3</v>
       </c>
       <c r="O44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P44" s="67" t="e">
         <f t="shared" si="135"/>
@@ -6185,7 +6179,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC44" s="67" t="e">
         <f>P44-C44</f>
@@ -6234,7 +6228,7 @@
     </row>
     <row r="45" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" s="59">
         <f t="shared" ref="C45:M45" si="146">C22/C$23</f>
@@ -6281,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P45" s="70" t="e">
         <f t="shared" si="135"/>
@@ -6328,7 +6322,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC45" s="70" t="e">
         <f>P45-C45</f>
@@ -6377,7 +6371,7 @@
     </row>
     <row r="46" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C46" s="62">
         <f t="shared" ref="C46:M46" si="148">C23/C$23</f>
@@ -6424,7 +6418,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P46" s="68" t="e">
         <f>P23/P$23</f>
@@ -6471,7 +6465,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC46" s="68" t="e">
         <f t="shared" ref="AC46" si="150">P46-C46</f>
@@ -6520,19 +6514,19 @@
     </row>
     <row r="48" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="11"/>
     </row>
     <row r="50" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
+        <v>50</v>
+      </c>
+      <c r="O50" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB50" t="s">
         <v>51</v>
-      </c>
-      <c r="O50" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:39" x14ac:dyDescent="0.25">
@@ -6638,10 +6632,10 @@
     </row>
     <row r="52" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C52" s="16" cm="1">
         <f t="array" ref="C52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
@@ -6688,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P52" s="16" t="e">
         <f>$C$48*LN(C27/P27)</f>
@@ -6735,7 +6729,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB52" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC52" s="16"/>
       <c r="AD52" s="17"/>
@@ -6751,10 +6745,10 @@
     </row>
     <row r="53" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C53" s="19" cm="1">
         <f t="array" ref="C53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
@@ -6801,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P53" s="19" t="e">
         <f>$C$48*LN(C28/P28)</f>
@@ -6848,7 +6842,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB53" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC53" s="19" t="e">
         <f>C53+P53-$P$52</f>
@@ -6897,10 +6891,10 @@
     </row>
     <row r="54" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" s="19" cm="1">
         <f t="array" ref="C54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
@@ -6947,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P54" s="19" t="e">
         <f>$C$48*LN(C29/P29)</f>
@@ -6994,7 +6988,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB54" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC54" s="19" t="e">
         <f t="shared" ref="AC54:AC55" si="155">C54+P54-$P$52</f>
@@ -7043,10 +7037,10 @@
     </row>
     <row r="55" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C55" s="21" cm="1">
         <f t="array" ref="C55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
@@ -7093,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P55" s="21" t="e">
         <f>$C$48*LN(C30/P30)</f>
@@ -7140,7 +7134,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB55" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC55" s="19" t="e">
         <f t="shared" si="155"/>
@@ -7189,10 +7183,10 @@
     </row>
     <row r="56" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C56" s="24" cm="1">
         <f t="array" ref="C56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
@@ -7239,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P56" s="24" t="e">
         <f>$C$48*LN(C33/P33)</f>
@@ -7286,7 +7280,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB56" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC56" s="24"/>
       <c r="AD56" s="25"/>
@@ -7302,10 +7296,10 @@
     </row>
     <row r="57" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C57" s="27" cm="1">
         <f t="array" ref="C57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
@@ -7352,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P57" s="27" t="e">
         <f>$C$48*LN(C34/P34)</f>
@@ -7399,7 +7393,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB57" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC57" s="27" t="e">
         <f t="shared" ref="AC57:AC58" si="159">C57+P57-$P$52</f>
@@ -7448,10 +7442,10 @@
     </row>
     <row r="58" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58" s="27" cm="1">
         <f t="array" ref="C58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
@@ -7498,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P58" s="27" t="e">
         <f>$C$48*LN(C35/P35)</f>
@@ -7545,7 +7539,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB58" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AC58" s="27" t="e">
         <f t="shared" si="159"/>
@@ -7594,10 +7588,10 @@
     </row>
     <row r="59" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" s="29" cm="1">
         <f t="array" ref="C59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
@@ -7644,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P59" s="29" t="e">
         <f>$C$48*LN(C36/P36)</f>
@@ -7691,7 +7685,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB59" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC59" s="29" t="e">
         <f t="shared" ref="AC59" si="171">C59+P59-$P$52</f>
@@ -7740,10 +7734,10 @@
     </row>
     <row r="60" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C60" s="32" cm="1">
         <f t="array" ref="C60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
@@ -7790,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P60" s="32" t="e">
         <f t="shared" ref="P60:P66" si="181">$C$48*LN(C39/P39)</f>
@@ -7837,7 +7831,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB60" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC60" s="32"/>
       <c r="AD60" s="33"/>
@@ -7853,10 +7847,10 @@
     </row>
     <row r="61" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C61" s="35" cm="1">
         <f t="array" ref="C61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
@@ -7903,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P61" s="35" t="e">
         <f t="shared" si="181"/>
@@ -7950,7 +7944,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB61" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC61" s="35"/>
       <c r="AD61" s="14"/>
@@ -7966,10 +7960,10 @@
     </row>
     <row r="62" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C62" s="35" cm="1">
         <f t="array" ref="C62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
@@ -8016,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P62" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8063,7 +8057,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB62" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC62" s="35" t="e">
         <f t="shared" ref="AC62:AC66" si="185">C62+P62-$P$60</f>
@@ -8112,10 +8106,10 @@
     </row>
     <row r="63" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C63" s="35" cm="1">
         <f t="array" ref="C63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
@@ -8162,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P63" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8209,7 +8203,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB63" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC63" s="35" t="e">
         <f t="shared" si="185"/>
@@ -8258,10 +8252,10 @@
     </row>
     <row r="64" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C64" s="35" cm="1">
         <f t="array" ref="C64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
@@ -8308,7 +8302,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P64" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8355,7 +8349,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB64" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC64" s="35" t="e">
         <f t="shared" si="185"/>
@@ -8404,10 +8398,10 @@
     </row>
     <row r="65" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C65" s="35" cm="1">
         <f t="array" ref="C65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
@@ -8454,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P65" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8501,7 +8495,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB65" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC65" s="35" t="e">
         <f t="shared" si="185"/>
@@ -8550,10 +8544,10 @@
     </row>
     <row r="66" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C66" s="37" cm="1">
         <f t="array" ref="C66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
@@ -8600,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P66" s="37" t="e">
         <f t="shared" si="181"/>
@@ -8647,7 +8641,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB66" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC66" s="37" t="e">
         <f t="shared" si="185"/>
@@ -8696,7 +8690,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AC27:AM45">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>ABS(AC27) &gt; 10%</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8714,405 +8708,405 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C1" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" s="73" t="s">
         <v>85</v>
-      </c>
-      <c r="S1" s="73" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>67</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>68</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>69</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>70</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>71</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>72</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>73</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>74</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>75</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>77</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>38</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>79</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G3" t="s">
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
         <v>37</v>
       </c>
-      <c r="H3" t="s">
+      <c r="V3" t="s">
         <v>38</v>
       </c>
-      <c r="I3" t="s">
+      <c r="W3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH3" t="s">
         <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>80</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" t="s">
-        <v>38</v>
-      </c>
-      <c r="V3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W3" t="s">
-        <v>37</v>
-      </c>
-      <c r="X3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" t="s">
         <v>33</v>
       </c>
-      <c r="T4" t="s">
+      <c r="X4" t="s">
         <v>33</v>
       </c>
-      <c r="U4" t="s">
+      <c r="Y4" t="s">
         <v>33</v>
       </c>
-      <c r="V4" t="s">
+      <c r="Z4" t="s">
         <v>33</v>
       </c>
-      <c r="W4" t="s">
-        <v>34</v>
-      </c>
-      <c r="X4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>34</v>
-      </c>
       <c r="AA4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AE4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AF4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AH4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="G5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="K5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="O5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="R5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="S5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="T5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="U5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="V5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="V5" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="W5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="Y5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="Y5" s="9" t="s">
+      <c r="Z5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="Z5" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="AA5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AC5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AC5" s="9" t="s">
+      <c r="AD5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AD5" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="AE5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AF5" s="9" t="s">
+      <c r="AG5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AG5" s="9" t="s">
+      <c r="AH5" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="AH5" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -9120,7 +9114,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6">
@@ -9193,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R7" s="7"/>
       <c r="S7">
@@ -9266,7 +9260,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R8" s="7"/>
       <c r="S8">
@@ -9339,7 +9333,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R9" s="7"/>
       <c r="S9">
@@ -9412,7 +9406,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R10" s="7"/>
       <c r="S10">
@@ -9485,7 +9479,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R11" s="7"/>
       <c r="S11">
@@ -9558,7 +9552,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R12" s="7"/>
       <c r="S12">
@@ -9631,7 +9625,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13">
@@ -9704,7 +9698,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R14" s="7"/>
       <c r="S14">
@@ -9777,7 +9771,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15">
@@ -9850,7 +9844,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R16" s="7"/>
       <c r="S16">
@@ -9923,7 +9917,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R17" s="7"/>
       <c r="S17">
@@ -9996,7 +9990,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R18" s="7"/>
       <c r="S18">
@@ -10069,7 +10063,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19">
@@ -10142,7 +10136,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R20" s="7"/>
       <c r="S20">
@@ -10215,7 +10209,7 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R21" s="7"/>
       <c r="S21">
@@ -10288,7 +10282,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R22" s="7"/>
       <c r="S22">
@@ -10361,7 +10355,7 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R23" s="7"/>
       <c r="S23">
@@ -10434,7 +10428,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R24" s="7"/>
       <c r="S24">
@@ -10507,7 +10501,7 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R25" s="7"/>
       <c r="S25">
@@ -10580,7 +10574,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R26" s="7"/>
       <c r="S26">
@@ -10653,7 +10647,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R27" s="7"/>
       <c r="S27">
@@ -10726,7 +10720,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R28" s="7"/>
       <c r="S28">
@@ -10799,7 +10793,7 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R29" s="7"/>
       <c r="S29">
@@ -10872,7 +10866,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R30" s="7"/>
       <c r="S30">
@@ -10945,7 +10939,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R31" s="7"/>
       <c r="S31">
@@ -11018,7 +11012,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R32" s="7"/>
       <c r="S32">
@@ -11091,7 +11085,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R33" s="7"/>
       <c r="S33">
@@ -11164,7 +11158,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R34" s="7"/>
       <c r="S34">
@@ -11237,7 +11231,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R35" s="7"/>
       <c r="S35">
@@ -11310,7 +11304,7 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R36" s="7"/>
       <c r="S36">
@@ -11383,7 +11377,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R37" s="7"/>
       <c r="S37">
@@ -11456,7 +11450,7 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R38" s="7"/>
       <c r="S38">
@@ -11700,7 +11694,7 @@
   <sheetData>
     <row r="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
@@ -12113,7 +12107,7 @@
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="42">
         <v>25474.951198525359</v>
@@ -12529,7 +12523,7 @@
     </row>
     <row r="13" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="42">
         <v>15059.392755897852</v>
@@ -12932,7 +12926,7 @@
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" s="42">
         <v>12594.924073455264</v>
@@ -13180,7 +13174,7 @@
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="42">
         <v>1668.63177660064</v>
@@ -13208,7 +13202,7 @@
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="42">
         <v>16199.986463378213</v>
@@ -13244,7 +13238,7 @@
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="42">
         <v>15058.072609072527</v>
@@ -13274,7 +13268,7 @@
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" s="42">
         <v>12989.715378425308</v>
@@ -13304,7 +13298,7 @@
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" s="42">
         <v>765.92383367125706</v>
@@ -13334,7 +13328,7 @@
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C28" s="42">
         <v>6877.3667650190509</v>

--- a/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one\utilities\calibration\workbook_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one-tm1.7_calibration\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DECCF4F-D169-4FA8-9A53-E82CC1C9364E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F1795A-B00B-4A4D-B4B6-5A96D9418CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="2" r:id="rId1"/>
@@ -64,10 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="88">
-  <si>
-    <t>Source:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="107">
   <si>
     <t>work</t>
   </si>
@@ -225,33 +222,6 @@
     <t>Change in Constant</t>
   </si>
   <si>
-    <t>0 out 4+ ret</t>
-  </si>
-  <si>
-    <t>1 out 4+ ret</t>
-  </si>
-  <si>
-    <t>2 out 4+ ret</t>
-  </si>
-  <si>
-    <t>3 out 4+ ret</t>
-  </si>
-  <si>
-    <t>4+ out 0 ret</t>
-  </si>
-  <si>
-    <t>4+ out 1 ret</t>
-  </si>
-  <si>
-    <t>4+ out 2 ret</t>
-  </si>
-  <si>
-    <t>4+ out 3 ret</t>
-  </si>
-  <si>
-    <t>4+ out 4+ ret</t>
-  </si>
-  <si>
     <t>Alt1</t>
   </si>
   <si>
@@ -327,7 +297,94 @@
     <t>Outbound Stops</t>
   </si>
   <si>
-    <t>Source: M:\Development\Travel Model One\Calibration\Version 1.7\2023_BATS_Summaries\pipeline_mt_20260821_NoMon_rmo\ctramp_2023\BATS_Summaries\BATS2023_stop_frequency.xlsx</t>
+    <t>outbound_inbound</t>
+  </si>
+  <si>
+    <t>ind_maint</t>
+  </si>
+  <si>
+    <t>social</t>
+  </si>
+  <si>
+    <t>ind_disc</t>
+  </si>
+  <si>
+    <t>0 out, 0 in</t>
+  </si>
+  <si>
+    <t>0 out, 1 in</t>
+  </si>
+  <si>
+    <t>0 out, 2 in</t>
+  </si>
+  <si>
+    <t>0 out, 3 in</t>
+  </si>
+  <si>
+    <t>0 out, 4 in</t>
+  </si>
+  <si>
+    <t>1 out, 0 in</t>
+  </si>
+  <si>
+    <t>1 out, 1 in</t>
+  </si>
+  <si>
+    <t>1 out, 2 in</t>
+  </si>
+  <si>
+    <t>1 out, 3 in</t>
+  </si>
+  <si>
+    <t>1 out, 4 in</t>
+  </si>
+  <si>
+    <t>2 out, 0 in</t>
+  </si>
+  <si>
+    <t>2 out, 1 in</t>
+  </si>
+  <si>
+    <t>2 out, 2 in</t>
+  </si>
+  <si>
+    <t>2 out, 3 in</t>
+  </si>
+  <si>
+    <t>2 out, 4 in</t>
+  </si>
+  <si>
+    <t>3 out, 0 in</t>
+  </si>
+  <si>
+    <t>3 out, 1 in</t>
+  </si>
+  <si>
+    <t>3 out, 2 in</t>
+  </si>
+  <si>
+    <t>3 out, 3 in</t>
+  </si>
+  <si>
+    <t>3 out, 4 in</t>
+  </si>
+  <si>
+    <t>4 out, 0 in</t>
+  </si>
+  <si>
+    <t>4 out, 1 in</t>
+  </si>
+  <si>
+    <t>4 out, 2 in</t>
+  </si>
+  <si>
+    <t>4 out, 3 in</t>
+  </si>
+  <si>
+    <t>4 out, 4 in</t>
+  </si>
+  <si>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/12_stop_freq_summary_BATS.csv</t>
   </si>
 </sst>
 </file>
@@ -965,7 +1022,7 @@
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
@@ -979,7 +1036,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P2" s="12"/>
       <c r="Q2" s="12"/>
@@ -994,7 +1051,7 @@
       <c r="Z2" s="12"/>
       <c r="AA2" s="12"/>
       <c r="AB2" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC2" s="12"/>
       <c r="AD2" s="12"/>
@@ -1010,155 +1067,155 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>9</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" t="s">
-        <v>11</v>
-      </c>
       <c r="P3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>2</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>3</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>4</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>5</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>7</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>8</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>9</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>10</v>
       </c>
-      <c r="Z3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>2</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>4</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>5</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>6</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>7</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>8</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>9</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AM3" t="s">
         <v>10</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="43">
-        <f>SUM('BATS 2023'!P4:P7)</f>
-        <v>1558003.9276389708</v>
+        <f>SUM('BATS 2023'!Q4:Q7)</f>
+        <v>19346</v>
       </c>
       <c r="D4" s="44">
-        <f>SUM('BATS 2023'!Q4:Q7)</f>
-        <v>40554.737344252106</v>
+        <f>SUM('BATS 2023'!R4:R7)</f>
+        <v>440</v>
       </c>
       <c r="E4" s="44">
-        <f>SUM('BATS 2023'!R4:R7)</f>
-        <v>269189.68761484697</v>
+        <f>SUM('BATS 2023'!S4:S7)</f>
+        <v>2368</v>
       </c>
       <c r="F4" s="44">
-        <f>SUM('BATS 2023'!S4:S7)</f>
-        <v>1275852.788037058</v>
+        <f>SUM('BATS 2023'!T4:T7)</f>
+        <v>11754</v>
       </c>
       <c r="G4" s="44">
-        <f>SUM('BATS 2023'!T4:T7)</f>
-        <v>638257.90033213084</v>
+        <f>SUM('BATS 2023'!U4:U7)</f>
+        <v>12910</v>
       </c>
       <c r="H4" s="44">
-        <f>SUM('BATS 2023'!U4:U7)</f>
-        <v>464601.533179486</v>
+        <f>SUM('BATS 2023'!V4:V7)</f>
+        <v>8324</v>
       </c>
       <c r="I4" s="44">
-        <f>SUM('BATS 2023'!V4:V7)</f>
-        <v>500267.25010883139</v>
+        <f>SUM('BATS 2023'!W4:W7)</f>
+        <v>9598</v>
       </c>
       <c r="J4" s="44">
-        <f>SUM('BATS 2023'!W4:W7)</f>
-        <v>1395681.293290538</v>
+        <f>SUM('BATS 2023'!X4:X7)</f>
+        <v>27932</v>
       </c>
       <c r="K4" s="44">
-        <f>SUM('BATS 2023'!X4:X7)</f>
-        <v>220060.53639025931</v>
+        <f>SUM('BATS 2023'!Y4:Y7)</f>
+        <v>3450</v>
       </c>
       <c r="L4" s="44">
-        <f>SUM('BATS 2023'!Y4:Y7)</f>
-        <v>316634.84347537957</v>
+        <f>SUM('BATS 2023'!Z4:Z7)</f>
+        <v>3560</v>
       </c>
       <c r="M4" s="45">
-        <f>SUM('BATS 2023'!Z4:Z7)</f>
-        <v>856344.68628552498</v>
+        <f>SUM('BATS 2023'!AA4:AA7)</f>
+        <v>36074</v>
       </c>
       <c r="O4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P4" s="43">
         <f>SUM(modeldata!C4:C7)</f>
@@ -1205,103 +1262,103 @@
         <v>0</v>
       </c>
       <c r="AB4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC4" s="3">
         <f>P4-C4</f>
-        <v>-1558003.9276389708</v>
+        <v>-19346</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" ref="AD4:AM5" si="0">Q4-D4</f>
-        <v>-40554.737344252106</v>
+        <v>-440</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="0"/>
-        <v>-269189.68761484697</v>
+        <v>-2368</v>
       </c>
       <c r="AF4" s="4">
         <f t="shared" si="0"/>
-        <v>-1275852.788037058</v>
+        <v>-11754</v>
       </c>
       <c r="AG4" s="4">
         <f t="shared" si="0"/>
-        <v>-638257.90033213084</v>
+        <v>-12910</v>
       </c>
       <c r="AH4" s="4">
         <f t="shared" si="0"/>
-        <v>-464601.533179486</v>
+        <v>-8324</v>
       </c>
       <c r="AI4" s="4">
         <f t="shared" si="0"/>
-        <v>-500267.25010883139</v>
+        <v>-9598</v>
       </c>
       <c r="AJ4" s="4">
         <f t="shared" si="0"/>
-        <v>-1395681.293290538</v>
+        <v>-27932</v>
       </c>
       <c r="AK4" s="4">
         <f t="shared" si="0"/>
-        <v>-220060.53639025931</v>
+        <v>-3450</v>
       </c>
       <c r="AL4" s="4">
         <f t="shared" si="0"/>
-        <v>-316634.84347537957</v>
+        <v>-3560</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="0"/>
-        <v>-856344.68628552498</v>
+        <v>-36074</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="46">
-        <f>SUM('BATS 2023'!P8:P11)</f>
-        <v>334175.82879334752</v>
+        <f>SUM('BATS 2023'!Q8:Q11)</f>
+        <v>4680</v>
       </c>
       <c r="D5" s="47">
-        <f>SUM('BATS 2023'!Q8:Q11)</f>
-        <v>6595.3494639700066</v>
+        <f>SUM('BATS 2023'!R8:R11)</f>
+        <v>94</v>
       </c>
       <c r="E5" s="47">
-        <f>SUM('BATS 2023'!R8:R11)</f>
-        <v>29870.186099394396</v>
+        <f>SUM('BATS 2023'!S8:S11)</f>
+        <v>222</v>
       </c>
       <c r="F5" s="47">
-        <f>SUM('BATS 2023'!S8:S11)</f>
-        <v>76033.312467158146</v>
+        <f>SUM('BATS 2023'!T8:T11)</f>
+        <v>896</v>
       </c>
       <c r="G5" s="47">
-        <f>SUM('BATS 2023'!T8:T11)</f>
-        <v>268600.22656890086</v>
+        <f>SUM('BATS 2023'!U8:U11)</f>
+        <v>4774</v>
       </c>
       <c r="H5" s="47">
-        <f>SUM('BATS 2023'!U8:U11)</f>
-        <v>84270.781166042041</v>
+        <f>SUM('BATS 2023'!V8:V11)</f>
+        <v>1704</v>
       </c>
       <c r="I5" s="47">
-        <f>SUM('BATS 2023'!V8:V11)</f>
-        <v>126933.38226799679</v>
+        <f>SUM('BATS 2023'!W8:W11)</f>
+        <v>3174</v>
       </c>
       <c r="J5" s="47">
-        <f>SUM('BATS 2023'!W8:W11)</f>
-        <v>123752.49077900458</v>
+        <f>SUM('BATS 2023'!X8:X11)</f>
+        <v>3548</v>
       </c>
       <c r="K5" s="47">
-        <f>SUM('BATS 2023'!X8:X11)</f>
-        <v>33041.153390274456</v>
+        <f>SUM('BATS 2023'!Y8:Y11)</f>
+        <v>480</v>
       </c>
       <c r="L5" s="47">
-        <f>SUM('BATS 2023'!Y8:Y11)</f>
-        <v>22597.761890965921</v>
+        <f>SUM('BATS 2023'!Z8:Z11)</f>
+        <v>344</v>
       </c>
       <c r="M5" s="48">
-        <f>SUM('BATS 2023'!Z8:Z11)</f>
-        <v>84280.883866961944</v>
+        <f>SUM('BATS 2023'!AA8:AA11)</f>
+        <v>6942</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P5" s="46">
         <f>SUM(modeldata!C8:C11)</f>
@@ -1348,103 +1405,103 @@
         <v>0</v>
       </c>
       <c r="AB5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC5" s="6">
         <f>P5-C5</f>
-        <v>-334175.82879334752</v>
+        <v>-4680</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>-6595.3494639700066</v>
+        <v>-94</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>-29870.186099394396</v>
+        <v>-222</v>
       </c>
       <c r="AF5">
         <f t="shared" si="0"/>
-        <v>-76033.312467158146</v>
+        <v>-896</v>
       </c>
       <c r="AG5">
         <f t="shared" si="0"/>
-        <v>-268600.22656890086</v>
+        <v>-4774</v>
       </c>
       <c r="AH5">
         <f t="shared" si="0"/>
-        <v>-84270.781166042041</v>
+        <v>-1704</v>
       </c>
       <c r="AI5">
         <f t="shared" si="0"/>
-        <v>-126933.38226799679</v>
+        <v>-3174</v>
       </c>
       <c r="AJ5">
         <f t="shared" si="0"/>
-        <v>-123752.49077900458</v>
+        <v>-3548</v>
       </c>
       <c r="AK5">
         <f t="shared" si="0"/>
-        <v>-33041.153390274456</v>
+        <v>-480</v>
       </c>
       <c r="AL5">
         <f t="shared" si="0"/>
-        <v>-22597.761890965921</v>
+        <v>-344</v>
       </c>
       <c r="AM5" s="7">
         <f t="shared" si="0"/>
-        <v>-84280.883866961944</v>
+        <v>-6942</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="46">
-        <f>SUM('BATS 2023'!P12:P15)</f>
-        <v>104577.12847181715</v>
+        <f>SUM('BATS 2023'!Q12:Q15)</f>
+        <v>1862</v>
       </c>
       <c r="D6" s="47">
-        <f>SUM('BATS 2023'!Q12:Q15)</f>
-        <v>9158.2600182803781</v>
+        <f>SUM('BATS 2023'!R12:R15)</f>
+        <v>24</v>
       </c>
       <c r="E6" s="47">
-        <f>SUM('BATS 2023'!R12:R15)</f>
-        <v>3093.6038179482925</v>
+        <f>SUM('BATS 2023'!S12:S15)</f>
+        <v>44</v>
       </c>
       <c r="F6" s="47">
-        <f>SUM('BATS 2023'!S12:S15)</f>
-        <v>17942.07688911595</v>
+        <f>SUM('BATS 2023'!T12:T15)</f>
+        <v>228</v>
       </c>
       <c r="G6" s="47">
-        <f>SUM('BATS 2023'!T12:T15)</f>
-        <v>111055.81639316399</v>
+        <f>SUM('BATS 2023'!U12:U15)</f>
+        <v>2048</v>
       </c>
       <c r="H6" s="47">
-        <f>SUM('BATS 2023'!U12:U15)</f>
-        <v>21641.367596702308</v>
+        <f>SUM('BATS 2023'!V12:V15)</f>
+        <v>598</v>
       </c>
       <c r="I6" s="47">
-        <f>SUM('BATS 2023'!V12:V15)</f>
-        <v>69263.29137108245</v>
+        <f>SUM('BATS 2023'!W12:W15)</f>
+        <v>1306</v>
       </c>
       <c r="J6" s="47">
-        <f>SUM('BATS 2023'!W12:W15)</f>
-        <v>66797.207403039327</v>
+        <f>SUM('BATS 2023'!X12:X15)</f>
+        <v>1756</v>
       </c>
       <c r="K6" s="47">
-        <f>SUM('BATS 2023'!X12:X15)</f>
-        <v>22410.180108614444</v>
+        <f>SUM('BATS 2023'!Y12:Y15)</f>
+        <v>212</v>
       </c>
       <c r="L6" s="47">
-        <f>SUM('BATS 2023'!Y12:Y15)</f>
-        <v>5802.2079246804597</v>
+        <f>SUM('BATS 2023'!Z12:Z15)</f>
+        <v>82</v>
       </c>
       <c r="M6" s="48">
-        <f>SUM('BATS 2023'!Z12:Z15)</f>
-        <v>37720.411891635027</v>
+        <f>SUM('BATS 2023'!AA12:AA15)</f>
+        <v>2620</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P6" s="46">
         <f>SUM(modeldata!C12:C15)</f>
@@ -1491,103 +1548,103 @@
         <v>0</v>
       </c>
       <c r="AB6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC6" s="6">
         <f t="shared" ref="AC6:AC8" si="1">P6-C6</f>
-        <v>-104577.12847181715</v>
+        <v>-1862</v>
       </c>
       <c r="AD6">
         <f t="shared" ref="AD6:AD8" si="2">Q6-D6</f>
-        <v>-9158.2600182803781</v>
+        <v>-24</v>
       </c>
       <c r="AE6">
         <f t="shared" ref="AE6:AE8" si="3">R6-E6</f>
-        <v>-3093.6038179482925</v>
+        <v>-44</v>
       </c>
       <c r="AF6">
         <f t="shared" ref="AF6:AF8" si="4">S6-F6</f>
-        <v>-17942.07688911595</v>
+        <v>-228</v>
       </c>
       <c r="AG6">
         <f t="shared" ref="AG6:AG8" si="5">T6-G6</f>
-        <v>-111055.81639316399</v>
+        <v>-2048</v>
       </c>
       <c r="AH6">
         <f t="shared" ref="AH6:AH8" si="6">U6-H6</f>
-        <v>-21641.367596702308</v>
+        <v>-598</v>
       </c>
       <c r="AI6">
         <f t="shared" ref="AI6:AI8" si="7">V6-I6</f>
-        <v>-69263.29137108245</v>
+        <v>-1306</v>
       </c>
       <c r="AJ6">
         <f t="shared" ref="AJ6:AJ8" si="8">W6-J6</f>
-        <v>-66797.207403039327</v>
+        <v>-1756</v>
       </c>
       <c r="AK6">
         <f t="shared" ref="AK6:AK8" si="9">X6-K6</f>
-        <v>-22410.180108614444</v>
+        <v>-212</v>
       </c>
       <c r="AL6">
         <f t="shared" ref="AL6:AL8" si="10">Y6-L6</f>
-        <v>-5802.2079246804597</v>
+        <v>-82</v>
       </c>
       <c r="AM6" s="7">
         <f t="shared" ref="AM6:AM8" si="11">Z6-M6</f>
-        <v>-37720.411891635027</v>
+        <v>-2620</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="49">
-        <f>SUM('BATS 2023'!P16:P19)</f>
-        <v>94984.439169259931</v>
+        <f>SUM('BATS 2023'!Q16:Q19)</f>
+        <v>1316</v>
       </c>
       <c r="D7" s="50">
-        <f>SUM('BATS 2023'!Q16:Q19)</f>
-        <v>928.17711670697759</v>
+        <f>SUM('BATS 2023'!R16:R19)</f>
+        <v>24</v>
       </c>
       <c r="E7" s="50">
-        <f>SUM('BATS 2023'!R16:R19)</f>
-        <v>240.33739060658587</v>
+        <f>SUM('BATS 2023'!S16:S19)</f>
+        <v>16</v>
       </c>
       <c r="F7" s="50">
-        <f>SUM('BATS 2023'!S16:S19)</f>
-        <v>4693.3019791369443</v>
+        <f>SUM('BATS 2023'!T16:T19)</f>
+        <v>92</v>
       </c>
       <c r="G7" s="50">
-        <f>SUM('BATS 2023'!T16:T19)</f>
-        <v>81296.670616799427</v>
+        <f>SUM('BATS 2023'!U16:U19)</f>
+        <v>1648</v>
       </c>
       <c r="H7" s="50">
-        <f>SUM('BATS 2023'!U16:U19)</f>
-        <v>17595.476025049709</v>
+        <f>SUM('BATS 2023'!V16:V19)</f>
+        <v>392</v>
       </c>
       <c r="I7" s="50">
-        <f>SUM('BATS 2023'!V16:V19)</f>
-        <v>33765.787575421375</v>
+        <f>SUM('BATS 2023'!W16:W19)</f>
+        <v>1266</v>
       </c>
       <c r="J7" s="50">
-        <f>SUM('BATS 2023'!W16:W19)</f>
-        <v>43375.017829872064</v>
+        <f>SUM('BATS 2023'!X16:X19)</f>
+        <v>1056</v>
       </c>
       <c r="K7" s="50">
-        <f>SUM('BATS 2023'!X16:X19)</f>
-        <v>4938.4636707453956</v>
+        <f>SUM('BATS 2023'!Y16:Y19)</f>
+        <v>192</v>
       </c>
       <c r="L7" s="50">
-        <f>SUM('BATS 2023'!Y16:Y19)</f>
-        <v>3757.2363234172062</v>
+        <f>SUM('BATS 2023'!Z16:Z19)</f>
+        <v>62</v>
       </c>
       <c r="M7" s="51">
-        <f>SUM('BATS 2023'!Z16:Z19)</f>
-        <v>7901.9660427044219</v>
+        <f>SUM('BATS 2023'!AA16:AA19)</f>
+        <v>1270</v>
       </c>
       <c r="O7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P7" s="49">
         <f>SUM(modeldata!C16:C19)</f>
@@ -1634,103 +1691,103 @@
         <v>0</v>
       </c>
       <c r="AB7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC7" s="8">
         <f t="shared" si="1"/>
-        <v>-94984.439169259931</v>
+        <v>-1316</v>
       </c>
       <c r="AD7" s="9">
         <f t="shared" si="2"/>
-        <v>-928.17711670697759</v>
+        <v>-24</v>
       </c>
       <c r="AE7" s="9">
         <f t="shared" si="3"/>
-        <v>-240.33739060658587</v>
+        <v>-16</v>
       </c>
       <c r="AF7" s="9">
         <f t="shared" si="4"/>
-        <v>-4693.3019791369443</v>
+        <v>-92</v>
       </c>
       <c r="AG7" s="9">
         <f t="shared" si="5"/>
-        <v>-81296.670616799427</v>
+        <v>-1648</v>
       </c>
       <c r="AH7" s="9">
         <f t="shared" si="6"/>
-        <v>-17595.476025049709</v>
+        <v>-392</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="7"/>
-        <v>-33765.787575421375</v>
+        <v>-1266</v>
       </c>
       <c r="AJ7" s="9">
         <f t="shared" si="8"/>
-        <v>-43375.017829872064</v>
+        <v>-1056</v>
       </c>
       <c r="AK7" s="9">
         <f t="shared" si="9"/>
-        <v>-4938.4636707453956</v>
+        <v>-192</v>
       </c>
       <c r="AL7" s="9">
         <f t="shared" si="10"/>
-        <v>-3757.2363234172062</v>
+        <v>-62</v>
       </c>
       <c r="AM7" s="10">
         <f t="shared" si="11"/>
-        <v>-7901.9660427044219</v>
+        <v>-1270</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="52">
         <f>SUM(C4:C7)</f>
-        <v>2091741.3240733955</v>
+        <v>27204</v>
       </c>
       <c r="D8" s="52">
         <f t="shared" ref="D8:M8" si="12">SUM(D4:D7)</f>
-        <v>57236.523943209468</v>
+        <v>582</v>
       </c>
       <c r="E8" s="52">
         <f t="shared" si="12"/>
-        <v>302393.81492279627</v>
+        <v>2650</v>
       </c>
       <c r="F8" s="52">
         <f t="shared" si="12"/>
-        <v>1374521.4793724688</v>
+        <v>12970</v>
       </c>
       <c r="G8" s="52">
         <f t="shared" si="12"/>
-        <v>1099210.6139109952</v>
+        <v>21380</v>
       </c>
       <c r="H8" s="52">
         <f t="shared" si="12"/>
-        <v>588109.15796728001</v>
+        <v>11018</v>
       </c>
       <c r="I8" s="52">
         <f t="shared" si="12"/>
-        <v>730229.71132333204</v>
+        <v>15344</v>
       </c>
       <c r="J8" s="52">
         <f t="shared" si="12"/>
-        <v>1629606.0093024538</v>
+        <v>34292</v>
       </c>
       <c r="K8" s="52">
         <f t="shared" si="12"/>
-        <v>280450.3335598936</v>
+        <v>4334</v>
       </c>
       <c r="L8" s="52">
         <f t="shared" si="12"/>
-        <v>348792.04961444315</v>
+        <v>4048</v>
       </c>
       <c r="M8" s="52">
         <f t="shared" si="12"/>
-        <v>986247.94808682636</v>
+        <v>46906</v>
       </c>
       <c r="O8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P8" s="52">
         <f>SUM(P4:P7)</f>
@@ -1777,51 +1834,51 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC8">
         <f t="shared" si="1"/>
-        <v>-2091741.3240733955</v>
+        <v>-27204</v>
       </c>
       <c r="AD8">
         <f t="shared" si="2"/>
-        <v>-57236.523943209468</v>
+        <v>-582</v>
       </c>
       <c r="AE8">
         <f t="shared" si="3"/>
-        <v>-302393.81492279627</v>
+        <v>-2650</v>
       </c>
       <c r="AF8">
         <f t="shared" si="4"/>
-        <v>-1374521.4793724688</v>
+        <v>-12970</v>
       </c>
       <c r="AG8">
         <f t="shared" si="5"/>
-        <v>-1099210.6139109952</v>
+        <v>-21380</v>
       </c>
       <c r="AH8">
         <f t="shared" si="6"/>
-        <v>-588109.15796728001</v>
+        <v>-11018</v>
       </c>
       <c r="AI8">
         <f t="shared" si="7"/>
-        <v>-730229.71132333204</v>
+        <v>-15344</v>
       </c>
       <c r="AJ8">
         <f t="shared" si="8"/>
-        <v>-1629606.0093024538</v>
+        <v>-34292</v>
       </c>
       <c r="AK8">
         <f t="shared" si="9"/>
-        <v>-280450.3335598936</v>
+        <v>-4334</v>
       </c>
       <c r="AL8">
         <f t="shared" si="10"/>
-        <v>-348792.04961444315</v>
+        <v>-4048</v>
       </c>
       <c r="AM8">
         <f t="shared" si="11"/>
-        <v>-986247.94808682636</v>
+        <v>-46906</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1839,54 +1896,54 @@
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="43">
-        <f>SUM('BATS 2023'!P4,'BATS 2023'!P8,'BATS 2023'!P12,'BATS 2023'!P16)</f>
-        <v>1321128.7780180252</v>
+        <f>SUM('BATS 2023'!Q4,'BATS 2023'!Q8,'BATS 2023'!Q12,'BATS 2023'!Q16)</f>
+        <v>17838</v>
       </c>
       <c r="D10" s="44">
-        <f>SUM('BATS 2023'!Q4,'BATS 2023'!Q8,'BATS 2023'!Q12,'BATS 2023'!Q16)</f>
-        <v>34637.362970421316</v>
+        <f>SUM('BATS 2023'!R4,'BATS 2023'!R8,'BATS 2023'!R12,'BATS 2023'!R16)</f>
+        <v>430</v>
       </c>
       <c r="E10" s="44">
-        <f>SUM('BATS 2023'!R4,'BATS 2023'!R8,'BATS 2023'!R12,'BATS 2023'!R16)</f>
-        <v>249751.1608017234</v>
+        <f>SUM('BATS 2023'!S4,'BATS 2023'!S8,'BATS 2023'!S12,'BATS 2023'!S16)</f>
+        <v>2102</v>
       </c>
       <c r="F10" s="44">
-        <f>SUM('BATS 2023'!S4,'BATS 2023'!S8,'BATS 2023'!S12,'BATS 2023'!S16)</f>
-        <v>1244757.6781573638</v>
+        <f>SUM('BATS 2023'!T4,'BATS 2023'!T8,'BATS 2023'!T12,'BATS 2023'!T16)</f>
+        <v>11578</v>
       </c>
       <c r="G10" s="44">
-        <f>SUM('BATS 2023'!T4,'BATS 2023'!T8,'BATS 2023'!T12,'BATS 2023'!T16)</f>
-        <v>767162.37650448969</v>
+        <f>SUM('BATS 2023'!U4,'BATS 2023'!U8,'BATS 2023'!U12,'BATS 2023'!U16)</f>
+        <v>15402</v>
       </c>
       <c r="H10" s="44">
-        <f>SUM('BATS 2023'!U4,'BATS 2023'!U8,'BATS 2023'!U12,'BATS 2023'!U16)</f>
-        <v>382526.16276042891</v>
+        <f>SUM('BATS 2023'!V4,'BATS 2023'!V8,'BATS 2023'!V12,'BATS 2023'!V16)</f>
+        <v>7714</v>
       </c>
       <c r="I10" s="44">
-        <f>SUM('BATS 2023'!V4,'BATS 2023'!V8,'BATS 2023'!V12,'BATS 2023'!V16)</f>
-        <v>546795.82724139979</v>
+        <f>SUM('BATS 2023'!W4,'BATS 2023'!W8,'BATS 2023'!W12,'BATS 2023'!W16)</f>
+        <v>11286</v>
       </c>
       <c r="J10" s="44">
-        <f>SUM('BATS 2023'!W4,'BATS 2023'!W8,'BATS 2023'!W12,'BATS 2023'!W16)</f>
-        <v>1390208.0819702325</v>
+        <f>SUM('BATS 2023'!X4,'BATS 2023'!X8,'BATS 2023'!X12,'BATS 2023'!X16)</f>
+        <v>29070</v>
       </c>
       <c r="K10" s="44">
-        <f>SUM('BATS 2023'!X4,'BATS 2023'!X8,'BATS 2023'!X12,'BATS 2023'!X16)</f>
-        <v>202888.85742930585</v>
+        <f>SUM('BATS 2023'!Y4,'BATS 2023'!Y8,'BATS 2023'!Y12,'BATS 2023'!Y16)</f>
+        <v>3536</v>
       </c>
       <c r="L10" s="44">
-        <f>SUM('BATS 2023'!Y4,'BATS 2023'!Y8,'BATS 2023'!Y12,'BATS 2023'!Y16)</f>
-        <v>303511.45440985123</v>
+        <f>SUM('BATS 2023'!Z4,'BATS 2023'!Z8,'BATS 2023'!Z12,'BATS 2023'!Z16)</f>
+        <v>3704</v>
       </c>
       <c r="M10" s="45">
-        <f>SUM('BATS 2023'!Z4,'BATS 2023'!Z8,'BATS 2023'!Z12,'BATS 2023'!Z16)</f>
-        <v>773789.05495939124</v>
+        <f>SUM('BATS 2023'!AA4,'BATS 2023'!AA8,'BATS 2023'!AA12,'BATS 2023'!AA16)</f>
+        <v>37348</v>
       </c>
       <c r="O10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P10" s="43">
         <f>modeldata!C4+modeldata!C8+modeldata!C12+modeldata!C16</f>
@@ -1933,103 +1990,103 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC10" s="3">
         <f>P10-C10</f>
-        <v>-1321128.7780180252</v>
+        <v>-17838</v>
       </c>
       <c r="AD10" s="4">
         <f t="shared" ref="AD10:AD14" si="23">Q10-D10</f>
-        <v>-34637.362970421316</v>
+        <v>-430</v>
       </c>
       <c r="AE10" s="4">
         <f t="shared" ref="AE10:AE14" si="24">R10-E10</f>
-        <v>-249751.1608017234</v>
+        <v>-2102</v>
       </c>
       <c r="AF10" s="4">
         <f t="shared" ref="AF10:AF14" si="25">S10-F10</f>
-        <v>-1244757.6781573638</v>
+        <v>-11578</v>
       </c>
       <c r="AG10" s="4">
         <f t="shared" ref="AG10:AG14" si="26">T10-G10</f>
-        <v>-767162.37650448969</v>
+        <v>-15402</v>
       </c>
       <c r="AH10" s="4">
         <f t="shared" ref="AH10:AH14" si="27">U10-H10</f>
-        <v>-382526.16276042891</v>
+        <v>-7714</v>
       </c>
       <c r="AI10" s="4">
         <f t="shared" ref="AI10:AI14" si="28">V10-I10</f>
-        <v>-546795.82724139979</v>
+        <v>-11286</v>
       </c>
       <c r="AJ10" s="4">
         <f t="shared" ref="AJ10:AJ14" si="29">W10-J10</f>
-        <v>-1390208.0819702325</v>
+        <v>-29070</v>
       </c>
       <c r="AK10" s="4">
         <f t="shared" ref="AK10:AK14" si="30">X10-K10</f>
-        <v>-202888.85742930585</v>
+        <v>-3536</v>
       </c>
       <c r="AL10" s="4">
         <f t="shared" ref="AL10:AL14" si="31">Y10-L10</f>
-        <v>-303511.45440985123</v>
+        <v>-3704</v>
       </c>
       <c r="AM10" s="5">
         <f t="shared" ref="AM10:AM14" si="32">Z10-M10</f>
-        <v>-773789.05495939124</v>
+        <v>-37348</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="46">
-        <f>SUM('BATS 2023'!P5,'BATS 2023'!P9,'BATS 2023'!P13,'BATS 2023'!P17)</f>
-        <v>477998.02468950959</v>
+        <f>SUM('BATS 2023'!Q5,'BATS 2023'!Q9,'BATS 2023'!Q13,'BATS 2023'!Q17)</f>
+        <v>5898</v>
       </c>
       <c r="D11" s="47">
-        <f>SUM('BATS 2023'!Q5,'BATS 2023'!Q9,'BATS 2023'!Q13,'BATS 2023'!Q17)</f>
-        <v>21098.041730334491</v>
+        <f>SUM('BATS 2023'!R5,'BATS 2023'!R9,'BATS 2023'!R13,'BATS 2023'!R17)</f>
+        <v>110</v>
       </c>
       <c r="E11" s="47">
-        <f>SUM('BATS 2023'!R5,'BATS 2023'!R9,'BATS 2023'!R13,'BATS 2023'!R17)</f>
-        <v>43208.15595590973</v>
+        <f>SUM('BATS 2023'!S5,'BATS 2023'!S9,'BATS 2023'!S13,'BATS 2023'!S17)</f>
+        <v>372</v>
       </c>
       <c r="F11" s="47">
-        <f>SUM('BATS 2023'!S5,'BATS 2023'!S9,'BATS 2023'!S13,'BATS 2023'!S17)</f>
-        <v>113234.86809676183</v>
+        <f>SUM('BATS 2023'!T5,'BATS 2023'!T9,'BATS 2023'!T13,'BATS 2023'!T17)</f>
+        <v>1192</v>
       </c>
       <c r="G11" s="47">
-        <f>SUM('BATS 2023'!T5,'BATS 2023'!T9,'BATS 2023'!T13,'BATS 2023'!T17)</f>
-        <v>215114.53379606016</v>
+        <f>SUM('BATS 2023'!U5,'BATS 2023'!U9,'BATS 2023'!U13,'BATS 2023'!U17)</f>
+        <v>4014</v>
       </c>
       <c r="H11" s="47">
-        <f>SUM('BATS 2023'!U5,'BATS 2023'!U9,'BATS 2023'!U13,'BATS 2023'!U17)</f>
-        <v>144100.43284247603</v>
+        <f>SUM('BATS 2023'!V5,'BATS 2023'!V9,'BATS 2023'!V13,'BATS 2023'!V17)</f>
+        <v>2246</v>
       </c>
       <c r="I11" s="47">
-        <f>SUM('BATS 2023'!V5,'BATS 2023'!V9,'BATS 2023'!V13,'BATS 2023'!V17)</f>
-        <v>104408.38179012193</v>
+        <f>SUM('BATS 2023'!W5,'BATS 2023'!W9,'BATS 2023'!W13,'BATS 2023'!W17)</f>
+        <v>2636</v>
       </c>
       <c r="J11" s="47">
-        <f>SUM('BATS 2023'!W5,'BATS 2023'!W9,'BATS 2023'!W13,'BATS 2023'!W17)</f>
-        <v>172582.78835435343</v>
+        <f>SUM('BATS 2023'!X5,'BATS 2023'!X9,'BATS 2023'!X13,'BATS 2023'!X17)</f>
+        <v>3682</v>
       </c>
       <c r="K11" s="47">
-        <f>SUM('BATS 2023'!X5,'BATS 2023'!X9,'BATS 2023'!X13,'BATS 2023'!X17)</f>
-        <v>58409.15164208605</v>
+        <f>SUM('BATS 2023'!Y5,'BATS 2023'!Y9,'BATS 2023'!Y13,'BATS 2023'!Y17)</f>
+        <v>552</v>
       </c>
       <c r="L11" s="47">
-        <f>SUM('BATS 2023'!Y5,'BATS 2023'!Y9,'BATS 2023'!Y13,'BATS 2023'!Y17)</f>
-        <v>36362.485849871642</v>
+        <f>SUM('BATS 2023'!Z5,'BATS 2023'!Z9,'BATS 2023'!Z13,'BATS 2023'!Z17)</f>
+        <v>274</v>
       </c>
       <c r="M11" s="48">
-        <f>SUM('BATS 2023'!Z5,'BATS 2023'!Z9,'BATS 2023'!Z13,'BATS 2023'!Z17)</f>
-        <v>138952.67010878486</v>
+        <f>SUM('BATS 2023'!AA5,'BATS 2023'!AA9,'BATS 2023'!AA13,'BATS 2023'!AA17)</f>
+        <v>7002</v>
       </c>
       <c r="O11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P11" s="46">
         <f>modeldata!C5+modeldata!C9+modeldata!C13+modeldata!C17</f>
@@ -2076,103 +2133,103 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC11" s="6">
         <f>P11-C11</f>
-        <v>-477998.02468950959</v>
+        <v>-5898</v>
       </c>
       <c r="AD11">
         <f t="shared" si="23"/>
-        <v>-21098.041730334491</v>
+        <v>-110</v>
       </c>
       <c r="AE11">
         <f t="shared" si="24"/>
-        <v>-43208.15595590973</v>
+        <v>-372</v>
       </c>
       <c r="AF11">
         <f t="shared" si="25"/>
-        <v>-113234.86809676183</v>
+        <v>-1192</v>
       </c>
       <c r="AG11">
         <f t="shared" si="26"/>
-        <v>-215114.53379606016</v>
+        <v>-4014</v>
       </c>
       <c r="AH11">
         <f t="shared" si="27"/>
-        <v>-144100.43284247603</v>
+        <v>-2246</v>
       </c>
       <c r="AI11">
         <f t="shared" si="28"/>
-        <v>-104408.38179012193</v>
+        <v>-2636</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="29"/>
-        <v>-172582.78835435343</v>
+        <v>-3682</v>
       </c>
       <c r="AK11">
         <f t="shared" si="30"/>
-        <v>-58409.15164208605</v>
+        <v>-552</v>
       </c>
       <c r="AL11">
         <f t="shared" si="31"/>
-        <v>-36362.485849871642</v>
+        <v>-274</v>
       </c>
       <c r="AM11" s="7">
         <f t="shared" si="32"/>
-        <v>-138952.67010878486</v>
+        <v>-7002</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="46">
-        <f>SUM('BATS 2023'!P6,'BATS 2023'!P10,'BATS 2023'!P14,'BATS 2023'!P18)</f>
-        <v>196730.99386732138</v>
+        <f>SUM('BATS 2023'!Q6,'BATS 2023'!Q10,'BATS 2023'!Q14,'BATS 2023'!Q18)</f>
+        <v>2110</v>
       </c>
       <c r="D12" s="47">
-        <f>SUM('BATS 2023'!Q6,'BATS 2023'!Q10,'BATS 2023'!Q14,'BATS 2023'!Q18)</f>
-        <v>337.08702834652337</v>
+        <f>SUM('BATS 2023'!R6,'BATS 2023'!R10,'BATS 2023'!R14,'BATS 2023'!R18)</f>
+        <v>34</v>
       </c>
       <c r="E12" s="47">
-        <f>SUM('BATS 2023'!R6,'BATS 2023'!R10,'BATS 2023'!R14,'BATS 2023'!R18)</f>
-        <v>3476.7847045273052</v>
+        <f>SUM('BATS 2023'!S6,'BATS 2023'!S10,'BATS 2023'!S14,'BATS 2023'!S18)</f>
+        <v>120</v>
       </c>
       <c r="F12" s="47">
-        <f>SUM('BATS 2023'!S6,'BATS 2023'!S10,'BATS 2023'!S14,'BATS 2023'!S18)</f>
-        <v>11974.019741018919</v>
+        <f>SUM('BATS 2023'!T6,'BATS 2023'!T10,'BATS 2023'!T14,'BATS 2023'!T18)</f>
+        <v>130</v>
       </c>
       <c r="G12" s="47">
-        <f>SUM('BATS 2023'!T6,'BATS 2023'!T10,'BATS 2023'!T14,'BATS 2023'!T18)</f>
-        <v>86503.535083547016</v>
+        <f>SUM('BATS 2023'!U6,'BATS 2023'!U10,'BATS 2023'!U14,'BATS 2023'!U18)</f>
+        <v>1260</v>
       </c>
       <c r="H12" s="47">
-        <f>SUM('BATS 2023'!U6,'BATS 2023'!U10,'BATS 2023'!U14,'BATS 2023'!U18)</f>
-        <v>38769.43465931739</v>
+        <f>SUM('BATS 2023'!V6,'BATS 2023'!V10,'BATS 2023'!V14,'BATS 2023'!V18)</f>
+        <v>594</v>
       </c>
       <c r="I12" s="47">
-        <f>SUM('BATS 2023'!V6,'BATS 2023'!V10,'BATS 2023'!V14,'BATS 2023'!V18)</f>
-        <v>41068.352115558439</v>
+        <f>SUM('BATS 2023'!W6,'BATS 2023'!W10,'BATS 2023'!W14,'BATS 2023'!W18)</f>
+        <v>800</v>
       </c>
       <c r="J12" s="47">
-        <f>SUM('BATS 2023'!W6,'BATS 2023'!W10,'BATS 2023'!W14,'BATS 2023'!W18)</f>
-        <v>45039.729642964856</v>
+        <f>SUM('BATS 2023'!X6,'BATS 2023'!X10,'BATS 2023'!X14,'BATS 2023'!X18)</f>
+        <v>1022</v>
       </c>
       <c r="K12" s="47">
-        <f>SUM('BATS 2023'!X6,'BATS 2023'!X10,'BATS 2023'!X14,'BATS 2023'!X18)</f>
-        <v>8130.5122028836149</v>
+        <f>SUM('BATS 2023'!Y6,'BATS 2023'!Y10,'BATS 2023'!Y14,'BATS 2023'!Y18)</f>
+        <v>144</v>
       </c>
       <c r="L12" s="47">
-        <f>SUM('BATS 2023'!Y6,'BATS 2023'!Y10,'BATS 2023'!Y14,'BATS 2023'!Y18)</f>
-        <v>5459.6937246499656</v>
+        <f>SUM('BATS 2023'!Z6,'BATS 2023'!Z10,'BATS 2023'!Z14,'BATS 2023'!Z18)</f>
+        <v>46</v>
       </c>
       <c r="M12" s="48">
-        <f>SUM('BATS 2023'!Z6,'BATS 2023'!Z10,'BATS 2023'!Z14,'BATS 2023'!Z18)</f>
-        <v>50928.770542269362</v>
+        <f>SUM('BATS 2023'!AA6,'BATS 2023'!AA10,'BATS 2023'!AA14,'BATS 2023'!AA18)</f>
+        <v>1854</v>
       </c>
       <c r="O12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P12" s="46">
         <f>modeldata!C6+modeldata!C10+modeldata!C14+modeldata!C18</f>
@@ -2219,103 +2276,103 @@
         <v>0</v>
       </c>
       <c r="AB12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC12" s="6">
         <f t="shared" ref="AC12:AC14" si="33">P12-C12</f>
-        <v>-196730.99386732138</v>
+        <v>-2110</v>
       </c>
       <c r="AD12">
         <f t="shared" si="23"/>
-        <v>-337.08702834652337</v>
+        <v>-34</v>
       </c>
       <c r="AE12">
         <f t="shared" si="24"/>
-        <v>-3476.7847045273052</v>
+        <v>-120</v>
       </c>
       <c r="AF12">
         <f t="shared" si="25"/>
-        <v>-11974.019741018919</v>
+        <v>-130</v>
       </c>
       <c r="AG12">
         <f t="shared" si="26"/>
-        <v>-86503.535083547016</v>
+        <v>-1260</v>
       </c>
       <c r="AH12">
         <f t="shared" si="27"/>
-        <v>-38769.43465931739</v>
+        <v>-594</v>
       </c>
       <c r="AI12">
         <f t="shared" si="28"/>
-        <v>-41068.352115558439</v>
+        <v>-800</v>
       </c>
       <c r="AJ12">
         <f t="shared" si="29"/>
-        <v>-45039.729642964856</v>
+        <v>-1022</v>
       </c>
       <c r="AK12">
         <f t="shared" si="30"/>
-        <v>-8130.5122028836149</v>
+        <v>-144</v>
       </c>
       <c r="AL12">
         <f t="shared" si="31"/>
-        <v>-5459.6937246499656</v>
+        <v>-46</v>
       </c>
       <c r="AM12" s="7">
         <f t="shared" si="32"/>
-        <v>-50928.770542269362</v>
+        <v>-1854</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="49">
-        <f>SUM('BATS 2023'!P7,'BATS 2023'!P11,'BATS 2023'!P15,'BATS 2023'!P19)</f>
-        <v>95883.527498539101</v>
+        <f>SUM('BATS 2023'!Q7,'BATS 2023'!Q11,'BATS 2023'!Q15,'BATS 2023'!Q19)</f>
+        <v>1358</v>
       </c>
       <c r="D13" s="50">
-        <f>SUM('BATS 2023'!Q7,'BATS 2023'!Q11,'BATS 2023'!Q15,'BATS 2023'!Q19)</f>
-        <v>1164.0322141071342</v>
+        <f>SUM('BATS 2023'!R7,'BATS 2023'!R11,'BATS 2023'!R15,'BATS 2023'!R19)</f>
+        <v>8</v>
       </c>
       <c r="E13" s="50">
-        <f>SUM('BATS 2023'!R7,'BATS 2023'!R11,'BATS 2023'!R15,'BATS 2023'!R19)</f>
-        <v>5957.7134606357959</v>
+        <f>SUM('BATS 2023'!S7,'BATS 2023'!S11,'BATS 2023'!S15,'BATS 2023'!S19)</f>
+        <v>56</v>
       </c>
       <c r="F13" s="50">
-        <f>SUM('BATS 2023'!S7,'BATS 2023'!S11,'BATS 2023'!S15,'BATS 2023'!S19)</f>
-        <v>4554.9133773245167</v>
+        <f>SUM('BATS 2023'!T7,'BATS 2023'!T11,'BATS 2023'!T15,'BATS 2023'!T19)</f>
+        <v>70</v>
       </c>
       <c r="G13" s="50">
-        <f>SUM('BATS 2023'!T7,'BATS 2023'!T11,'BATS 2023'!T15,'BATS 2023'!T19)</f>
-        <v>30430.168526898116</v>
+        <f>SUM('BATS 2023'!U7,'BATS 2023'!U11,'BATS 2023'!U15,'BATS 2023'!U19)</f>
+        <v>704</v>
       </c>
       <c r="H13" s="50">
-        <f>SUM('BATS 2023'!U7,'BATS 2023'!U11,'BATS 2023'!U15,'BATS 2023'!U19)</f>
-        <v>22713.12770505773</v>
+        <f>SUM('BATS 2023'!V7,'BATS 2023'!V11,'BATS 2023'!V15,'BATS 2023'!V19)</f>
+        <v>464</v>
       </c>
       <c r="I13" s="50">
-        <f>SUM('BATS 2023'!V7,'BATS 2023'!V11,'BATS 2023'!V15,'BATS 2023'!V19)</f>
-        <v>37957.150176251926</v>
+        <f>SUM('BATS 2023'!W7,'BATS 2023'!W11,'BATS 2023'!W15,'BATS 2023'!W19)</f>
+        <v>622</v>
       </c>
       <c r="J13" s="50">
-        <f>SUM('BATS 2023'!W7,'BATS 2023'!W11,'BATS 2023'!W15,'BATS 2023'!W19)</f>
-        <v>21775.409334903165</v>
+        <f>SUM('BATS 2023'!X7,'BATS 2023'!X11,'BATS 2023'!X15,'BATS 2023'!X19)</f>
+        <v>518</v>
       </c>
       <c r="K13" s="50">
-        <f>SUM('BATS 2023'!X7,'BATS 2023'!X11,'BATS 2023'!X15,'BATS 2023'!X19)</f>
-        <v>11021.812285618093</v>
+        <f>SUM('BATS 2023'!Y7,'BATS 2023'!Y11,'BATS 2023'!Y15,'BATS 2023'!Y19)</f>
+        <v>102</v>
       </c>
       <c r="L13" s="50">
-        <f>SUM('BATS 2023'!Y7,'BATS 2023'!Y11,'BATS 2023'!Y15,'BATS 2023'!Y19)</f>
-        <v>3458.4156300703139</v>
+        <f>SUM('BATS 2023'!Z7,'BATS 2023'!Z11,'BATS 2023'!Z15,'BATS 2023'!Z19)</f>
+        <v>24</v>
       </c>
       <c r="M13" s="51">
-        <f>SUM('BATS 2023'!Z7,'BATS 2023'!Z11,'BATS 2023'!Z15,'BATS 2023'!Z19)</f>
-        <v>22577.452476380953</v>
+        <f>SUM('BATS 2023'!AA7,'BATS 2023'!AA11,'BATS 2023'!AA15,'BATS 2023'!AA19)</f>
+        <v>702</v>
       </c>
       <c r="O13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P13" s="49">
         <f>modeldata!C7+modeldata!C11+modeldata!C15+modeldata!C19</f>
@@ -2362,103 +2419,103 @@
         <v>0</v>
       </c>
       <c r="AB13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AC13" s="8">
         <f t="shared" si="33"/>
-        <v>-95883.527498539101</v>
+        <v>-1358</v>
       </c>
       <c r="AD13" s="9">
         <f t="shared" si="23"/>
-        <v>-1164.0322141071342</v>
+        <v>-8</v>
       </c>
       <c r="AE13" s="9">
         <f t="shared" si="24"/>
-        <v>-5957.7134606357959</v>
+        <v>-56</v>
       </c>
       <c r="AF13" s="9">
         <f t="shared" si="25"/>
-        <v>-4554.9133773245167</v>
+        <v>-70</v>
       </c>
       <c r="AG13" s="9">
         <f t="shared" si="26"/>
-        <v>-30430.168526898116</v>
+        <v>-704</v>
       </c>
       <c r="AH13" s="9">
         <f t="shared" si="27"/>
-        <v>-22713.12770505773</v>
+        <v>-464</v>
       </c>
       <c r="AI13" s="9">
         <f t="shared" si="28"/>
-        <v>-37957.150176251926</v>
+        <v>-622</v>
       </c>
       <c r="AJ13" s="9">
         <f t="shared" si="29"/>
-        <v>-21775.409334903165</v>
+        <v>-518</v>
       </c>
       <c r="AK13" s="9">
         <f t="shared" si="30"/>
-        <v>-11021.812285618093</v>
+        <v>-102</v>
       </c>
       <c r="AL13" s="9">
         <f t="shared" si="31"/>
-        <v>-3458.4156300703139</v>
+        <v>-24</v>
       </c>
       <c r="AM13" s="10">
         <f t="shared" si="32"/>
-        <v>-22577.452476380953</v>
+        <v>-702</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="52">
         <f>SUM(C10:C13)</f>
-        <v>2091741.3240733952</v>
+        <v>27204</v>
       </c>
       <c r="D14" s="52">
         <f t="shared" ref="D14:M14" si="34">SUM(D10:D13)</f>
-        <v>57236.523943209475</v>
+        <v>582</v>
       </c>
       <c r="E14" s="52">
         <f t="shared" si="34"/>
-        <v>302393.81492279621</v>
+        <v>2650</v>
       </c>
       <c r="F14" s="52">
         <f t="shared" si="34"/>
-        <v>1374521.4793724692</v>
+        <v>12970</v>
       </c>
       <c r="G14" s="52">
         <f t="shared" si="34"/>
-        <v>1099210.613910995</v>
+        <v>21380</v>
       </c>
       <c r="H14" s="52">
         <f t="shared" si="34"/>
-        <v>588109.15796728001</v>
+        <v>11018</v>
       </c>
       <c r="I14" s="52">
         <f t="shared" si="34"/>
-        <v>730229.71132333204</v>
+        <v>15344</v>
       </c>
       <c r="J14" s="52">
         <f t="shared" si="34"/>
-        <v>1629606.0093024541</v>
+        <v>34292</v>
       </c>
       <c r="K14" s="52">
         <f t="shared" si="34"/>
-        <v>280450.3335598936</v>
+        <v>4334</v>
       </c>
       <c r="L14" s="52">
         <f t="shared" si="34"/>
-        <v>348792.04961444315</v>
+        <v>4048</v>
       </c>
       <c r="M14" s="52">
         <f t="shared" si="34"/>
-        <v>986247.94808682648</v>
+        <v>46906</v>
       </c>
       <c r="O14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P14" s="52">
         <f>SUM(P10:P13)</f>
@@ -2505,51 +2562,51 @@
         <v>0</v>
       </c>
       <c r="AB14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC14">
         <f t="shared" si="33"/>
-        <v>-2091741.3240733952</v>
+        <v>-27204</v>
       </c>
       <c r="AD14">
         <f t="shared" si="23"/>
-        <v>-57236.523943209475</v>
+        <v>-582</v>
       </c>
       <c r="AE14">
         <f t="shared" si="24"/>
-        <v>-302393.81492279621</v>
+        <v>-2650</v>
       </c>
       <c r="AF14">
         <f t="shared" si="25"/>
-        <v>-1374521.4793724692</v>
+        <v>-12970</v>
       </c>
       <c r="AG14">
         <f t="shared" si="26"/>
-        <v>-1099210.613910995</v>
+        <v>-21380</v>
       </c>
       <c r="AH14">
         <f t="shared" si="27"/>
-        <v>-588109.15796728001</v>
+        <v>-11018</v>
       </c>
       <c r="AI14">
         <f t="shared" si="28"/>
-        <v>-730229.71132333204</v>
+        <v>-15344</v>
       </c>
       <c r="AJ14">
         <f t="shared" si="29"/>
-        <v>-1629606.0093024541</v>
+        <v>-34292</v>
       </c>
       <c r="AK14">
         <f t="shared" si="30"/>
-        <v>-280450.3335598936</v>
+        <v>-4334</v>
       </c>
       <c r="AL14">
         <f t="shared" si="31"/>
-        <v>-348792.04961444315</v>
+        <v>-4048</v>
       </c>
       <c r="AM14">
         <f t="shared" si="32"/>
-        <v>-986247.94808682648</v>
+        <v>-46906</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2578,54 +2635,54 @@
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="43">
-        <f>'BATS 2023'!P4</f>
-        <v>1073836.7390483427</v>
+        <f>'BATS 2023'!Q4</f>
+        <v>13536</v>
       </c>
       <c r="D16" s="44">
-        <f>'BATS 2023'!Q4</f>
-        <v>27215.565172606839</v>
+        <f>'BATS 2023'!R4</f>
+        <v>328</v>
       </c>
       <c r="E16" s="44">
-        <f>'BATS 2023'!R4</f>
-        <v>220460.70513257475</v>
+        <f>'BATS 2023'!S4</f>
+        <v>1936</v>
       </c>
       <c r="F16" s="44">
-        <f>'BATS 2023'!S4</f>
-        <v>1153447.6274418959</v>
+        <f>'BATS 2023'!T4</f>
+        <v>10630</v>
       </c>
       <c r="G16" s="44">
-        <f>'BATS 2023'!T4</f>
-        <v>481077.72790936055</v>
+        <f>'BATS 2023'!U4</f>
+        <v>9868</v>
       </c>
       <c r="H16" s="44">
-        <f>'BATS 2023'!U4</f>
-        <v>307865.80422767292</v>
+        <f>'BATS 2023'!V4</f>
+        <v>6004</v>
       </c>
       <c r="I16" s="44">
-        <f>'BATS 2023'!V4</f>
-        <v>417960.03210757487</v>
+        <f>'BATS 2023'!W4</f>
+        <v>7624</v>
       </c>
       <c r="J16" s="44">
-        <f>'BATS 2023'!W4</f>
-        <v>1238342.289831331</v>
+        <f>'BATS 2023'!X4</f>
+        <v>24698</v>
       </c>
       <c r="K16" s="44">
-        <f>'BATS 2023'!X4</f>
-        <v>167717.11888182827</v>
+        <f>'BATS 2023'!Y4</f>
+        <v>2954</v>
       </c>
       <c r="L16" s="44">
-        <f>'BATS 2023'!Y4</f>
-        <v>284812.38567461743</v>
+        <f>'BATS 2023'!Z4</f>
+        <v>3334</v>
       </c>
       <c r="M16" s="45">
-        <f>'BATS 2023'!Z4</f>
-        <v>675881.93703013682</v>
+        <f>'BATS 2023'!AA4</f>
+        <v>29986</v>
       </c>
       <c r="O16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P16" s="43">
         <f>modeldata!C4</f>
@@ -2672,103 +2729,103 @@
         <v>0</v>
       </c>
       <c r="AB16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC16" s="3">
         <f>P16-C16</f>
-        <v>-1073836.7390483427</v>
+        <v>-13536</v>
       </c>
       <c r="AD16" s="4">
         <f t="shared" ref="AD16:AD20" si="45">Q16-D16</f>
-        <v>-27215.565172606839</v>
+        <v>-328</v>
       </c>
       <c r="AE16" s="4">
         <f t="shared" ref="AE16:AE20" si="46">R16-E16</f>
-        <v>-220460.70513257475</v>
+        <v>-1936</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" ref="AF16:AF20" si="47">S16-F16</f>
-        <v>-1153447.6274418959</v>
+        <v>-10630</v>
       </c>
       <c r="AG16" s="4">
         <f t="shared" ref="AG16:AG20" si="48">T16-G16</f>
-        <v>-481077.72790936055</v>
+        <v>-9868</v>
       </c>
       <c r="AH16" s="4">
         <f t="shared" ref="AH16:AH20" si="49">U16-H16</f>
-        <v>-307865.80422767292</v>
+        <v>-6004</v>
       </c>
       <c r="AI16" s="4">
         <f t="shared" ref="AI16:AI20" si="50">V16-I16</f>
-        <v>-417960.03210757487</v>
+        <v>-7624</v>
       </c>
       <c r="AJ16" s="4">
         <f t="shared" ref="AJ16:AJ20" si="51">W16-J16</f>
-        <v>-1238342.289831331</v>
+        <v>-24698</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" ref="AK16:AK20" si="52">X16-K16</f>
-        <v>-167717.11888182827</v>
+        <v>-2954</v>
       </c>
       <c r="AL16" s="4">
         <f t="shared" ref="AL16:AL20" si="53">Y16-L16</f>
-        <v>-284812.38567461743</v>
+        <v>-3334</v>
       </c>
       <c r="AM16" s="5">
         <f t="shared" ref="AM16:AM20" si="54">Z16-M16</f>
-        <v>-675881.93703013682</v>
+        <v>-29986</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="46">
-        <f>'BATS 2023'!P5+'BATS 2023'!P8</f>
-        <v>483408.33032300865</v>
+        <f>'BATS 2023'!Q5+'BATS 2023'!Q8</f>
+        <v>6512</v>
       </c>
       <c r="D17" s="47">
-        <f>'BATS 2023'!Q5+'BATS 2023'!Q8</f>
-        <v>18449.654979825711</v>
+        <f>'BATS 2023'!R5+'BATS 2023'!R8</f>
+        <v>166</v>
       </c>
       <c r="E17" s="47">
-        <f>'BATS 2023'!R5+'BATS 2023'!R8</f>
-        <v>66147.542492996407</v>
+        <f>'BATS 2023'!S5+'BATS 2023'!S8</f>
+        <v>442</v>
       </c>
       <c r="F17" s="47">
-        <f>'BATS 2023'!S5+'BATS 2023'!S8</f>
-        <v>179308.49187775506</v>
+        <f>'BATS 2023'!T5+'BATS 2023'!T8</f>
+        <v>1704</v>
       </c>
       <c r="G17" s="47">
-        <f>'BATS 2023'!T5+'BATS 2023'!T8</f>
-        <v>266214.85775244806</v>
+        <f>'BATS 2023'!U5+'BATS 2023'!U8</f>
+        <v>5386</v>
       </c>
       <c r="H17" s="47">
-        <f>'BATS 2023'!U5+'BATS 2023'!U8</f>
-        <v>160374.44940324183</v>
+        <f>'BATS 2023'!V5+'BATS 2023'!V8</f>
+        <v>2674</v>
       </c>
       <c r="I17" s="47">
-        <f>'BATS 2023'!V5+'BATS 2023'!V8</f>
-        <v>149409.41161625594</v>
+        <f>'BATS 2023'!W5+'BATS 2023'!W8</f>
+        <v>3444</v>
       </c>
       <c r="J17" s="47">
-        <f>'BATS 2023'!W5+'BATS 2023'!W8</f>
-        <v>186191.71529355465</v>
+        <f>'BATS 2023'!X5+'BATS 2023'!X8</f>
+        <v>4744</v>
       </c>
       <c r="K17" s="47">
-        <f>'BATS 2023'!X5+'BATS 2023'!X8</f>
-        <v>54026.310772533572</v>
+        <f>'BATS 2023'!Y5+'BATS 2023'!Y8</f>
+        <v>676</v>
       </c>
       <c r="L17" s="47">
-        <f>'BATS 2023'!Y5+'BATS 2023'!Y8</f>
-        <v>37814.008800528864</v>
+        <f>'BATS 2023'!Z5+'BATS 2023'!Z8</f>
+        <v>474</v>
       </c>
       <c r="M17" s="48">
-        <f>'BATS 2023'!Z5+'BATS 2023'!Z8</f>
-        <v>186753.41224701353</v>
+        <f>'BATS 2023'!AA5+'BATS 2023'!AA8</f>
+        <v>9286</v>
       </c>
       <c r="O17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P17" s="46">
         <f>modeldata!C5+modeldata!C8</f>
@@ -2815,103 +2872,103 @@
         <v>0</v>
       </c>
       <c r="AB17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC17" s="6">
         <f>P17-C17</f>
-        <v>-483408.33032300865</v>
+        <v>-6512</v>
       </c>
       <c r="AD17">
         <f t="shared" si="45"/>
-        <v>-18449.654979825711</v>
+        <v>-166</v>
       </c>
       <c r="AE17">
         <f t="shared" si="46"/>
-        <v>-66147.542492996407</v>
+        <v>-442</v>
       </c>
       <c r="AF17">
         <f t="shared" si="47"/>
-        <v>-179308.49187775506</v>
+        <v>-1704</v>
       </c>
       <c r="AG17">
         <f t="shared" si="48"/>
-        <v>-266214.85775244806</v>
+        <v>-5386</v>
       </c>
       <c r="AH17">
         <f t="shared" si="49"/>
-        <v>-160374.44940324183</v>
+        <v>-2674</v>
       </c>
       <c r="AI17">
         <f t="shared" si="50"/>
-        <v>-149409.41161625594</v>
+        <v>-3444</v>
       </c>
       <c r="AJ17">
         <f t="shared" si="51"/>
-        <v>-186191.71529355465</v>
+        <v>-4744</v>
       </c>
       <c r="AK17">
         <f t="shared" si="52"/>
-        <v>-54026.310772533572</v>
+        <v>-676</v>
       </c>
       <c r="AL17">
         <f t="shared" si="53"/>
-        <v>-37814.008800528864</v>
+        <v>-474</v>
       </c>
       <c r="AM17" s="7">
         <f t="shared" si="54"/>
-        <v>-186753.41224701353</v>
+        <v>-9286</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="46">
-        <f>SUM('BATS 2023'!P6,'BATS 2023'!P12,'BATS 2023'!P9)</f>
-        <v>276292.94569033547</v>
+        <f>SUM('BATS 2023'!Q6,'BATS 2023'!Q12,'BATS 2023'!Q9)</f>
+        <v>3440</v>
       </c>
       <c r="D18" s="47">
-        <f>SUM('BATS 2023'!Q6,'BATS 2023'!Q12,'BATS 2023'!Q9)</f>
-        <v>1812.0243967091401</v>
+        <f>SUM('BATS 2023'!R6,'BATS 2023'!R12,'BATS 2023'!R9)</f>
+        <v>40</v>
       </c>
       <c r="E18" s="47">
-        <f>SUM('BATS 2023'!R6,'BATS 2023'!R12,'BATS 2023'!R9)</f>
-        <v>8863.6639817632076</v>
+        <f>SUM('BATS 2023'!S6,'BATS 2023'!S12,'BATS 2023'!S9)</f>
+        <v>156</v>
       </c>
       <c r="F18" s="47">
-        <f>SUM('BATS 2023'!S6,'BATS 2023'!S12,'BATS 2023'!S9)</f>
-        <v>28596.592283942504</v>
+        <f>SUM('BATS 2023'!T6,'BATS 2023'!T12,'BATS 2023'!T9)</f>
+        <v>406</v>
       </c>
       <c r="G18" s="47">
-        <f>SUM('BATS 2023'!T6,'BATS 2023'!T12,'BATS 2023'!T9)</f>
-        <v>163237.33995532661</v>
+        <f>SUM('BATS 2023'!U6,'BATS 2023'!U12,'BATS 2023'!U9)</f>
+        <v>2858</v>
       </c>
       <c r="H18" s="47">
-        <f>SUM('BATS 2023'!U6,'BATS 2023'!U12,'BATS 2023'!U9)</f>
-        <v>71605.597144860367</v>
+        <f>SUM('BATS 2023'!V6,'BATS 2023'!V12,'BATS 2023'!V9)</f>
+        <v>1272</v>
       </c>
       <c r="I18" s="47">
-        <f>SUM('BATS 2023'!V6,'BATS 2023'!V12,'BATS 2023'!V9)</f>
-        <v>52841.762803074605</v>
+        <f>SUM('BATS 2023'!W6,'BATS 2023'!W12,'BATS 2023'!W9)</f>
+        <v>1844</v>
       </c>
       <c r="J18" s="47">
-        <f>SUM('BATS 2023'!W6,'BATS 2023'!W12,'BATS 2023'!W9)</f>
-        <v>115982.65009232027</v>
+        <f>SUM('BATS 2023'!X6,'BATS 2023'!X12,'BATS 2023'!X9)</f>
+        <v>2696</v>
       </c>
       <c r="K18" s="47">
-        <f>SUM('BATS 2023'!X6,'BATS 2023'!X12,'BATS 2023'!X9)</f>
-        <v>35200.776799639076</v>
+        <f>SUM('BATS 2023'!Y6,'BATS 2023'!Y12,'BATS 2023'!Y9)</f>
+        <v>350</v>
       </c>
       <c r="L18" s="47">
-        <f>SUM('BATS 2023'!Y6,'BATS 2023'!Y12,'BATS 2023'!Y9)</f>
-        <v>16814.9283974231</v>
+        <f>SUM('BATS 2023'!Z6,'BATS 2023'!Z12,'BATS 2023'!Z9)</f>
+        <v>132</v>
       </c>
       <c r="M18" s="48">
-        <f>SUM('BATS 2023'!Z6,'BATS 2023'!Z12,'BATS 2023'!Z9)</f>
-        <v>72312.696812277689</v>
+        <f>SUM('BATS 2023'!AA6,'BATS 2023'!AA12,'BATS 2023'!AA9)</f>
+        <v>4416</v>
       </c>
       <c r="O18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P18" s="46">
         <f>modeldata!C6+modeldata!C9+modeldata!C12</f>
@@ -2958,103 +3015,103 @@
         <v>0</v>
       </c>
       <c r="AB18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC18" s="6">
         <f t="shared" ref="AC18:AC20" si="55">P18-C18</f>
-        <v>-276292.94569033547</v>
+        <v>-3440</v>
       </c>
       <c r="AD18">
         <f t="shared" si="45"/>
-        <v>-1812.0243967091401</v>
+        <v>-40</v>
       </c>
       <c r="AE18">
         <f t="shared" si="46"/>
-        <v>-8863.6639817632076</v>
+        <v>-156</v>
       </c>
       <c r="AF18">
         <f t="shared" si="47"/>
-        <v>-28596.592283942504</v>
+        <v>-406</v>
       </c>
       <c r="AG18">
         <f t="shared" si="48"/>
-        <v>-163237.33995532661</v>
+        <v>-2858</v>
       </c>
       <c r="AH18">
         <f t="shared" si="49"/>
-        <v>-71605.597144860367</v>
+        <v>-1272</v>
       </c>
       <c r="AI18">
         <f t="shared" si="50"/>
-        <v>-52841.762803074605</v>
+        <v>-1844</v>
       </c>
       <c r="AJ18">
         <f t="shared" si="51"/>
-        <v>-115982.65009232027</v>
+        <v>-2696</v>
       </c>
       <c r="AK18">
         <f t="shared" si="52"/>
-        <v>-35200.776799639076</v>
+        <v>-350</v>
       </c>
       <c r="AL18">
         <f t="shared" si="53"/>
-        <v>-16814.9283974231</v>
+        <v>-132</v>
       </c>
       <c r="AM18" s="7">
         <f t="shared" si="54"/>
-        <v>-72312.696812277689</v>
+        <v>-4416</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="46">
-        <f>SUM('BATS 2023'!P7,'BATS 2023'!P10,'BATS 2023'!P13,'BATS 2023'!P16)</f>
-        <v>139525.83045769023</v>
+        <f>SUM('BATS 2023'!Q7,'BATS 2023'!Q10,'BATS 2023'!Q13,'BATS 2023'!Q16)</f>
+        <v>2368</v>
       </c>
       <c r="D19" s="47">
-        <f>SUM('BATS 2023'!Q7,'BATS 2023'!Q10,'BATS 2023'!Q13,'BATS 2023'!Q16)</f>
-        <v>9210.8511498422467</v>
+        <f>SUM('BATS 2023'!R7,'BATS 2023'!R10,'BATS 2023'!R13,'BATS 2023'!R16)</f>
+        <v>36</v>
       </c>
       <c r="E19" s="47">
-        <f>SUM('BATS 2023'!R7,'BATS 2023'!R10,'BATS 2023'!R13,'BATS 2023'!R16)</f>
-        <v>6749.2120643878961</v>
+        <f>SUM('BATS 2023'!S7,'BATS 2023'!S10,'BATS 2023'!S13,'BATS 2023'!S16)</f>
+        <v>86</v>
       </c>
       <c r="F19" s="47">
-        <f>SUM('BATS 2023'!S7,'BATS 2023'!S10,'BATS 2023'!S13,'BATS 2023'!S16)</f>
-        <v>12331.727627568071</v>
+        <f>SUM('BATS 2023'!T7,'BATS 2023'!T10,'BATS 2023'!T13,'BATS 2023'!T16)</f>
+        <v>172</v>
       </c>
       <c r="G19" s="47">
-        <f>SUM('BATS 2023'!T7,'BATS 2023'!T10,'BATS 2023'!T13,'BATS 2023'!T16)</f>
-        <v>148574.85196096188</v>
+        <f>SUM('BATS 2023'!U7,'BATS 2023'!U10,'BATS 2023'!U13,'BATS 2023'!U16)</f>
+        <v>2184</v>
       </c>
       <c r="H19" s="47">
-        <f>SUM('BATS 2023'!U7,'BATS 2023'!U10,'BATS 2023'!U13,'BATS 2023'!U16)</f>
-        <v>31511.186509642281</v>
+        <f>SUM('BATS 2023'!V7,'BATS 2023'!V10,'BATS 2023'!V13,'BATS 2023'!V16)</f>
+        <v>736</v>
       </c>
       <c r="I19" s="47">
-        <f>SUM('BATS 2023'!V7,'BATS 2023'!V10,'BATS 2023'!V13,'BATS 2023'!V16)</f>
-        <v>52344.067416085032</v>
+        <f>SUM('BATS 2023'!W7,'BATS 2023'!W10,'BATS 2023'!W13,'BATS 2023'!W16)</f>
+        <v>1564</v>
       </c>
       <c r="J19" s="47">
-        <f>SUM('BATS 2023'!W7,'BATS 2023'!W10,'BATS 2023'!W13,'BATS 2023'!W16)</f>
-        <v>71505.464000598178</v>
+        <f>SUM('BATS 2023'!X7,'BATS 2023'!X10,'BATS 2023'!X13,'BATS 2023'!X16)</f>
+        <v>1512</v>
       </c>
       <c r="K19" s="47">
-        <f>SUM('BATS 2023'!X7,'BATS 2023'!X10,'BATS 2023'!X13,'BATS 2023'!X16)</f>
-        <v>19705.733134861315</v>
+        <f>SUM('BATS 2023'!Y7,'BATS 2023'!Y10,'BATS 2023'!Y13,'BATS 2023'!Y16)</f>
+        <v>240</v>
       </c>
       <c r="L19" s="47">
-        <f>SUM('BATS 2023'!Y7,'BATS 2023'!Y10,'BATS 2023'!Y13,'BATS 2023'!Y16)</f>
-        <v>6682.7121687720728</v>
+        <f>SUM('BATS 2023'!Z7,'BATS 2023'!Z10,'BATS 2023'!Z13,'BATS 2023'!Z16)</f>
+        <v>66</v>
       </c>
       <c r="M19" s="48">
-        <f>SUM('BATS 2023'!Z7,'BATS 2023'!Z10,'BATS 2023'!Z13,'BATS 2023'!Z16)</f>
-        <v>47050.923678754792</v>
+        <f>SUM('BATS 2023'!AA7,'BATS 2023'!AA10,'BATS 2023'!AA13,'BATS 2023'!AA16)</f>
+        <v>2374</v>
       </c>
       <c r="O19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P19" s="46">
         <f>modeldata!C7+modeldata!C10+modeldata!C13+modeldata!C16</f>
@@ -3101,103 +3158,103 @@
         <v>0</v>
       </c>
       <c r="AB19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="55"/>
-        <v>-139525.83045769023</v>
+        <v>-2368</v>
       </c>
       <c r="AD19">
         <f t="shared" si="45"/>
-        <v>-9210.8511498422467</v>
+        <v>-36</v>
       </c>
       <c r="AE19">
         <f t="shared" si="46"/>
-        <v>-6749.2120643878961</v>
+        <v>-86</v>
       </c>
       <c r="AF19">
         <f t="shared" si="47"/>
-        <v>-12331.727627568071</v>
+        <v>-172</v>
       </c>
       <c r="AG19">
         <f t="shared" si="48"/>
-        <v>-148574.85196096188</v>
+        <v>-2184</v>
       </c>
       <c r="AH19">
         <f t="shared" si="49"/>
-        <v>-31511.186509642281</v>
+        <v>-736</v>
       </c>
       <c r="AI19">
         <f t="shared" si="50"/>
-        <v>-52344.067416085032</v>
+        <v>-1564</v>
       </c>
       <c r="AJ19">
         <f t="shared" si="51"/>
-        <v>-71505.464000598178</v>
+        <v>-1512</v>
       </c>
       <c r="AK19">
         <f t="shared" si="52"/>
-        <v>-19705.733134861315</v>
+        <v>-240</v>
       </c>
       <c r="AL19">
         <f t="shared" si="53"/>
-        <v>-6682.7121687720728</v>
+        <v>-66</v>
       </c>
       <c r="AM19" s="7">
         <f t="shared" si="54"/>
-        <v>-47050.923678754792</v>
+        <v>-2374</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="46">
-        <f>SUM('BATS 2023'!P11,'BATS 2023'!P14,'BATS 2023'!P17)</f>
-        <v>70055.358911589399</v>
+        <f>SUM('BATS 2023'!Q11,'BATS 2023'!Q14,'BATS 2023'!Q17)</f>
+        <v>846</v>
       </c>
       <c r="D20" s="47">
-        <f>SUM('BATS 2023'!Q11,'BATS 2023'!Q14,'BATS 2023'!Q17)</f>
-        <v>0</v>
+        <f>SUM('BATS 2023'!R11,'BATS 2023'!R14,'BATS 2023'!R17)</f>
+        <v>2</v>
       </c>
       <c r="E20" s="47">
-        <f>SUM('BATS 2023'!R11,'BATS 2023'!R14,'BATS 2023'!R17)</f>
-        <v>172.69125107398773</v>
+        <f>SUM('BATS 2023'!S11,'BATS 2023'!S14,'BATS 2023'!S17)</f>
+        <v>26</v>
       </c>
       <c r="F20" s="47">
-        <f>SUM('BATS 2023'!S11,'BATS 2023'!S14,'BATS 2023'!S17)</f>
-        <v>837.04014130744849</v>
+        <f>SUM('BATS 2023'!T11,'BATS 2023'!T14,'BATS 2023'!T17)</f>
+        <v>38</v>
       </c>
       <c r="G20" s="47">
-        <f>SUM('BATS 2023'!T11,'BATS 2023'!T14,'BATS 2023'!T17)</f>
-        <v>28487.113283528623</v>
+        <f>SUM('BATS 2023'!U11,'BATS 2023'!U14,'BATS 2023'!U17)</f>
+        <v>714</v>
       </c>
       <c r="H20" s="47">
-        <f>SUM('BATS 2023'!U11,'BATS 2023'!U14,'BATS 2023'!U17)</f>
-        <v>12749.634705260138</v>
+        <f>SUM('BATS 2023'!V11,'BATS 2023'!V14,'BATS 2023'!V17)</f>
+        <v>226</v>
       </c>
       <c r="I20" s="47">
-        <f>SUM('BATS 2023'!V11,'BATS 2023'!V14,'BATS 2023'!V17)</f>
-        <v>37387.129389165144</v>
+        <f>SUM('BATS 2023'!W11,'BATS 2023'!W14,'BATS 2023'!W17)</f>
+        <v>576</v>
       </c>
       <c r="J20" s="47">
-        <f>SUM('BATS 2023'!W11,'BATS 2023'!W14,'BATS 2023'!W17)</f>
-        <v>7850.3212668839296</v>
+        <f>SUM('BATS 2023'!X11,'BATS 2023'!X14,'BATS 2023'!X17)</f>
+        <v>430</v>
       </c>
       <c r="K20" s="47">
-        <f>SUM('BATS 2023'!X11,'BATS 2023'!X14,'BATS 2023'!X17)</f>
-        <v>2768.5011781905282</v>
+        <f>SUM('BATS 2023'!Y11,'BATS 2023'!Y14,'BATS 2023'!Y17)</f>
+        <v>58</v>
       </c>
       <c r="L20" s="47">
-        <f>SUM('BATS 2023'!Y11,'BATS 2023'!Y14,'BATS 2023'!Y17)</f>
-        <v>1770.3739791504088</v>
+        <f>SUM('BATS 2023'!Z11,'BATS 2023'!Z14,'BATS 2023'!Z17)</f>
+        <v>22</v>
       </c>
       <c r="M20" s="48">
-        <f>SUM('BATS 2023'!Z11,'BATS 2023'!Z14,'BATS 2023'!Z17)</f>
-        <v>1806.2941002392156</v>
+        <f>SUM('BATS 2023'!AA11,'BATS 2023'!AA14,'BATS 2023'!AA17)</f>
+        <v>702</v>
       </c>
       <c r="O20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P20" s="46">
         <f>modeldata!C11+modeldata!C14+modeldata!C17</f>
@@ -3244,103 +3301,103 @@
         <v>0</v>
       </c>
       <c r="AB20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="55"/>
-        <v>-70055.358911589399</v>
+        <v>-846</v>
       </c>
       <c r="AD20">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE20">
         <f t="shared" si="46"/>
-        <v>-172.69125107398773</v>
+        <v>-26</v>
       </c>
       <c r="AF20">
         <f t="shared" si="47"/>
-        <v>-837.04014130744849</v>
+        <v>-38</v>
       </c>
       <c r="AG20">
         <f t="shared" si="48"/>
-        <v>-28487.113283528623</v>
+        <v>-714</v>
       </c>
       <c r="AH20">
         <f t="shared" si="49"/>
-        <v>-12749.634705260138</v>
+        <v>-226</v>
       </c>
       <c r="AI20">
         <f t="shared" si="50"/>
-        <v>-37387.129389165144</v>
+        <v>-576</v>
       </c>
       <c r="AJ20">
         <f t="shared" si="51"/>
-        <v>-7850.3212668839296</v>
+        <v>-430</v>
       </c>
       <c r="AK20">
         <f t="shared" si="52"/>
-        <v>-2768.5011781905282</v>
+        <v>-58</v>
       </c>
       <c r="AL20">
         <f t="shared" si="53"/>
-        <v>-1770.3739791504088</v>
+        <v>-22</v>
       </c>
       <c r="AM20" s="7">
         <f t="shared" si="54"/>
-        <v>-1806.2941002392156</v>
+        <v>-702</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="46">
-        <f>SUM('BATS 2023'!P15,'BATS 2023'!P18)</f>
-        <v>39131.86841315018</v>
+        <f>SUM('BATS 2023'!Q15,'BATS 2023'!Q18)</f>
+        <v>348</v>
       </c>
       <c r="D21" s="47">
-        <f>SUM('BATS 2023'!Q15,'BATS 2023'!Q18)</f>
-        <v>36.113408123269096</v>
+        <f>SUM('BATS 2023'!R15,'BATS 2023'!R18)</f>
+        <v>6</v>
       </c>
       <c r="E21" s="47">
-        <f>SUM('BATS 2023'!R15,'BATS 2023'!R18)</f>
-        <v>0</v>
+        <f>SUM('BATS 2023'!S15,'BATS 2023'!S18)</f>
+        <v>2</v>
       </c>
       <c r="F21" s="47">
-        <f>SUM('BATS 2023'!S15,'BATS 2023'!S18)</f>
-        <v>0</v>
+        <f>SUM('BATS 2023'!T15,'BATS 2023'!T18)</f>
+        <v>14</v>
       </c>
       <c r="G21" s="47">
-        <f>SUM('BATS 2023'!T15,'BATS 2023'!T18)</f>
-        <v>8060.9042268412395</v>
+        <f>SUM('BATS 2023'!U15,'BATS 2023'!U18)</f>
+        <v>270</v>
       </c>
       <c r="H21" s="47">
-        <f>SUM('BATS 2023'!U15,'BATS 2023'!U18)</f>
-        <v>3014.0281916655372</v>
+        <f>SUM('BATS 2023'!V15,'BATS 2023'!V18)</f>
+        <v>64</v>
       </c>
       <c r="I21" s="47">
-        <f>SUM('BATS 2023'!V15,'BATS 2023'!V18)</f>
-        <v>16223.640687958883</v>
+        <f>SUM('BATS 2023'!W15,'BATS 2023'!W18)</f>
+        <v>194</v>
       </c>
       <c r="J21" s="47">
-        <f>SUM('BATS 2023'!W15,'BATS 2023'!W18)</f>
-        <v>7015.6707344284314</v>
+        <f>SUM('BATS 2023'!X15,'BATS 2023'!X18)</f>
+        <v>156</v>
       </c>
       <c r="K21" s="47">
-        <f>SUM('BATS 2023'!X15,'BATS 2023'!X18)</f>
-        <v>397.90772175569771</v>
+        <f>SUM('BATS 2023'!Y15,'BATS 2023'!Y18)</f>
+        <v>38</v>
       </c>
       <c r="L21" s="47">
-        <f>SUM('BATS 2023'!Y15,'BATS 2023'!Y18)</f>
-        <v>828.3346820397868</v>
+        <f>SUM('BATS 2023'!Z15,'BATS 2023'!Z18)</f>
+        <v>12</v>
       </c>
       <c r="M21" s="48">
-        <f>SUM('BATS 2023'!Z15,'BATS 2023'!Z18)</f>
-        <v>2442.6842184043094</v>
+        <f>SUM('BATS 2023'!AA15,'BATS 2023'!AA18)</f>
+        <v>92</v>
       </c>
       <c r="O21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P21" s="46">
         <f>modeldata!C15+modeldata!C18</f>
@@ -3387,103 +3444,103 @@
         <v>0</v>
       </c>
       <c r="AB21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC21" s="6">
         <f>P21-C21</f>
-        <v>-39131.86841315018</v>
+        <v>-348</v>
       </c>
       <c r="AD21">
         <f t="shared" ref="AD21:AD23" si="56">Q21-D21</f>
-        <v>-36.113408123269096</v>
+        <v>-6</v>
       </c>
       <c r="AE21">
         <f t="shared" ref="AE21:AE23" si="57">R21-E21</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF21">
         <f t="shared" ref="AF21:AF23" si="58">S21-F21</f>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AG21">
         <f t="shared" ref="AG21:AG23" si="59">T21-G21</f>
-        <v>-8060.9042268412395</v>
+        <v>-270</v>
       </c>
       <c r="AH21">
         <f t="shared" ref="AH21:AH23" si="60">U21-H21</f>
-        <v>-3014.0281916655372</v>
+        <v>-64</v>
       </c>
       <c r="AI21">
         <f t="shared" ref="AI21:AI23" si="61">V21-I21</f>
-        <v>-16223.640687958883</v>
+        <v>-194</v>
       </c>
       <c r="AJ21">
         <f t="shared" ref="AJ21:AJ23" si="62">W21-J21</f>
-        <v>-7015.6707344284314</v>
+        <v>-156</v>
       </c>
       <c r="AK21">
         <f t="shared" ref="AK21:AK23" si="63">X21-K21</f>
-        <v>-397.90772175569771</v>
+        <v>-38</v>
       </c>
       <c r="AL21">
         <f t="shared" ref="AL21:AL23" si="64">Y21-L21</f>
-        <v>-828.3346820397868</v>
+        <v>-12</v>
       </c>
       <c r="AM21" s="7">
         <f t="shared" ref="AM21:AM23" si="65">Z21-M21</f>
-        <v>-2442.6842184043094</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="49">
-        <f>'BATS 2023'!P19</f>
-        <v>9490.2512292787542</v>
+        <f>'BATS 2023'!Q19</f>
+        <v>154</v>
       </c>
       <c r="D22" s="50">
-        <f>'BATS 2023'!Q19</f>
-        <v>512.31483610226019</v>
+        <f>'BATS 2023'!R19</f>
+        <v>4</v>
       </c>
       <c r="E22" s="50">
-        <f>'BATS 2023'!R19</f>
-        <v>0</v>
+        <f>'BATS 2023'!S19</f>
+        <v>2</v>
       </c>
       <c r="F22" s="50">
-        <f>'BATS 2023'!S19</f>
-        <v>0</v>
+        <f>'BATS 2023'!T19</f>
+        <v>6</v>
       </c>
       <c r="G22" s="50">
-        <f>'BATS 2023'!T19</f>
-        <v>3557.818822527991</v>
+        <f>'BATS 2023'!U19</f>
+        <v>100</v>
       </c>
       <c r="H22" s="50">
-        <f>'BATS 2023'!U19</f>
-        <v>988.45778493702903</v>
+        <f>'BATS 2023'!V19</f>
+        <v>42</v>
       </c>
       <c r="I22" s="50">
-        <f>'BATS 2023'!V19</f>
-        <v>4063.667303217534</v>
+        <f>'BATS 2023'!W19</f>
+        <v>98</v>
       </c>
       <c r="J22" s="50">
-        <f>'BATS 2023'!W19</f>
-        <v>2717.8980833374176</v>
+        <f>'BATS 2023'!X19</f>
+        <v>56</v>
       </c>
       <c r="K22" s="50">
-        <f>'BATS 2023'!X19</f>
-        <v>633.98507108513695</v>
+        <f>'BATS 2023'!Y19</f>
+        <v>18</v>
       </c>
       <c r="L22" s="50">
-        <f>'BATS 2023'!Y19</f>
-        <v>69.305911911520766</v>
+        <f>'BATS 2023'!Z19</f>
+        <v>8</v>
       </c>
       <c r="M22" s="51">
-        <f>'BATS 2023'!Z19</f>
-        <v>0</v>
+        <f>'BATS 2023'!AA19</f>
+        <v>50</v>
       </c>
       <c r="O22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P22" s="49">
         <f>modeldata!C19</f>
@@ -3530,103 +3587,103 @@
         <v>0</v>
       </c>
       <c r="AB22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC22" s="8">
         <f>P22-C22</f>
-        <v>-9490.2512292787542</v>
+        <v>-154</v>
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="56"/>
-        <v>-512.31483610226019</v>
+        <v>-4</v>
       </c>
       <c r="AE22" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF22" s="9">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AG22" s="9">
         <f t="shared" si="59"/>
-        <v>-3557.818822527991</v>
+        <v>-100</v>
       </c>
       <c r="AH22" s="9">
         <f t="shared" si="60"/>
-        <v>-988.45778493702903</v>
+        <v>-42</v>
       </c>
       <c r="AI22" s="9">
         <f t="shared" si="61"/>
-        <v>-4063.667303217534</v>
+        <v>-98</v>
       </c>
       <c r="AJ22" s="9">
         <f t="shared" si="62"/>
-        <v>-2717.8980833374176</v>
+        <v>-56</v>
       </c>
       <c r="AK22" s="9">
         <f t="shared" si="63"/>
-        <v>-633.98507108513695</v>
+        <v>-18</v>
       </c>
       <c r="AL22" s="9">
         <f t="shared" si="64"/>
-        <v>-69.305911911520766</v>
+        <v>-8</v>
       </c>
       <c r="AM22" s="10">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="52">
         <f>SUM(C16:C22)</f>
-        <v>2091741.3240733952</v>
+        <v>27204</v>
       </c>
       <c r="D23" s="52">
         <f t="shared" ref="D23:M23" si="66">SUM(D16:D22)</f>
-        <v>57236.52394320946</v>
+        <v>582</v>
       </c>
       <c r="E23" s="52">
         <f t="shared" si="66"/>
-        <v>302393.81492279621</v>
+        <v>2650</v>
       </c>
       <c r="F23" s="52">
         <f t="shared" si="66"/>
-        <v>1374521.4793724692</v>
+        <v>12970</v>
       </c>
       <c r="G23" s="52">
         <f t="shared" si="66"/>
-        <v>1099210.613910995</v>
+        <v>21380</v>
       </c>
       <c r="H23" s="52">
         <f t="shared" si="66"/>
-        <v>588109.15796728001</v>
+        <v>11018</v>
       </c>
       <c r="I23" s="52">
         <f t="shared" si="66"/>
-        <v>730229.71132333216</v>
+        <v>15344</v>
       </c>
       <c r="J23" s="52">
         <f t="shared" si="66"/>
-        <v>1629606.0093024538</v>
+        <v>34292</v>
       </c>
       <c r="K23" s="52">
         <f t="shared" si="66"/>
-        <v>280450.3335598936</v>
+        <v>4334</v>
       </c>
       <c r="L23" s="52">
         <f t="shared" si="66"/>
-        <v>348792.04961444327</v>
+        <v>4048</v>
       </c>
       <c r="M23" s="52">
         <f t="shared" si="66"/>
-        <v>986247.94808682636</v>
+        <v>46906</v>
       </c>
       <c r="O23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P23" s="52">
         <f>SUM(P16:P22)</f>
@@ -3673,57 +3730,57 @@
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC23">
         <f t="shared" ref="AC23" si="77">P23-C23</f>
-        <v>-2091741.3240733952</v>
+        <v>-27204</v>
       </c>
       <c r="AD23">
         <f t="shared" si="56"/>
-        <v>-57236.52394320946</v>
+        <v>-582</v>
       </c>
       <c r="AE23">
         <f t="shared" si="57"/>
-        <v>-302393.81492279621</v>
+        <v>-2650</v>
       </c>
       <c r="AF23">
         <f t="shared" si="58"/>
-        <v>-1374521.4793724692</v>
+        <v>-12970</v>
       </c>
       <c r="AG23">
         <f t="shared" si="59"/>
-        <v>-1099210.613910995</v>
+        <v>-21380</v>
       </c>
       <c r="AH23">
         <f t="shared" si="60"/>
-        <v>-588109.15796728001</v>
+        <v>-11018</v>
       </c>
       <c r="AI23">
         <f t="shared" si="61"/>
-        <v>-730229.71132333216</v>
+        <v>-15344</v>
       </c>
       <c r="AJ23">
         <f t="shared" si="62"/>
-        <v>-1629606.0093024538</v>
+        <v>-34292</v>
       </c>
       <c r="AK23">
         <f t="shared" si="63"/>
-        <v>-280450.3335598936</v>
+        <v>-4334</v>
       </c>
       <c r="AL23">
         <f t="shared" si="64"/>
-        <v>-348792.04961444327</v>
+        <v>-4048</v>
       </c>
       <c r="AM23">
         <f t="shared" si="65"/>
-        <v>-986247.94808682636</v>
+        <v>-46906</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -3738,7 +3795,7 @@
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P25" s="12"/>
       <c r="Q25" s="12"/>
@@ -3753,7 +3810,7 @@
       <c r="Z25" s="12"/>
       <c r="AA25" s="12"/>
       <c r="AB25" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC25" s="12"/>
       <c r="AD25" s="12"/>
@@ -3769,155 +3826,155 @@
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
         <v>1</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>2</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>3</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>4</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>5</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>6</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>7</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>8</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>9</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>10</v>
       </c>
-      <c r="M26" t="s">
-        <v>11</v>
-      </c>
       <c r="P26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="s">
         <v>1</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>2</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>3</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>4</v>
       </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
         <v>5</v>
       </c>
-      <c r="U26" t="s">
+      <c r="V26" t="s">
         <v>6</v>
       </c>
-      <c r="V26" t="s">
+      <c r="W26" t="s">
         <v>7</v>
       </c>
-      <c r="W26" t="s">
+      <c r="X26" t="s">
         <v>8</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>9</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Z26" t="s">
         <v>10</v>
       </c>
-      <c r="Z26" t="s">
-        <v>11</v>
-      </c>
       <c r="AC26" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="s">
         <v>1</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AE26" t="s">
         <v>2</v>
       </c>
-      <c r="AE26" t="s">
+      <c r="AF26" t="s">
         <v>3</v>
       </c>
-      <c r="AF26" t="s">
+      <c r="AG26" t="s">
         <v>4</v>
       </c>
-      <c r="AG26" t="s">
+      <c r="AH26" t="s">
         <v>5</v>
       </c>
-      <c r="AH26" t="s">
+      <c r="AI26" t="s">
         <v>6</v>
       </c>
-      <c r="AI26" t="s">
+      <c r="AJ26" t="s">
         <v>7</v>
       </c>
-      <c r="AJ26" t="s">
+      <c r="AK26" t="s">
         <v>8</v>
       </c>
-      <c r="AK26" t="s">
+      <c r="AL26" t="s">
         <v>9</v>
       </c>
-      <c r="AL26" t="s">
+      <c r="AM26" t="s">
         <v>10</v>
-      </c>
-      <c r="AM26" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" s="53">
         <f t="shared" ref="C27:M27" si="78">C4/C$8</f>
-        <v>0.74483585025941923</v>
+        <v>0.71114541979120716</v>
       </c>
       <c r="D27" s="54">
         <f t="shared" si="78"/>
-        <v>0.70854647610135857</v>
+        <v>0.75601374570446733</v>
       </c>
       <c r="E27" s="54">
         <f t="shared" si="78"/>
-        <v>0.89019574584742556</v>
+        <v>0.8935849056603774</v>
       </c>
       <c r="F27" s="54">
         <f t="shared" si="78"/>
-        <v>0.92821596983667543</v>
+        <v>0.90624518118735542</v>
       </c>
       <c r="G27" s="54">
         <f t="shared" si="78"/>
-        <v>0.58065114387970385</v>
+        <v>0.60383536014967254</v>
       </c>
       <c r="H27" s="54">
         <f t="shared" si="78"/>
-        <v>0.78999200554080562</v>
+        <v>0.75549101470321289</v>
       </c>
       <c r="I27" s="54">
         <f t="shared" si="78"/>
-        <v>0.68508202604114865</v>
+        <v>0.62552137643378525</v>
       </c>
       <c r="J27" s="54">
         <f t="shared" si="78"/>
-        <v>0.85645320729269625</v>
+        <v>0.81453400209961502</v>
       </c>
       <c r="K27" s="54">
         <f t="shared" si="78"/>
-        <v>0.78466847800436901</v>
+        <v>0.79603137978772498</v>
       </c>
       <c r="L27" s="54">
         <f t="shared" si="78"/>
-        <v>0.90780407358880355</v>
+        <v>0.87944664031620556</v>
       </c>
       <c r="M27" s="55">
         <f t="shared" si="78"/>
-        <v>0.8682853920727599</v>
+        <v>0.76907005500362424</v>
       </c>
       <c r="O27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P27" s="64" t="e">
         <f>P4/P$8</f>
@@ -3964,7 +4021,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC27" s="64" t="e">
         <f>P27-C27</f>
@@ -4013,54 +4070,54 @@
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="56">
         <f t="shared" ref="C28:M28" si="90">C5/C$8</f>
-        <v>0.15975963420877651</v>
+        <v>0.17203352448169387</v>
       </c>
       <c r="D28" s="57">
         <f t="shared" si="90"/>
-        <v>0.11522973460991384</v>
+        <v>0.16151202749140894</v>
       </c>
       <c r="E28" s="57">
         <f t="shared" si="90"/>
-        <v>9.8779090792649016E-2</v>
+        <v>8.3773584905660378E-2</v>
       </c>
       <c r="F28" s="57">
         <f t="shared" si="90"/>
-        <v>5.5316205390890501E-2</v>
+        <v>6.9082498072474949E-2</v>
       </c>
       <c r="G28" s="57">
         <f t="shared" si="90"/>
-        <v>0.24435738080550398</v>
+        <v>0.22329279700654817</v>
       </c>
       <c r="H28" s="57">
         <f t="shared" si="90"/>
-        <v>0.14329105409157822</v>
+        <v>0.15465601742603013</v>
       </c>
       <c r="I28" s="57">
         <f t="shared" si="90"/>
-        <v>0.1738266470121661</v>
+        <v>0.2068561001042753</v>
       </c>
       <c r="J28" s="57">
         <f t="shared" si="90"/>
-        <v>7.5940129130952536E-2</v>
+        <v>0.10346436486644116</v>
       </c>
       <c r="K28" s="57">
         <f t="shared" si="90"/>
-        <v>0.11781463395271061</v>
+        <v>0.11075219197046608</v>
       </c>
       <c r="L28" s="57">
         <f t="shared" si="90"/>
-        <v>6.4788638146843158E-2</v>
+        <v>8.4980237154150193E-2</v>
       </c>
       <c r="M28" s="58">
         <f t="shared" si="90"/>
-        <v>8.5456080319816399E-2</v>
+        <v>0.14799812390738926</v>
       </c>
       <c r="O28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P28" s="67" t="e">
         <f t="shared" ref="P28:P30" si="91">P5/P$8</f>
@@ -4107,7 +4164,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC28" s="67" t="e">
         <f>P28-C28</f>
@@ -4156,54 +4213,54 @@
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="56">
         <f t="shared" ref="C29:M29" si="93">C6/C$8</f>
-        <v>4.9995249062712369E-2</v>
+        <v>6.8445816791648281E-2</v>
       </c>
       <c r="D29" s="57">
         <f t="shared" si="93"/>
-        <v>0.16000727135993228</v>
+        <v>4.1237113402061855E-2</v>
       </c>
       <c r="E29" s="57">
         <f t="shared" si="93"/>
-        <v>1.0230380600668424E-2</v>
+        <v>1.6603773584905661E-2</v>
       </c>
       <c r="F29" s="57">
         <f t="shared" si="93"/>
-        <v>1.3053325945337223E-2</v>
+        <v>1.7579028527370855E-2</v>
       </c>
       <c r="G29" s="57">
         <f t="shared" si="93"/>
-        <v>0.10103233628542486</v>
+        <v>9.5790458372310566E-2</v>
       </c>
       <c r="H29" s="57">
         <f t="shared" si="93"/>
-        <v>3.67982156093314E-2</v>
+        <v>5.4274823016881468E-2</v>
       </c>
       <c r="I29" s="57">
         <f t="shared" si="93"/>
-        <v>9.4851373885571688E-2</v>
+        <v>8.5114702815432736E-2</v>
       </c>
       <c r="J29" s="57">
         <f t="shared" si="93"/>
-        <v>4.0989789569830806E-2</v>
+        <v>5.1207278665577977E-2</v>
       </c>
       <c r="K29" s="57">
         <f t="shared" si="93"/>
-        <v>7.9907839025010377E-2</v>
+        <v>4.8915551453622523E-2</v>
       </c>
       <c r="L29" s="57">
         <f t="shared" si="93"/>
-        <v>1.6635149600153602E-2</v>
+        <v>2.0256916996047432E-2</v>
       </c>
       <c r="M29" s="58">
         <f t="shared" si="93"/>
-        <v>3.824637806832145E-2</v>
+        <v>5.585639363834051E-2</v>
       </c>
       <c r="O29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P29" s="67" t="e">
         <f t="shared" si="91"/>
@@ -4250,7 +4307,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC29" s="67" t="e">
         <f t="shared" ref="AC29:AC31" si="95">P29-C29</f>
@@ -4299,54 +4356,54 @@
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="59">
         <f t="shared" ref="C30:M30" si="96">C7/C$8</f>
-        <v>4.5409266469091901E-2</v>
+        <v>4.8375238935450669E-2</v>
       </c>
       <c r="D30" s="60">
         <f t="shared" si="96"/>
-        <v>1.6216517928795297E-2</v>
+        <v>4.1237113402061855E-2</v>
       </c>
       <c r="E30" s="60">
         <f t="shared" si="96"/>
-        <v>7.9478275925698439E-4</v>
+        <v>6.0377358490566035E-3</v>
       </c>
       <c r="F30" s="60">
         <f t="shared" si="96"/>
-        <v>3.4144988270970117E-3</v>
+        <v>7.0932922127987666E-3</v>
       </c>
       <c r="G30" s="60">
         <f t="shared" si="96"/>
-        <v>7.3959139029367252E-2</v>
+        <v>7.7081384471468659E-2</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="96"/>
-        <v>2.9918724758284838E-2</v>
+        <v>3.5578144853875476E-2</v>
       </c>
       <c r="I30" s="60">
         <f t="shared" si="96"/>
-        <v>4.6239953061113552E-2</v>
+        <v>8.2507820646506774E-2</v>
       </c>
       <c r="J30" s="60">
         <f t="shared" si="96"/>
-        <v>2.6616874006520484E-2</v>
+        <v>3.0794354368365799E-2</v>
       </c>
       <c r="K30" s="60">
         <f t="shared" si="96"/>
-        <v>1.7609049017910067E-2</v>
+        <v>4.4300876788186436E-2</v>
       </c>
       <c r="L30" s="60">
         <f t="shared" si="96"/>
-        <v>1.077213866419971E-2</v>
+        <v>1.5316205533596838E-2</v>
       </c>
       <c r="M30" s="61">
         <f t="shared" si="96"/>
-        <v>8.012149539102266E-3</v>
+        <v>2.7075427450645971E-2</v>
       </c>
       <c r="O30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P30" s="70" t="e">
         <f t="shared" si="91"/>
@@ -4393,7 +4450,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC30" s="70" t="e">
         <f t="shared" si="95"/>
@@ -4442,7 +4499,7 @@
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="62">
         <f t="shared" ref="C31:M31" si="98">C8/C$8</f>
@@ -4489,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P31" s="68" t="e">
         <f>P8/P$8</f>
@@ -4536,7 +4593,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC31" s="68" t="e">
         <f t="shared" si="95"/>
@@ -4620,54 +4677,54 @@
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="53">
         <f t="shared" ref="C33:M33" si="100">C10/C$14</f>
-        <v>0.63159280873473311</v>
+        <v>0.65571239523599467</v>
       </c>
       <c r="D33" s="54">
         <f t="shared" si="100"/>
-        <v>0.60516188936960569</v>
+        <v>0.73883161512027495</v>
       </c>
       <c r="E33" s="54">
         <f t="shared" si="100"/>
-        <v>0.82591358842933693</v>
+        <v>0.79320754716981134</v>
       </c>
       <c r="F33" s="54">
         <f t="shared" si="100"/>
-        <v>0.90559347150082481</v>
+        <v>0.89267540478026219</v>
       </c>
       <c r="G33" s="54">
         <f t="shared" si="100"/>
-        <v>0.69792118707344308</v>
+        <v>0.72039289055191769</v>
       </c>
       <c r="H33" s="54">
         <f t="shared" si="100"/>
-        <v>0.650433950191456</v>
+        <v>0.70012706480304954</v>
       </c>
       <c r="I33" s="54">
         <f t="shared" si="100"/>
-        <v>0.7487997526839727</v>
+        <v>0.73553180396246087</v>
       </c>
       <c r="J33" s="54">
         <f t="shared" si="100"/>
-        <v>0.85309459712001501</v>
+        <v>0.84771958474279718</v>
       </c>
       <c r="K33" s="54">
         <f t="shared" si="100"/>
-        <v>0.72343952975180348</v>
+        <v>0.81587448084910019</v>
       </c>
       <c r="L33" s="54">
         <f t="shared" si="100"/>
-        <v>0.87017882071955088</v>
+        <v>0.91501976284584985</v>
       </c>
       <c r="M33" s="55">
         <f t="shared" si="100"/>
-        <v>0.78457862088375063</v>
+        <v>0.79623075939112264</v>
       </c>
       <c r="O33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P33" s="64" t="e">
         <f>P10/P$14</f>
@@ -4714,7 +4771,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC33" s="64" t="e">
         <f>P33-C33</f>
@@ -4763,54 +4820,54 @@
     </row>
     <row r="34" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" s="56">
         <f t="shared" ref="C34:M34" si="112">C11/C$14</f>
-        <v>0.22851679564214489</v>
+        <v>0.21680635200705778</v>
       </c>
       <c r="D34" s="57">
         <f t="shared" si="112"/>
-        <v>0.36861151371226059</v>
+        <v>0.18900343642611683</v>
       </c>
       <c r="E34" s="57">
         <f t="shared" si="112"/>
-        <v>0.1428870361218901</v>
+        <v>0.14037735849056604</v>
       </c>
       <c r="F34" s="57">
         <f t="shared" si="112"/>
-        <v>8.2381301271813243E-2</v>
+        <v>9.1904394757131844E-2</v>
       </c>
       <c r="G34" s="57">
         <f t="shared" si="112"/>
-        <v>0.19569910540681731</v>
+        <v>0.18774555659494854</v>
       </c>
       <c r="H34" s="57">
         <f t="shared" si="112"/>
-        <v>0.24502327653005734</v>
+        <v>0.20384824832092938</v>
       </c>
       <c r="I34" s="57">
         <f t="shared" si="112"/>
-        <v>0.14298018852302197</v>
+        <v>0.17179353493222108</v>
       </c>
       <c r="J34" s="57">
         <f t="shared" si="112"/>
-        <v>0.10590460968429219</v>
+        <v>0.10737198180333606</v>
       </c>
       <c r="K34" s="57">
         <f t="shared" si="112"/>
-        <v>0.20826914662810361</v>
+        <v>0.12736502076603601</v>
       </c>
       <c r="L34" s="57">
         <f t="shared" si="112"/>
-        <v>0.10425262241518106</v>
+        <v>6.768774703557312E-2</v>
       </c>
       <c r="M34" s="58">
         <f t="shared" si="112"/>
-        <v>0.14089019944561837</v>
+        <v>0.14927727796017567</v>
       </c>
       <c r="O34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P34" s="67" t="e">
         <f t="shared" ref="P34:P36" si="113">P11/P$14</f>
@@ -4857,7 +4914,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC34" s="67" t="e">
         <f>P34-C34</f>
@@ -4906,54 +4963,54 @@
     </row>
     <row r="35" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35" s="56">
         <f t="shared" ref="C35:M35" si="115">C12/C$14</f>
-        <v>9.4051301469826709E-2</v>
+        <v>7.7562123217173942E-2</v>
       </c>
       <c r="D35" s="57">
         <f t="shared" si="115"/>
-        <v>5.8893693244017357E-3</v>
+        <v>5.8419243986254296E-2</v>
       </c>
       <c r="E35" s="57">
         <f t="shared" si="115"/>
-        <v>1.1497539079676477E-2</v>
+        <v>4.5283018867924525E-2</v>
       </c>
       <c r="F35" s="57">
         <f t="shared" si="115"/>
-        <v>8.7114096947292496E-3</v>
+        <v>1.0023130300693909E-2</v>
       </c>
       <c r="G35" s="57">
         <f t="shared" si="115"/>
-        <v>7.8696051501692801E-2</v>
+        <v>5.8933582787652011E-2</v>
       </c>
       <c r="H35" s="57">
         <f t="shared" si="115"/>
-        <v>6.5922174708720249E-2</v>
+        <v>5.3911780722454165E-2</v>
       </c>
       <c r="I35" s="57">
         <f t="shared" si="115"/>
-        <v>5.6240319284097361E-2</v>
+        <v>5.213764337851929E-2</v>
       </c>
       <c r="J35" s="57">
         <f t="shared" si="115"/>
-        <v>2.7638416516544341E-2</v>
+        <v>2.980286947392978E-2</v>
       </c>
       <c r="K35" s="57">
         <f t="shared" si="115"/>
-        <v>2.89909165008971E-2</v>
+        <v>3.3225657591139823E-2</v>
       </c>
       <c r="L35" s="57">
         <f t="shared" si="115"/>
-        <v>1.5653148432382975E-2</v>
+        <v>1.1363636363636364E-2</v>
       </c>
       <c r="M35" s="58">
         <f t="shared" si="115"/>
-        <v>5.1638911534430627E-2</v>
+        <v>3.9525860231100496E-2</v>
       </c>
       <c r="O35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P35" s="67" t="e">
         <f t="shared" si="113"/>
@@ -5000,7 +5057,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC35" s="67" t="e">
         <f t="shared" ref="AC35:AC37" si="117">P35-C35</f>
@@ -5049,54 +5106,54 @@
     </row>
     <row r="36" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C36" s="59">
         <f t="shared" ref="C36:M36" si="118">C13/C$14</f>
-        <v>4.5839094153295373E-2</v>
+        <v>4.9919129539773566E-2</v>
       </c>
       <c r="D36" s="60">
         <f t="shared" si="118"/>
-        <v>2.0337227593731865E-2</v>
+        <v>1.3745704467353952E-2</v>
       </c>
       <c r="E36" s="60">
         <f t="shared" si="118"/>
-        <v>1.9701836369096545E-2</v>
+        <v>2.1132075471698115E-2</v>
       </c>
       <c r="F36" s="60">
         <f t="shared" si="118"/>
-        <v>3.3138175326325485E-3</v>
+        <v>5.3970701619121047E-3</v>
       </c>
       <c r="G36" s="60">
         <f t="shared" si="118"/>
-        <v>2.7683656018046877E-2</v>
+        <v>3.292797006548176E-2</v>
       </c>
       <c r="H36" s="60">
         <f t="shared" si="118"/>
-        <v>3.8620598569766525E-2</v>
+        <v>4.2112906153566894E-2</v>
       </c>
       <c r="I36" s="60">
         <f t="shared" si="118"/>
-        <v>5.1979739508908052E-2</v>
+        <v>4.0537017726798748E-2</v>
       </c>
       <c r="J36" s="60">
         <f t="shared" si="118"/>
-        <v>1.3362376679148377E-2</v>
+        <v>1.5105563979937012E-2</v>
       </c>
       <c r="K36" s="60">
         <f t="shared" si="118"/>
-        <v>3.930040711919585E-2</v>
+        <v>2.3534840793724043E-2</v>
       </c>
       <c r="L36" s="60">
         <f t="shared" si="118"/>
-        <v>9.91540843288506E-3</v>
+        <v>5.9288537549407111E-3</v>
       </c>
       <c r="M36" s="61">
         <f t="shared" si="118"/>
-        <v>2.2892268136200267E-2</v>
+        <v>1.496610241760116E-2</v>
       </c>
       <c r="O36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P36" s="70" t="e">
         <f t="shared" si="113"/>
@@ -5143,7 +5200,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AC36" s="70" t="e">
         <f t="shared" si="117"/>
@@ -5192,7 +5249,7 @@
     </row>
     <row r="37" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="62">
         <f t="shared" ref="C37:M37" si="120">C14/C$14</f>
@@ -5239,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P37" s="68" t="e">
         <f>P14/P$14</f>
@@ -5286,7 +5343,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC37" s="68" t="e">
         <f t="shared" si="117"/>
@@ -5370,54 +5427,54 @@
     </row>
     <row r="39" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="53">
         <f t="shared" ref="C39:M39" si="122">C16/C$23</f>
-        <v>0.51336975881758873</v>
+        <v>0.49757388619320686</v>
       </c>
       <c r="D39" s="54">
         <f t="shared" si="122"/>
-        <v>0.47549297716979355</v>
+        <v>0.56357388316151202</v>
       </c>
       <c r="E39" s="54">
         <f t="shared" si="122"/>
-        <v>0.72905163483208246</v>
+        <v>0.73056603773584905</v>
       </c>
       <c r="F39" s="54">
         <f t="shared" si="122"/>
-        <v>0.83916304310391465</v>
+        <v>0.81958365458750959</v>
       </c>
       <c r="G39" s="54">
         <f t="shared" si="122"/>
-        <v>0.43765746238355946</v>
+        <v>0.46155285313376987</v>
       </c>
       <c r="H39" s="54">
         <f t="shared" si="122"/>
-        <v>0.52348411864860178</v>
+        <v>0.54492648393537846</v>
       </c>
       <c r="I39" s="54">
         <f t="shared" si="122"/>
-        <v>0.57236788044428111</v>
+        <v>0.49687174139728885</v>
       </c>
       <c r="J39" s="54">
         <f t="shared" si="122"/>
-        <v>0.75990287392312594</v>
+        <v>0.72022629184649478</v>
       </c>
       <c r="K39" s="54">
         <f t="shared" si="122"/>
-        <v>0.59802788163206166</v>
+        <v>0.68158744808491001</v>
       </c>
       <c r="L39" s="54">
         <f t="shared" si="122"/>
-        <v>0.81656788332604102</v>
+        <v>0.8236166007905138</v>
       </c>
       <c r="M39" s="55">
         <f t="shared" si="122"/>
-        <v>0.68530630491170785</v>
+        <v>0.63927855711422843</v>
       </c>
       <c r="O39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P39" s="64" t="e">
         <f>P16/P$23</f>
@@ -5464,7 +5521,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC39" s="64" t="e">
         <f>P39-C39</f>
@@ -5513,54 +5570,54 @@
     </row>
     <row r="40" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="56">
         <f t="shared" ref="C40:M40" si="134">C17/C$23</f>
-        <v>0.23110330362534195</v>
+        <v>0.23937656227025436</v>
       </c>
       <c r="D40" s="57">
         <f t="shared" si="134"/>
-        <v>0.32234059144003235</v>
+        <v>0.28522336769759449</v>
       </c>
       <c r="E40" s="57">
         <f t="shared" si="134"/>
-        <v>0.21874634740755017</v>
+        <v>0.16679245283018868</v>
       </c>
       <c r="F40" s="57">
         <f t="shared" si="134"/>
-        <v>0.13045157501621396</v>
+        <v>0.13138010794140323</v>
       </c>
       <c r="G40" s="57">
         <f t="shared" si="134"/>
-        <v>0.24218730640277819</v>
+        <v>0.25191768007483628</v>
       </c>
       <c r="H40" s="57">
         <f t="shared" si="134"/>
-        <v>0.2726950383795323</v>
+        <v>0.24269377382465057</v>
       </c>
       <c r="I40" s="57">
         <f t="shared" si="134"/>
-        <v>0.20460604286491463</v>
+        <v>0.22445255474452555</v>
       </c>
       <c r="J40" s="57">
         <f t="shared" si="134"/>
-        <v>0.11425566316686157</v>
+        <v>0.13834130409424938</v>
       </c>
       <c r="K40" s="57">
         <f t="shared" si="134"/>
-        <v>0.19264127835667413</v>
+        <v>0.15597600369173972</v>
       </c>
       <c r="L40" s="57">
         <f t="shared" si="134"/>
-        <v>0.10841419362146783</v>
+        <v>0.11709486166007906</v>
       </c>
       <c r="M40" s="58">
         <f t="shared" si="134"/>
-        <v>0.18935746594888966</v>
+        <v>0.1979704089029122</v>
       </c>
       <c r="O40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P40" s="67" t="e">
         <f t="shared" ref="P40:P45" si="135">P17/P$23</f>
@@ -5607,7 +5664,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC40" s="67" t="e">
         <f>P40-C40</f>
@@ -5656,54 +5713,54 @@
     </row>
     <row r="41" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="56">
         <f t="shared" ref="C41:M41" si="137">C18/C$23</f>
-        <v>0.13208753037985155</v>
+        <v>0.12645199235406557</v>
       </c>
       <c r="D41" s="57">
         <f t="shared" si="137"/>
-        <v>3.1658533255916194E-2</v>
+        <v>6.8728522336769765E-2</v>
       </c>
       <c r="E41" s="57">
         <f t="shared" si="137"/>
-        <v>2.9311657660809558E-2</v>
+        <v>5.8867924528301883E-2</v>
       </c>
       <c r="F41" s="57">
         <f t="shared" si="137"/>
-        <v>2.0804762030345376E-2</v>
+        <v>3.130300693909021E-2</v>
       </c>
       <c r="G41" s="57">
         <f t="shared" si="137"/>
-        <v>0.1485041518790722</v>
+        <v>0.13367633302151544</v>
       </c>
       <c r="H41" s="57">
         <f t="shared" si="137"/>
-        <v>0.1217556233818148</v>
+        <v>0.11544744962788164</v>
       </c>
       <c r="I41" s="57">
         <f t="shared" si="137"/>
-        <v>7.2363205692239016E-2</v>
+        <v>0.12017726798748697</v>
       </c>
       <c r="J41" s="57">
         <f t="shared" si="137"/>
-        <v>7.1172203238233131E-2</v>
+        <v>7.8618919864691467E-2</v>
       </c>
       <c r="K41" s="57">
         <f t="shared" si="137"/>
-        <v>0.12551518963382341</v>
+        <v>8.0756806645131518E-2</v>
       </c>
       <c r="L41" s="57">
         <f t="shared" si="137"/>
-        <v>4.8209035773637672E-2</v>
+        <v>3.2608695652173912E-2</v>
       </c>
       <c r="M41" s="58">
         <f t="shared" si="137"/>
-        <v>7.3321011164133226E-2</v>
+        <v>9.4145738285080799E-2</v>
       </c>
       <c r="O41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P41" s="67" t="e">
         <f t="shared" si="135"/>
@@ -5750,7 +5807,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC41" s="67" t="e">
         <f t="shared" ref="AC41:AC43" si="139">P41-C41</f>
@@ -5799,54 +5856,54 @@
     </row>
     <row r="42" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" s="56">
         <f t="shared" ref="C42:M42" si="140">C19/C$23</f>
-        <v>6.6703195491678552E-2</v>
+        <v>8.7046022643728863E-2</v>
       </c>
       <c r="D42" s="57">
         <f t="shared" si="140"/>
-        <v>0.1609261100303947</v>
+        <v>6.1855670103092786E-2</v>
       </c>
       <c r="E42" s="57">
         <f t="shared" si="140"/>
-        <v>2.2319279467111552E-2</v>
+        <v>3.2452830188679248E-2</v>
       </c>
       <c r="F42" s="57">
         <f t="shared" si="140"/>
-        <v>8.9716514529827925E-3</v>
+        <v>1.3261372397841172E-2</v>
       </c>
       <c r="G42" s="57">
         <f t="shared" si="140"/>
-        <v>0.13516504487919023</v>
+        <v>0.10215154349859681</v>
       </c>
       <c r="H42" s="57">
         <f t="shared" si="140"/>
-        <v>5.3580506412374954E-2</v>
+        <v>6.6799782174623346E-2</v>
       </c>
       <c r="I42" s="57">
         <f t="shared" si="140"/>
-        <v>7.1681645658085325E-2</v>
+        <v>0.10192909280500521</v>
       </c>
       <c r="J42" s="57">
         <f t="shared" si="140"/>
-        <v>4.3878988904321604E-2</v>
+        <v>4.4091916481978306E-2</v>
       </c>
       <c r="K42" s="57">
         <f t="shared" si="140"/>
-        <v>7.026460936853518E-2</v>
+        <v>5.5376095985233041E-2</v>
       </c>
       <c r="L42" s="57">
         <f t="shared" si="140"/>
-        <v>1.9159588574794585E-2</v>
+        <v>1.6304347826086956E-2</v>
       </c>
       <c r="M42" s="58">
         <f t="shared" si="140"/>
-        <v>4.7706992719251336E-2</v>
+        <v>5.0611862021916171E-2</v>
       </c>
       <c r="O42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P42" s="67" t="e">
         <f t="shared" si="135"/>
@@ -5893,7 +5950,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC42" s="67" t="e">
         <f t="shared" si="139"/>
@@ -5942,54 +5999,54 @@
     </row>
     <row r="43" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="56">
         <f t="shared" ref="C43:M43" si="142">C20/C$23</f>
-        <v>3.3491406468542519E-2</v>
+        <v>3.1098367887075429E-2</v>
       </c>
       <c r="D43" s="57">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>3.4364261168384879E-3</v>
       </c>
       <c r="E43" s="57">
         <f t="shared" si="142"/>
-        <v>5.710806324463922E-4</v>
+        <v>9.8113207547169817E-3</v>
       </c>
       <c r="F43" s="57">
         <f t="shared" si="142"/>
-        <v>6.0896839654306085E-4</v>
+        <v>2.9298380878951427E-3</v>
       </c>
       <c r="G43" s="57">
         <f t="shared" si="142"/>
-        <v>2.5915973629631706E-2</v>
+        <v>3.3395696913002808E-2</v>
       </c>
       <c r="H43" s="57">
         <f t="shared" si="142"/>
-        <v>2.1679027664400823E-2</v>
+        <v>2.0511889635142493E-2</v>
       </c>
       <c r="I43" s="57">
         <f t="shared" si="142"/>
-        <v>5.1199134750915136E-2</v>
+        <v>3.7539103232533892E-2</v>
       </c>
       <c r="J43" s="57">
         <f t="shared" si="142"/>
-        <v>4.8173124191191637E-3</v>
+        <v>1.2539367782573195E-2</v>
       </c>
       <c r="K43" s="57">
         <f t="shared" si="142"/>
-        <v>9.8716273325425759E-3</v>
+        <v>1.3382556529764651E-2</v>
       </c>
       <c r="L43" s="57">
         <f t="shared" si="142"/>
-        <v>5.0757291661532719E-3</v>
+        <v>5.434782608695652E-3</v>
       </c>
       <c r="M43" s="58">
         <f t="shared" si="142"/>
-        <v>1.8314807181532354E-3</v>
+        <v>1.496610241760116E-2</v>
       </c>
       <c r="O43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P43" s="67" t="e">
         <f t="shared" si="135"/>
@@ -6036,7 +6093,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC43" s="67" t="e">
         <f t="shared" si="139"/>
@@ -6085,54 +6142,54 @@
     </row>
     <row r="44" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C44" s="56">
         <f t="shared" ref="C44:M44" si="144">C21/C$23</f>
-        <v>1.870779525306979E-2</v>
+        <v>1.2792236435818262E-2</v>
       </c>
       <c r="D44" s="57">
         <f t="shared" si="144"/>
-        <v>6.3095040780430879E-4</v>
+        <v>1.0309278350515464E-2</v>
       </c>
       <c r="E44" s="57">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>7.5471698113207543E-4</v>
       </c>
       <c r="F44" s="57">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>1.0794140323824211E-3</v>
       </c>
       <c r="G44" s="57">
         <f t="shared" si="144"/>
-        <v>7.3333573428303392E-3</v>
+        <v>1.2628624883068288E-2</v>
       </c>
       <c r="H44" s="57">
         <f t="shared" si="144"/>
-        <v>5.1249468756499545E-3</v>
+        <v>5.8086767108368126E-3</v>
       </c>
       <c r="I44" s="57">
         <f t="shared" si="144"/>
-        <v>2.221717418010585E-2</v>
+        <v>1.2643378519290928E-2</v>
       </c>
       <c r="J44" s="57">
         <f t="shared" si="144"/>
-        <v>4.3051330777992532E-3</v>
+        <v>4.5491659862358568E-3</v>
       </c>
       <c r="K44" s="57">
         <f t="shared" si="144"/>
-        <v>1.418817074327778E-3</v>
+        <v>8.7678818643285653E-3</v>
       </c>
       <c r="L44" s="57">
         <f t="shared" si="144"/>
-        <v>2.374866866820596E-3</v>
+        <v>2.9644268774703555E-3</v>
       </c>
       <c r="M44" s="58">
         <f t="shared" si="144"/>
-        <v>2.4767445378646941E-3</v>
+        <v>1.9613695476058501E-3</v>
       </c>
       <c r="O44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P44" s="67" t="e">
         <f t="shared" si="135"/>
@@ -6179,7 +6236,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC44" s="67" t="e">
         <f>P44-C44</f>
@@ -6228,54 +6285,54 @@
     </row>
     <row r="45" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" s="59">
         <f t="shared" ref="C45:M45" si="146">C22/C$23</f>
-        <v>4.5370099639269537E-3</v>
+        <v>5.6609322158506104E-3</v>
       </c>
       <c r="D45" s="60">
         <f t="shared" si="146"/>
-        <v>8.9508376960589549E-3</v>
+        <v>6.8728522336769758E-3</v>
       </c>
       <c r="E45" s="60">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>7.5471698113207543E-4</v>
       </c>
       <c r="F45" s="60">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>4.6260601387818041E-4</v>
       </c>
       <c r="G45" s="60">
         <f t="shared" si="146"/>
-        <v>3.2367034829378694E-3</v>
+        <v>4.6772684752104769E-3</v>
       </c>
       <c r="H45" s="60">
         <f t="shared" si="146"/>
-        <v>1.6807386376255389E-3</v>
+        <v>3.8119440914866584E-3</v>
       </c>
       <c r="I45" s="60">
         <f t="shared" si="146"/>
-        <v>5.564916409458746E-3</v>
+        <v>6.3868613138686131E-3</v>
       </c>
       <c r="J45" s="60">
         <f t="shared" si="146"/>
-        <v>1.6678252705393513E-3</v>
+        <v>1.6330339437769742E-3</v>
       </c>
       <c r="K45" s="60">
         <f t="shared" si="146"/>
-        <v>2.2605966020352109E-3</v>
+        <v>4.1532071988924779E-3</v>
       </c>
       <c r="L45" s="60">
         <f t="shared" si="146"/>
-        <v>1.987026710847679E-4</v>
+        <v>1.976284584980237E-3</v>
       </c>
       <c r="M45" s="61">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>1.0659617106553532E-3</v>
       </c>
       <c r="O45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P45" s="70" t="e">
         <f t="shared" si="135"/>
@@ -6322,7 +6379,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC45" s="70" t="e">
         <f>P45-C45</f>
@@ -6371,7 +6428,7 @@
     </row>
     <row r="46" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C46" s="62">
         <f t="shared" ref="C46:M46" si="148">C23/C$23</f>
@@ -6418,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P46" s="68" t="e">
         <f>P23/P$23</f>
@@ -6465,7 +6522,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC46" s="68" t="e">
         <f t="shared" ref="AC46" si="150">P46-C46</f>
@@ -6514,128 +6571,128 @@
     </row>
     <row r="48" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="11"/>
     </row>
     <row r="50" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
+        <v>49</v>
+      </c>
+      <c r="O50" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB50" t="s">
         <v>50</v>
-      </c>
-      <c r="O50" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:39" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
         <v>1</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>2</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>3</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>4</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>5</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>6</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>7</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>8</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>9</v>
       </c>
-      <c r="L51" t="s">
+      <c r="M51" t="s">
         <v>10</v>
       </c>
-      <c r="M51" t="s">
-        <v>11</v>
-      </c>
       <c r="P51" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="s">
         <v>1</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
         <v>2</v>
       </c>
-      <c r="R51" t="s">
+      <c r="S51" t="s">
         <v>3</v>
       </c>
-      <c r="S51" t="s">
+      <c r="T51" t="s">
         <v>4</v>
       </c>
-      <c r="T51" t="s">
+      <c r="U51" t="s">
         <v>5</v>
       </c>
-      <c r="U51" t="s">
+      <c r="V51" t="s">
         <v>6</v>
       </c>
-      <c r="V51" t="s">
+      <c r="W51" t="s">
         <v>7</v>
       </c>
-      <c r="W51" t="s">
+      <c r="X51" t="s">
         <v>8</v>
       </c>
-      <c r="X51" t="s">
+      <c r="Y51" t="s">
         <v>9</v>
       </c>
-      <c r="Y51" t="s">
+      <c r="Z51" t="s">
         <v>10</v>
       </c>
-      <c r="Z51" t="s">
-        <v>11</v>
-      </c>
       <c r="AC51" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="s">
         <v>1</v>
       </c>
-      <c r="AD51" t="s">
+      <c r="AE51" t="s">
         <v>2</v>
       </c>
-      <c r="AE51" t="s">
+      <c r="AF51" t="s">
         <v>3</v>
       </c>
-      <c r="AF51" t="s">
+      <c r="AG51" t="s">
         <v>4</v>
       </c>
-      <c r="AG51" t="s">
+      <c r="AH51" t="s">
         <v>5</v>
       </c>
-      <c r="AH51" t="s">
+      <c r="AI51" t="s">
         <v>6</v>
       </c>
-      <c r="AI51" t="s">
+      <c r="AJ51" t="s">
         <v>7</v>
       </c>
-      <c r="AJ51" t="s">
+      <c r="AK51" t="s">
         <v>8</v>
       </c>
-      <c r="AK51" t="s">
+      <c r="AL51" t="s">
         <v>9</v>
       </c>
-      <c r="AL51" t="s">
+      <c r="AM51" t="s">
         <v>10</v>
-      </c>
-      <c r="AM51" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C52" s="16" cm="1">
         <f t="array" ref="C52">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A52),0),MATCH(calibration!$B52,constants!$C$4:$R$4,0))</f>
@@ -6682,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P52" s="16" t="e">
         <f>$C$48*LN(C27/P27)</f>
@@ -6729,7 +6786,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB52" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC52" s="16"/>
       <c r="AD52" s="17"/>
@@ -6745,10 +6802,10 @@
     </row>
     <row r="53" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C53" s="19" cm="1">
         <f t="array" ref="C53">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A53),0),MATCH(calibration!$B53,constants!$C$4:$R$4,0))</f>
@@ -6795,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P53" s="19" t="e">
         <f>$C$48*LN(C28/P28)</f>
@@ -6842,7 +6899,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB53" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC53" s="19" t="e">
         <f>C53+P53-$P$52</f>
@@ -6891,10 +6948,10 @@
     </row>
     <row r="54" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" s="19" cm="1">
         <f t="array" ref="C54">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A54),0),MATCH(calibration!$B54,constants!$C$4:$R$4,0))</f>
@@ -6941,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P54" s="19" t="e">
         <f>$C$48*LN(C29/P29)</f>
@@ -6988,7 +7045,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB54" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC54" s="19" t="e">
         <f t="shared" ref="AC54:AC55" si="155">C54+P54-$P$52</f>
@@ -7037,10 +7094,10 @@
     </row>
     <row r="55" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" s="21" cm="1">
         <f t="array" ref="C55">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A55),0),MATCH(calibration!$B55,constants!$C$4:$R$4,0))</f>
@@ -7087,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P55" s="21" t="e">
         <f>$C$48*LN(C30/P30)</f>
@@ -7134,7 +7191,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB55" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC55" s="19" t="e">
         <f t="shared" si="155"/>
@@ -7183,10 +7240,10 @@
     </row>
     <row r="56" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C56" s="24" cm="1">
         <f t="array" ref="C56">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A56),0),MATCH(calibration!$B56,constants!$C$5:$R$5,0))</f>
@@ -7233,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P56" s="24" t="e">
         <f>$C$48*LN(C33/P33)</f>
@@ -7280,7 +7337,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB56" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC56" s="24"/>
       <c r="AD56" s="25"/>
@@ -7296,10 +7353,10 @@
     </row>
     <row r="57" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57" s="27" cm="1">
         <f t="array" ref="C57">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A57),0),MATCH(calibration!$B57,constants!$C$5:$R$5,0))</f>
@@ -7346,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P57" s="27" t="e">
         <f>$C$48*LN(C34/P34)</f>
@@ -7393,7 +7450,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB57" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC57" s="27" t="e">
         <f t="shared" ref="AC57:AC58" si="159">C57+P57-$P$52</f>
@@ -7442,10 +7499,10 @@
     </row>
     <row r="58" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C58" s="27" cm="1">
         <f t="array" ref="C58">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A58),0),MATCH(calibration!$B58,constants!$C$5:$R$5,0))</f>
@@ -7492,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P58" s="27" t="e">
         <f>$C$48*LN(C35/P35)</f>
@@ -7539,7 +7596,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB58" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC58" s="27" t="e">
         <f t="shared" si="159"/>
@@ -7588,10 +7645,10 @@
     </row>
     <row r="59" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59" s="29" cm="1">
         <f t="array" ref="C59">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A59),0),MATCH(calibration!$B59,constants!$C$5:$R$5,0))</f>
@@ -7638,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P59" s="29" t="e">
         <f>$C$48*LN(C36/P36)</f>
@@ -7685,7 +7742,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB59" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AC59" s="29" t="e">
         <f t="shared" ref="AC59" si="171">C59+P59-$P$52</f>
@@ -7734,10 +7791,10 @@
     </row>
     <row r="60" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C60" s="32" cm="1">
         <f t="array" ref="C60">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A60),0),MATCH(calibration!$B60,constants!$C$3:$R$3,0))</f>
@@ -7784,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P60" s="32" t="e">
         <f t="shared" ref="P60:P66" si="181">$C$48*LN(C39/P39)</f>
@@ -7831,7 +7888,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB60" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC60" s="32"/>
       <c r="AD60" s="33"/>
@@ -7847,10 +7904,10 @@
     </row>
     <row r="61" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C61" s="35" cm="1">
         <f t="array" ref="C61">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A61),0),MATCH(calibration!$B61,constants!$C$3:$R$3,0))</f>
@@ -7897,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P61" s="35" t="e">
         <f t="shared" si="181"/>
@@ -7944,7 +8001,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB61" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC61" s="35"/>
       <c r="AD61" s="14"/>
@@ -7960,10 +8017,10 @@
     </row>
     <row r="62" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62" s="35" cm="1">
         <f t="array" ref="C62">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A62),0),MATCH(calibration!$B62,constants!$C$3:$R$3,0))</f>
@@ -8010,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P62" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8057,7 +8114,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB62" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC62" s="35" t="e">
         <f t="shared" ref="AC62:AC66" si="185">C62+P62-$P$60</f>
@@ -8106,10 +8163,10 @@
     </row>
     <row r="63" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C63" s="35" cm="1">
         <f t="array" ref="C63">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A63),0),MATCH(calibration!$B63,constants!$C$3:$R$3,0))</f>
@@ -8156,7 +8213,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P63" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8203,7 +8260,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB63" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC63" s="35" t="e">
         <f t="shared" si="185"/>
@@ -8252,10 +8309,10 @@
     </row>
     <row r="64" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C64" s="35" cm="1">
         <f t="array" ref="C64">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A64),0),MATCH(calibration!$B64,constants!$C$3:$R$3,0))</f>
@@ -8302,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P64" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8349,7 +8406,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB64" s="14" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="AC64" s="35" t="e">
         <f t="shared" si="185"/>
@@ -8398,10 +8455,10 @@
     </row>
     <row r="65" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C65" s="35" cm="1">
         <f t="array" ref="C65">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A65),0),MATCH(calibration!$B65,constants!$C$3:$R$3,0))</f>
@@ -8448,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P65" s="35" t="e">
         <f t="shared" si="181"/>
@@ -8495,7 +8552,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB65" s="14" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="AC65" s="35" t="e">
         <f t="shared" si="185"/>
@@ -8544,10 +8601,10 @@
     </row>
     <row r="66" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" s="37" cm="1">
         <f t="array" ref="C66">INDEX(constants!$C$6:$R$38,MATCH(1,(constants!$A$6:$A$38=calibration!C$51)*(constants!$B$6:$B$38=calibration!$A66),0),MATCH(calibration!$B66,constants!$C$3:$R$3,0))</f>
@@ -8594,7 +8651,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P66" s="37" t="e">
         <f t="shared" si="181"/>
@@ -8641,7 +8698,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB66" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC66" s="37" t="e">
         <f t="shared" si="185"/>
@@ -8708,413 +8765,413 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C1" s="73" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="S1" s="73" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
+      <c r="N2" t="s">
         <v>63</v>
       </c>
-      <c r="E2" t="s">
+      <c r="O2" t="s">
         <v>64</v>
       </c>
-      <c r="F2" t="s">
+      <c r="P2" t="s">
         <v>65</v>
       </c>
-      <c r="G2" t="s">
+      <c r="Q2" t="s">
         <v>66</v>
       </c>
-      <c r="H2" t="s">
+      <c r="R2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" t="s">
-        <v>73</v>
-      </c>
-      <c r="O2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>76</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>77</v>
-      </c>
       <c r="S2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" t="s">
+        <v>55</v>
+      </c>
+      <c r="W2" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC2" t="s">
         <v>62</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AD2" t="s">
         <v>63</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AE2" t="s">
         <v>64</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AF2" t="s">
         <v>65</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AG2" t="s">
         <v>66</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AH2" t="s">
         <v>67</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>37</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G3" t="s">
+      <c r="S3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" t="s">
+      <c r="V3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="W3" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH3" t="s">
         <v>38</v>
-      </c>
-      <c r="J3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s">
-        <v>78</v>
-      </c>
-      <c r="N3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>79</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" t="s">
-        <v>38</v>
-      </c>
-      <c r="W3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>33</v>
-      </c>
       <c r="K4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" t="s">
+        <v>31</v>
+      </c>
+      <c r="W4" t="s">
         <v>32</v>
       </c>
-      <c r="T4" t="s">
+      <c r="X4" t="s">
         <v>32</v>
       </c>
-      <c r="U4" t="s">
+      <c r="Y4" t="s">
         <v>32</v>
       </c>
-      <c r="V4" t="s">
+      <c r="Z4" t="s">
         <v>32</v>
       </c>
-      <c r="W4" t="s">
-        <v>33</v>
-      </c>
-      <c r="X4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>33</v>
-      </c>
       <c r="AA4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AC4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AD4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AE4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AH4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="73" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="G5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="K5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="O5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="R5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R5" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="S5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="U5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="V5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="V5" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="W5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="Y5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Y5" s="9" t="s">
+      <c r="Z5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="Z5" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="AA5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AC5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AC5" s="9" t="s">
+      <c r="AD5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AD5" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="AE5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AF5" s="9" t="s">
+      <c r="AG5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AG5" s="9" t="s">
+      <c r="AH5" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="AH5" s="9" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6">
@@ -9184,10 +9241,10 @@
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R7" s="7"/>
       <c r="S7">
@@ -9257,10 +9314,10 @@
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R8" s="7"/>
       <c r="S8">
@@ -9330,10 +9387,10 @@
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R9" s="7"/>
       <c r="S9">
@@ -9403,10 +9460,10 @@
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R10" s="7"/>
       <c r="S10">
@@ -9476,10 +9533,10 @@
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R11" s="7"/>
       <c r="S11">
@@ -9549,10 +9606,10 @@
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R12" s="7"/>
       <c r="S12">
@@ -9622,10 +9679,10 @@
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13">
@@ -9695,10 +9752,10 @@
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R14" s="7"/>
       <c r="S14">
@@ -9768,10 +9825,10 @@
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15">
@@ -9841,10 +9898,10 @@
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R16" s="7"/>
       <c r="S16">
@@ -9914,10 +9971,10 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R17" s="7"/>
       <c r="S17">
@@ -9987,10 +10044,10 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R18" s="7"/>
       <c r="S18">
@@ -10060,10 +10117,10 @@
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19">
@@ -10133,10 +10190,10 @@
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R20" s="7"/>
       <c r="S20">
@@ -10206,10 +10263,10 @@
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R21" s="7"/>
       <c r="S21">
@@ -10279,10 +10336,10 @@
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R22" s="7"/>
       <c r="S22">
@@ -10352,10 +10409,10 @@
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R23" s="7"/>
       <c r="S23">
@@ -10425,10 +10482,10 @@
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R24" s="7"/>
       <c r="S24">
@@ -10498,10 +10555,10 @@
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R25" s="7"/>
       <c r="S25">
@@ -10571,10 +10628,10 @@
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R26" s="7"/>
       <c r="S26">
@@ -10644,10 +10701,10 @@
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R27" s="7"/>
       <c r="S27">
@@ -10717,10 +10774,10 @@
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R28" s="7"/>
       <c r="S28">
@@ -10790,10 +10847,10 @@
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R29" s="7"/>
       <c r="S29">
@@ -10863,10 +10920,10 @@
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R30" s="7"/>
       <c r="S30">
@@ -10936,10 +10993,10 @@
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R31" s="7"/>
       <c r="S31">
@@ -11009,10 +11066,10 @@
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R32" s="7"/>
       <c r="S32">
@@ -11082,10 +11139,10 @@
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R33" s="7"/>
       <c r="S33">
@@ -11155,10 +11212,10 @@
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R34" s="7"/>
       <c r="S34">
@@ -11228,10 +11285,10 @@
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R35" s="7"/>
       <c r="S35">
@@ -11301,10 +11358,10 @@
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R36" s="7"/>
       <c r="S36">
@@ -11374,10 +11431,10 @@
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R37" s="7"/>
       <c r="S37">
@@ -11447,10 +11504,10 @@
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="R38" s="7"/>
       <c r="S38">
@@ -11528,56 +11585,57 @@
   <sheetPr>
     <tabColor rgb="FF9BBB59"/>
   </sheetPr>
-  <dimension ref="B1:S19"/>
+  <dimension ref="B1:S4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
       <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" t="s">
-        <v>7</v>
-      </c>
       <c r="J3" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" t="s">
         <v>9</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" t="s">
-        <v>11</v>
+      <c r="N3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -11595,81 +11653,6 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11680,1062 +11663,1115 @@
   <sheetPr>
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="B1:Z50"/>
+  <dimension ref="B1:AA50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" t="s">
+      <c r="W3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" t="s">
+      <c r="X3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" t="s">
+      <c r="Y3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" t="s">
+      <c r="Z3" t="s">
         <v>9</v>
       </c>
-      <c r="L3" t="s">
+      <c r="AA3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" t="s">
+    </row>
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="40">
+        <v>13536</v>
+      </c>
+      <c r="D4" s="40">
+        <v>328</v>
+      </c>
+      <c r="E4" s="40">
+        <v>1936</v>
+      </c>
+      <c r="F4" s="40">
+        <v>10630</v>
+      </c>
+      <c r="G4" s="40">
+        <v>9868</v>
+      </c>
+      <c r="H4" s="40">
+        <v>6004</v>
+      </c>
+      <c r="I4" s="40">
+        <v>7624</v>
+      </c>
+      <c r="J4" s="40">
+        <v>24698</v>
+      </c>
+      <c r="K4" s="40">
+        <v>2954</v>
+      </c>
+      <c r="L4" s="40">
+        <v>3334</v>
+      </c>
+      <c r="M4" s="40">
+        <v>29986</v>
+      </c>
+      <c r="N4">
+        <v>110898</v>
+      </c>
+      <c r="P4" t="s">
         <v>11</v>
       </c>
-      <c r="P3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U3" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="40">
-        <v>1073836.7390483427</v>
-      </c>
-      <c r="D4" s="40">
-        <v>27215.565172606839</v>
-      </c>
-      <c r="E4" s="40">
-        <v>220460.70513257475</v>
-      </c>
-      <c r="F4" s="40">
-        <v>1153447.6274418959</v>
-      </c>
-      <c r="G4" s="40">
-        <v>481077.72790936055</v>
-      </c>
-      <c r="H4" s="40">
-        <v>307865.80422767292</v>
-      </c>
-      <c r="I4" s="40">
-        <v>417960.03210757487</v>
-      </c>
-      <c r="J4" s="40">
-        <v>1238342.289831331</v>
-      </c>
-      <c r="K4" s="40">
-        <v>167717.11888182827</v>
-      </c>
-      <c r="L4" s="40">
-        <v>284812.38567461743</v>
-      </c>
-      <c r="M4" s="40">
-        <v>675881.93703013682</v>
-      </c>
-      <c r="O4" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="41">
+      <c r="Q4" s="41">
         <f>C4</f>
-        <v>1073836.7390483427</v>
-      </c>
-      <c r="Q4" s="41">
-        <f t="shared" ref="Q4:Z6" si="0">D4</f>
-        <v>27215.565172606839</v>
+        <v>13536</v>
       </c>
       <c r="R4" s="41">
-        <f t="shared" si="0"/>
-        <v>220460.70513257475</v>
+        <f t="shared" ref="R4:AA6" si="0">D4</f>
+        <v>328</v>
       </c>
       <c r="S4" s="41">
         <f t="shared" si="0"/>
-        <v>1153447.6274418959</v>
+        <v>1936</v>
       </c>
       <c r="T4" s="41">
         <f t="shared" si="0"/>
-        <v>481077.72790936055</v>
+        <v>10630</v>
       </c>
       <c r="U4" s="41">
         <f t="shared" si="0"/>
-        <v>307865.80422767292</v>
+        <v>9868</v>
       </c>
       <c r="V4" s="41">
         <f t="shared" si="0"/>
-        <v>417960.03210757487</v>
+        <v>6004</v>
       </c>
       <c r="W4" s="41">
         <f t="shared" si="0"/>
-        <v>1238342.289831331</v>
+        <v>7624</v>
       </c>
       <c r="X4" s="41">
         <f t="shared" si="0"/>
-        <v>167717.11888182827</v>
+        <v>24698</v>
       </c>
       <c r="Y4" s="41">
         <f t="shared" si="0"/>
-        <v>284812.38567461743</v>
+        <v>2954</v>
       </c>
       <c r="Z4" s="41">
         <f t="shared" si="0"/>
-        <v>675881.93703013682</v>
-      </c>
-    </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.25">
+        <v>3334</v>
+      </c>
+      <c r="AA4" s="41">
+        <f t="shared" si="0"/>
+        <v>29986</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="C5" s="40">
-        <v>315775.85863241396</v>
+        <v>3858</v>
       </c>
       <c r="D5" s="40">
-        <v>12509.849452174283</v>
+        <v>90</v>
       </c>
       <c r="E5" s="40">
-        <v>39778.288994175316</v>
+        <v>306</v>
       </c>
       <c r="F5" s="40">
-        <v>108767.47002583783</v>
+        <v>986</v>
       </c>
       <c r="G5" s="40">
-        <v>97998.864931216172</v>
+        <v>2138</v>
       </c>
       <c r="H5" s="40">
-        <v>109850.45301999335</v>
+        <v>1602</v>
       </c>
       <c r="I5" s="40">
-        <v>65620.366254890396</v>
+        <v>1326</v>
       </c>
       <c r="J5" s="40">
-        <v>113589.2090666775</v>
+        <v>2330</v>
       </c>
       <c r="K5" s="40">
-        <v>37104.387632676371</v>
+        <v>364</v>
       </c>
       <c r="L5" s="40">
-        <v>25258.982962475002</v>
+        <v>198</v>
       </c>
       <c r="M5" s="40">
-        <v>116417.94978422167</v>
-      </c>
-      <c r="O5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P5" s="41">
+        <v>4514</v>
+      </c>
+      <c r="N5">
+        <v>17712</v>
+      </c>
+      <c r="P5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="41">
         <f>C5</f>
-        <v>315775.85863241396</v>
-      </c>
-      <c r="Q5" s="41">
-        <f t="shared" si="0"/>
-        <v>12509.849452174283</v>
+        <v>3858</v>
       </c>
       <c r="R5" s="41">
         <f t="shared" si="0"/>
-        <v>39778.288994175316</v>
+        <v>90</v>
       </c>
       <c r="S5" s="41">
         <f t="shared" si="0"/>
-        <v>108767.47002583783</v>
+        <v>306</v>
       </c>
       <c r="T5" s="41">
         <f t="shared" si="0"/>
-        <v>97998.864931216172</v>
+        <v>986</v>
       </c>
       <c r="U5" s="41">
         <f t="shared" si="0"/>
-        <v>109850.45301999335</v>
+        <v>2138</v>
       </c>
       <c r="V5" s="41">
         <f t="shared" si="0"/>
-        <v>65620.366254890396</v>
+        <v>1602</v>
       </c>
       <c r="W5" s="41">
         <f t="shared" si="0"/>
-        <v>113589.2090666775</v>
+        <v>1326</v>
       </c>
       <c r="X5" s="41">
         <f t="shared" si="0"/>
-        <v>37104.387632676371</v>
+        <v>2330</v>
       </c>
       <c r="Y5" s="41">
         <f t="shared" si="0"/>
-        <v>25258.982962475002</v>
+        <v>364</v>
       </c>
       <c r="Z5" s="41">
         <f t="shared" si="0"/>
-        <v>116417.94978422167</v>
-      </c>
-    </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="AA5" s="41">
+        <f t="shared" si="0"/>
+        <v>4514</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="C6" s="40">
-        <v>127349.73902724685</v>
+        <v>1188</v>
       </c>
       <c r="D6" s="40">
-        <v>206.68553779535097</v>
+        <v>20</v>
       </c>
       <c r="E6" s="40">
-        <v>2992.9800274611152</v>
+        <v>86</v>
       </c>
       <c r="F6" s="40">
-        <v>9230.7439825105721</v>
+        <v>96</v>
       </c>
       <c r="G6" s="40">
-        <v>39890.973751079022</v>
+        <v>598</v>
       </c>
       <c r="H6" s="40">
-        <v>31983.864040336633</v>
+        <v>432</v>
       </c>
       <c r="I6" s="40">
-        <v>7925.5563281712903</v>
+        <v>368</v>
       </c>
       <c r="J6" s="40">
-        <v>30818.135489512057</v>
+        <v>612</v>
       </c>
       <c r="K6" s="40">
-        <v>5504.9332423887126</v>
+        <v>72</v>
       </c>
       <c r="L6" s="40">
-        <v>4530.2128170515725</v>
+        <v>20</v>
       </c>
       <c r="M6" s="40">
-        <v>44119.54007160609</v>
-      </c>
-      <c r="O6" t="s">
-        <v>14</v>
-      </c>
-      <c r="P6" s="41">
+        <v>1150</v>
+      </c>
+      <c r="N6">
+        <v>4642</v>
+      </c>
+      <c r="P6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q6" s="41">
         <f>C6</f>
-        <v>127349.73902724685</v>
-      </c>
-      <c r="Q6" s="41">
-        <f t="shared" si="0"/>
-        <v>206.68553779535097</v>
+        <v>1188</v>
       </c>
       <c r="R6" s="41">
         <f t="shared" si="0"/>
-        <v>2992.9800274611152</v>
+        <v>20</v>
       </c>
       <c r="S6" s="41">
         <f t="shared" si="0"/>
-        <v>9230.7439825105721</v>
+        <v>86</v>
       </c>
       <c r="T6" s="41">
         <f t="shared" si="0"/>
-        <v>39890.973751079022</v>
+        <v>96</v>
       </c>
       <c r="U6" s="41">
         <f t="shared" si="0"/>
-        <v>31983.864040336633</v>
+        <v>598</v>
       </c>
       <c r="V6" s="41">
         <f t="shared" si="0"/>
-        <v>7925.5563281712903</v>
+        <v>432</v>
       </c>
       <c r="W6" s="41">
         <f t="shared" si="0"/>
-        <v>30818.135489512057</v>
+        <v>368</v>
       </c>
       <c r="X6" s="41">
         <f t="shared" si="0"/>
-        <v>5504.9332423887126</v>
+        <v>612</v>
       </c>
       <c r="Y6" s="41">
         <f t="shared" si="0"/>
-        <v>4530.2128170515725</v>
+        <v>72</v>
       </c>
       <c r="Z6" s="41">
         <f t="shared" si="0"/>
-        <v>44119.54007160609</v>
-      </c>
-    </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="AA6" s="41">
+        <f t="shared" si="0"/>
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C7" s="40">
-        <v>15566.639732441907</v>
+        <v>440</v>
       </c>
       <c r="D7" s="40">
-        <v>622.63718167563036</v>
+        <v>2</v>
       </c>
       <c r="E7" s="40">
-        <v>2685.890632548128</v>
+        <v>28</v>
       </c>
       <c r="F7" s="40">
-        <v>3111.9954308458819</v>
+        <v>18</v>
       </c>
       <c r="G7" s="40">
-        <v>13482.435228174367</v>
+        <v>198</v>
       </c>
       <c r="H7" s="40">
-        <v>10480.434941002824</v>
+        <v>180</v>
       </c>
       <c r="I7" s="40">
-        <v>7620.3648267969029</v>
+        <v>176</v>
       </c>
       <c r="J7" s="40">
-        <v>7033.3335792413018</v>
+        <v>182</v>
       </c>
       <c r="K7" s="40">
-        <v>5855.4576634179175</v>
+        <v>34</v>
       </c>
       <c r="L7" s="40">
-        <v>2009.6574935658898</v>
+        <v>4</v>
       </c>
       <c r="M7" s="40">
-        <v>19925.259399560397</v>
-      </c>
-      <c r="O7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="41">
+        <v>314</v>
+      </c>
+      <c r="N7">
+        <v>1576</v>
+      </c>
+      <c r="P7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="41">
         <f>C7+C8</f>
-        <v>41041.590930967264</v>
-      </c>
-      <c r="Q7" s="41">
-        <f t="shared" ref="Q7:Z7" si="1">D7+D8</f>
-        <v>622.63718167563036</v>
+        <v>764</v>
       </c>
       <c r="R7" s="41">
-        <f t="shared" si="1"/>
-        <v>5957.7134606357959</v>
+        <f t="shared" ref="R7:AA7" si="1">D7+D8</f>
+        <v>2</v>
       </c>
       <c r="S7" s="41">
         <f t="shared" si="1"/>
-        <v>4406.9465868136558</v>
+        <v>40</v>
       </c>
       <c r="T7" s="41">
         <f t="shared" si="1"/>
-        <v>19290.333740475005</v>
+        <v>42</v>
       </c>
       <c r="U7" s="41">
         <f t="shared" si="1"/>
-        <v>14901.411891483125</v>
+        <v>306</v>
       </c>
       <c r="V7" s="41">
         <f t="shared" si="1"/>
-        <v>8761.2954181948298</v>
+        <v>286</v>
       </c>
       <c r="W7" s="41">
         <f t="shared" si="1"/>
-        <v>12931.658903017335</v>
+        <v>280</v>
       </c>
       <c r="X7" s="41">
         <f t="shared" si="1"/>
-        <v>9734.0966333659471</v>
+        <v>292</v>
       </c>
       <c r="Y7" s="41">
         <f t="shared" si="1"/>
-        <v>2033.2620212355866</v>
+        <v>60</v>
       </c>
       <c r="Z7" s="41">
         <f t="shared" si="1"/>
-        <v>19925.259399560397</v>
-      </c>
-    </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="AA7" s="41">
+        <f t="shared" si="1"/>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C8" s="42">
-        <v>25474.951198525359</v>
-      </c>
-      <c r="D8" s="1"/>
+        <v>324</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
       <c r="E8" s="42">
-        <v>3271.8228280876683</v>
+        <v>12</v>
       </c>
       <c r="F8" s="42">
-        <v>1294.9511559677737</v>
+        <v>24</v>
       </c>
       <c r="G8" s="42">
-        <v>5807.8985123006378</v>
+        <v>108</v>
       </c>
       <c r="H8" s="42">
-        <v>4420.9769504803007</v>
+        <v>106</v>
       </c>
       <c r="I8" s="42">
-        <v>1140.930591397926</v>
+        <v>104</v>
       </c>
       <c r="J8" s="42">
-        <v>5898.3253237760327</v>
+        <v>110</v>
       </c>
       <c r="K8" s="42">
-        <v>3878.6389699480301</v>
+        <v>26</v>
       </c>
       <c r="L8" s="42">
-        <v>23.604527669696733</v>
-      </c>
-      <c r="M8" s="42"/>
-      <c r="O8" t="s">
-        <v>16</v>
-      </c>
-      <c r="P8" s="41">
+        <v>4</v>
+      </c>
+      <c r="M8" s="42">
+        <v>110</v>
+      </c>
+      <c r="N8">
+        <v>928</v>
+      </c>
+      <c r="P8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="41">
         <f>C9</f>
-        <v>167632.47169059468</v>
-      </c>
-      <c r="Q8" s="41">
-        <f t="shared" ref="Q8:Z10" si="2">D9</f>
-        <v>5939.8055276514287</v>
+        <v>2654</v>
       </c>
       <c r="R8" s="41">
-        <f t="shared" si="2"/>
-        <v>26369.253498821094</v>
+        <f t="shared" ref="R8:AA10" si="2">D9</f>
+        <v>76</v>
       </c>
       <c r="S8" s="41">
         <f t="shared" si="2"/>
-        <v>70541.021851917234</v>
+        <v>136</v>
       </c>
       <c r="T8" s="41">
         <f t="shared" si="2"/>
-        <v>168215.99282123192</v>
+        <v>718</v>
       </c>
       <c r="U8" s="41">
         <f t="shared" si="2"/>
-        <v>50523.996383248486</v>
+        <v>3248</v>
       </c>
       <c r="V8" s="41">
         <f t="shared" si="2"/>
-        <v>83789.045361365555</v>
+        <v>1072</v>
       </c>
       <c r="W8" s="41">
         <f t="shared" si="2"/>
-        <v>72602.506226877158</v>
+        <v>2118</v>
       </c>
       <c r="X8" s="41">
         <f t="shared" si="2"/>
-        <v>16921.923139857205</v>
+        <v>2414</v>
       </c>
       <c r="Y8" s="41">
         <f t="shared" si="2"/>
-        <v>12555.02583805386</v>
+        <v>312</v>
       </c>
       <c r="Z8" s="41">
         <f t="shared" si="2"/>
-        <v>70335.462462791882</v>
-      </c>
-    </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="AA8" s="41">
+        <f t="shared" si="2"/>
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="40">
+        <v>2654</v>
+      </c>
+      <c r="D9" s="40">
+        <v>76</v>
+      </c>
+      <c r="E9" s="40">
+        <v>136</v>
+      </c>
+      <c r="F9" s="40">
+        <v>718</v>
+      </c>
+      <c r="G9" s="40">
+        <v>3248</v>
+      </c>
+      <c r="H9" s="40">
+        <v>1072</v>
+      </c>
+      <c r="I9" s="40">
+        <v>2118</v>
+      </c>
+      <c r="J9" s="40">
+        <v>2414</v>
+      </c>
+      <c r="K9" s="40">
+        <v>312</v>
+      </c>
+      <c r="L9" s="40">
+        <v>276</v>
+      </c>
+      <c r="M9" s="40">
+        <v>4772</v>
+      </c>
+      <c r="N9">
+        <v>17796</v>
+      </c>
+      <c r="P9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40">
-        <v>167632.47169059468</v>
-      </c>
-      <c r="D9" s="40">
-        <v>5939.8055276514287</v>
-      </c>
-      <c r="E9" s="40">
-        <v>26369.253498821094</v>
-      </c>
-      <c r="F9" s="40">
-        <v>70541.021851917234</v>
-      </c>
-      <c r="G9" s="40">
-        <v>168215.99282123192</v>
-      </c>
-      <c r="H9" s="40">
-        <v>50523.996383248486</v>
-      </c>
-      <c r="I9" s="40">
-        <v>83789.045361365555</v>
-      </c>
-      <c r="J9" s="40">
-        <v>72602.506226877158</v>
-      </c>
-      <c r="K9" s="40">
-        <v>16921.923139857205</v>
-      </c>
-      <c r="L9" s="40">
-        <v>12555.02583805386</v>
-      </c>
-      <c r="M9" s="40">
-        <v>70335.462462791882</v>
-      </c>
-      <c r="O9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P9" s="41">
+      <c r="Q9" s="41">
         <f>C10</f>
-        <v>106116.20788078338</v>
-      </c>
-      <c r="Q9" s="41">
-        <f t="shared" si="2"/>
-        <v>532.17565756143108</v>
+        <v>1230</v>
       </c>
       <c r="R9" s="41">
         <f t="shared" si="2"/>
-        <v>3017.1279235071124</v>
+        <v>8</v>
       </c>
       <c r="S9" s="41">
         <f t="shared" si="2"/>
-        <v>3173.1402228270817</v>
+        <v>48</v>
       </c>
       <c r="T9" s="41">
         <f t="shared" si="2"/>
-        <v>63516.01382013593</v>
+        <v>142</v>
       </c>
       <c r="U9" s="41">
         <f t="shared" si="2"/>
-        <v>24961.339755559951</v>
+        <v>998</v>
       </c>
       <c r="V9" s="41">
         <f t="shared" si="2"/>
-        <v>16246.579478337515</v>
+        <v>438</v>
       </c>
       <c r="W9" s="41">
         <f t="shared" si="2"/>
-        <v>40077.615246067988</v>
+        <v>680</v>
       </c>
       <c r="X9" s="41">
         <f t="shared" si="2"/>
-        <v>15172.047276505744</v>
+        <v>812</v>
       </c>
       <c r="Y9" s="41">
         <f t="shared" si="2"/>
-        <v>8585.7421304302497</v>
+        <v>120</v>
       </c>
       <c r="Z9" s="41">
         <f t="shared" si="2"/>
-        <v>8523.467316913524</v>
-      </c>
-    </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="AA9" s="41">
+        <f t="shared" si="2"/>
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="40">
+        <v>1230</v>
+      </c>
+      <c r="D10" s="40">
+        <v>8</v>
+      </c>
+      <c r="E10" s="40">
+        <v>48</v>
+      </c>
+      <c r="F10" s="40">
+        <v>142</v>
+      </c>
+      <c r="G10" s="40">
+        <v>998</v>
+      </c>
+      <c r="H10" s="40">
+        <v>438</v>
+      </c>
+      <c r="I10" s="40">
+        <v>680</v>
+      </c>
+      <c r="J10" s="40">
+        <v>812</v>
+      </c>
+      <c r="K10" s="40">
+        <v>120</v>
+      </c>
+      <c r="L10" s="40">
+        <v>48</v>
+      </c>
+      <c r="M10" s="40">
+        <v>1474</v>
+      </c>
+      <c r="N10">
+        <v>5998</v>
+      </c>
+      <c r="P10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="40">
-        <v>106116.20788078338</v>
-      </c>
-      <c r="D10" s="40">
-        <v>532.17565756143108</v>
-      </c>
-      <c r="E10" s="40">
-        <v>3017.1279235071124</v>
-      </c>
-      <c r="F10" s="40">
-        <v>3173.1402228270817</v>
-      </c>
-      <c r="G10" s="40">
-        <v>63516.01382013593</v>
-      </c>
-      <c r="H10" s="40">
-        <v>24961.339755559951</v>
-      </c>
-      <c r="I10" s="40">
-        <v>16246.579478337515</v>
-      </c>
-      <c r="J10" s="40">
-        <v>40077.615246067988</v>
-      </c>
-      <c r="K10" s="40">
-        <v>15172.047276505744</v>
-      </c>
-      <c r="L10" s="40">
-        <v>8585.7421304302497</v>
-      </c>
-      <c r="M10" s="40">
-        <v>8523.467316913524</v>
-      </c>
-      <c r="O10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P10" s="41">
+      <c r="Q10" s="41">
         <f>C11</f>
-        <v>38799.270123411319</v>
-      </c>
-      <c r="Q10" s="41">
-        <f t="shared" si="2"/>
-        <v>123.36827875714707</v>
+        <v>506</v>
       </c>
       <c r="R10" s="41">
         <f t="shared" si="2"/>
-        <v>483.80467706618981</v>
+        <v>10</v>
       </c>
       <c r="S10" s="41">
         <f t="shared" si="2"/>
-        <v>2171.1836019029624</v>
+        <v>24</v>
       </c>
       <c r="T10" s="41">
         <f t="shared" si="2"/>
-        <v>33386.705591565915</v>
+        <v>18</v>
       </c>
       <c r="U10" s="41">
         <f t="shared" si="2"/>
-        <v>2117.4029250321109</v>
+        <v>348</v>
       </c>
       <c r="V10" s="41">
         <f t="shared" si="2"/>
-        <v>14398.96363486398</v>
+        <v>80</v>
       </c>
       <c r="W10" s="41">
         <f t="shared" si="2"/>
-        <v>8172.1764349093455</v>
+        <v>218</v>
       </c>
       <c r="X10" s="41">
         <f t="shared" si="2"/>
-        <v>438.50805913442167</v>
+        <v>204</v>
       </c>
       <c r="Y10" s="41">
         <f t="shared" si="2"/>
-        <v>101.14622555860629</v>
+        <v>36</v>
       </c>
       <c r="Z10" s="41">
         <f t="shared" si="2"/>
-        <v>5212.4452288403045</v>
-      </c>
-    </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="AA10" s="41">
+        <f t="shared" si="2"/>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="40">
+        <v>506</v>
+      </c>
+      <c r="D11" s="40">
+        <v>10</v>
+      </c>
+      <c r="E11" s="40">
+        <v>24</v>
+      </c>
+      <c r="F11" s="40">
         <v>18</v>
       </c>
-      <c r="C11" s="40">
-        <v>38799.270123411319</v>
-      </c>
-      <c r="D11" s="40">
-        <v>123.36827875714707</v>
-      </c>
-      <c r="E11" s="40">
-        <v>483.80467706618981</v>
-      </c>
-      <c r="F11" s="40">
-        <v>2171.1836019029624</v>
-      </c>
       <c r="G11" s="40">
-        <v>33386.705591565915</v>
+        <v>348</v>
       </c>
       <c r="H11" s="40">
-        <v>2117.4029250321109</v>
+        <v>80</v>
       </c>
       <c r="I11" s="40">
-        <v>14398.96363486398</v>
+        <v>218</v>
       </c>
       <c r="J11" s="40">
-        <v>8172.1764349093455</v>
+        <v>204</v>
       </c>
       <c r="K11" s="40">
-        <v>438.50805913442167</v>
+        <v>36</v>
       </c>
       <c r="L11" s="40">
-        <v>101.14622555860629</v>
+        <v>14</v>
       </c>
       <c r="M11" s="40">
-        <v>5212.4452288403045</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" s="41">
+        <v>528</v>
+      </c>
+      <c r="N11">
+        <v>1986</v>
+      </c>
+      <c r="P11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q11" s="41">
         <f>C12+C13</f>
-        <v>21627.879098558173</v>
-      </c>
-      <c r="Q11" s="41">
-        <f t="shared" ref="Q11:Z11" si="3">D12+D13</f>
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="R11" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="R11:AA11" si="3">D12+D13</f>
         <v>0</v>
       </c>
       <c r="S11" s="41">
         <f t="shared" si="3"/>
-        <v>147.96679051086124</v>
+        <v>14</v>
       </c>
       <c r="T11" s="41">
         <f t="shared" si="3"/>
-        <v>3481.5143359670674</v>
+        <v>18</v>
       </c>
       <c r="U11" s="41">
         <f t="shared" si="3"/>
-        <v>6668.0421022015071</v>
+        <v>180</v>
       </c>
       <c r="V11" s="41">
         <f t="shared" si="3"/>
-        <v>12498.793793429744</v>
+        <v>114</v>
       </c>
       <c r="W11" s="41">
         <f t="shared" si="3"/>
-        <v>2900.1928711500959</v>
+        <v>158</v>
       </c>
       <c r="X11" s="41">
         <f t="shared" si="3"/>
-        <v>508.67491477708342</v>
+        <v>118</v>
       </c>
       <c r="Y11" s="41">
         <f t="shared" si="3"/>
-        <v>1355.8476969232061</v>
+        <v>12</v>
       </c>
       <c r="Z11" s="41">
         <f t="shared" si="3"/>
-        <v>209.50885841624745</v>
-      </c>
-    </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="41">
+        <f t="shared" si="3"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="40">
+        <v>144</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="40">
+        <v>10</v>
+      </c>
+      <c r="F12" s="40">
+        <v>16</v>
+      </c>
+      <c r="G12" s="40">
+        <v>122</v>
+      </c>
+      <c r="H12" s="40">
+        <v>82</v>
+      </c>
+      <c r="I12" s="40">
+        <v>82</v>
+      </c>
+      <c r="J12" s="40">
+        <v>64</v>
+      </c>
+      <c r="K12" s="40">
+        <v>6</v>
+      </c>
+      <c r="L12" s="40">
+        <v>2</v>
+      </c>
+      <c r="M12" s="40">
+        <v>108</v>
+      </c>
+      <c r="N12">
+        <v>636</v>
+      </c>
+      <c r="P12" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="40">
-        <v>6568.4863426603188</v>
-      </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40">
-        <v>96.411068929855773</v>
-      </c>
-      <c r="G12" s="40">
-        <v>2501.3596230932471</v>
-      </c>
-      <c r="H12" s="40">
-        <v>4966.7332938480613</v>
-      </c>
-      <c r="I12" s="40">
-        <v>7092.2219740165037</v>
-      </c>
-      <c r="J12" s="40">
-        <v>707.29728903081127</v>
-      </c>
-      <c r="K12" s="40">
-        <v>102.3500664298307</v>
-      </c>
-      <c r="L12" s="40">
-        <v>1300.5772253607934</v>
-      </c>
-      <c r="M12" s="40">
-        <v>209.50885841624745</v>
-      </c>
-      <c r="O12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P12" s="41">
+      <c r="Q12" s="41">
         <f>C14</f>
-        <v>42826.998782305265</v>
-      </c>
-      <c r="Q12" s="41">
-        <f t="shared" ref="Q12:Z12" si="4">D14</f>
-        <v>1073.1632013523581</v>
+        <v>1022</v>
       </c>
       <c r="R12" s="41">
-        <f t="shared" si="4"/>
-        <v>2853.5560307949795</v>
+        <f t="shared" ref="R12:AA12" si="4">D14</f>
+        <v>12</v>
       </c>
       <c r="S12" s="41">
         <f t="shared" si="4"/>
-        <v>16192.708078604852</v>
+        <v>22</v>
       </c>
       <c r="T12" s="41">
         <f t="shared" si="4"/>
-        <v>59830.35238411164</v>
+        <v>168</v>
       </c>
       <c r="U12" s="41">
         <f t="shared" si="4"/>
-        <v>14660.393348963778</v>
+        <v>1262</v>
       </c>
       <c r="V12" s="41">
         <f t="shared" si="4"/>
-        <v>28669.626996565799</v>
+        <v>402</v>
       </c>
       <c r="W12" s="41">
         <f t="shared" si="4"/>
-        <v>45086.899356740221</v>
+        <v>796</v>
       </c>
       <c r="X12" s="41">
         <f t="shared" si="4"/>
-        <v>14523.796280744618</v>
+        <v>1272</v>
       </c>
       <c r="Y12" s="41">
         <f t="shared" si="4"/>
-        <v>3698.9734499412752</v>
+        <v>158</v>
       </c>
       <c r="Z12" s="41">
         <f t="shared" si="4"/>
-        <v>19669.689423758082</v>
-      </c>
-    </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="AA12" s="41">
+        <f t="shared" si="4"/>
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="42">
+        <v>146</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="42">
+        <v>4</v>
+      </c>
+      <c r="F13" s="42">
+        <v>2</v>
+      </c>
+      <c r="G13" s="42">
+        <v>58</v>
+      </c>
+      <c r="H13" s="42">
+        <v>32</v>
+      </c>
+      <c r="I13" s="42">
+        <v>76</v>
+      </c>
+      <c r="J13" s="42">
         <v>54</v>
       </c>
-      <c r="C13" s="42">
-        <v>15059.392755897852</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42">
-        <v>51.555721581005464</v>
-      </c>
-      <c r="G13" s="42">
-        <v>980.15471287382002</v>
-      </c>
-      <c r="H13" s="42">
-        <v>1701.3088083534453</v>
-      </c>
-      <c r="I13" s="42">
-        <v>5406.5718194132414</v>
-      </c>
-      <c r="J13" s="42">
-        <v>2192.8955821192844</v>
-      </c>
       <c r="K13" s="42">
-        <v>406.32484834725273</v>
+        <v>6</v>
       </c>
       <c r="L13" s="42">
-        <v>55.270471562412752</v>
-      </c>
-      <c r="M13" s="42"/>
-      <c r="O13" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" s="41">
+        <v>4</v>
+      </c>
+      <c r="M13" s="42">
+        <v>60</v>
+      </c>
+      <c r="N13">
+        <v>442</v>
+      </c>
+      <c r="P13" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="41">
         <f>C15</f>
-        <v>22852.400906529012</v>
-      </c>
-      <c r="Q13" s="41">
-        <f t="shared" ref="Q13:Z13" si="5">D15</f>
-        <v>8056.0166205987771</v>
+        <v>472</v>
       </c>
       <c r="R13" s="41">
-        <f t="shared" si="5"/>
-        <v>240.04778715331315</v>
+        <f t="shared" ref="R13:AA13" si="5">D15</f>
+        <v>10</v>
       </c>
       <c r="S13" s="41">
         <f t="shared" si="5"/>
-        <v>1177.2766539057095</v>
+        <v>14</v>
       </c>
       <c r="T13" s="41">
         <f t="shared" si="5"/>
-        <v>37859.50923913539</v>
+        <v>50</v>
       </c>
       <c r="U13" s="41">
         <f t="shared" si="5"/>
-        <v>5016.4028925832881</v>
+        <v>506</v>
       </c>
       <c r="V13" s="41">
         <f t="shared" si="5"/>
-        <v>12806.685587132732</v>
+        <v>134</v>
       </c>
       <c r="W13" s="41">
         <f t="shared" si="5"/>
-        <v>16225.24210738745</v>
+        <v>318</v>
       </c>
       <c r="X13" s="41">
         <f t="shared" si="5"/>
-        <v>5807.1093154851969</v>
+        <v>330</v>
       </c>
       <c r="Y13" s="41">
         <f t="shared" si="5"/>
-        <v>2103.2344747391844</v>
+        <v>32</v>
       </c>
       <c r="Z13" s="41">
         <f t="shared" si="5"/>
-        <v>14011.25300764967</v>
-      </c>
-    </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="AA13" s="41">
+        <f t="shared" si="5"/>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C14" s="40">
-        <v>42826.998782305265</v>
+        <v>1022</v>
       </c>
       <c r="D14" s="40">
-        <v>1073.1632013523581</v>
+        <v>12</v>
       </c>
       <c r="E14" s="40">
-        <v>2853.5560307949795</v>
+        <v>22</v>
       </c>
       <c r="F14" s="40">
-        <v>16192.708078604852</v>
+        <v>168</v>
       </c>
       <c r="G14" s="40">
-        <v>59830.35238411164</v>
+        <v>1262</v>
       </c>
       <c r="H14" s="40">
-        <v>14660.393348963778</v>
+        <v>402</v>
       </c>
       <c r="I14" s="40">
-        <v>28669.626996565799</v>
+        <v>796</v>
       </c>
       <c r="J14" s="40">
-        <v>45086.899356740221</v>
+        <v>1272</v>
       </c>
       <c r="K14" s="40">
-        <v>14523.796280744618</v>
+        <v>158</v>
       </c>
       <c r="L14" s="40">
-        <v>3698.9734499412752</v>
+        <v>64</v>
       </c>
       <c r="M14" s="40">
-        <v>19669.689423758082</v>
-      </c>
-      <c r="O14" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="41">
+        <v>1792</v>
+      </c>
+      <c r="N14">
+        <v>6970</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="41">
         <f>C16</f>
-        <v>15173.922543247952</v>
-      </c>
-      <c r="Q14" s="41">
-        <f t="shared" ref="Q14:Z14" si="6">D16</f>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="R14" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="R14:AA14" si="6">D16</f>
         <v>0</v>
       </c>
       <c r="S14" s="41">
         <f t="shared" si="6"/>
-        <v>572.09215660538655</v>
+        <v>8</v>
       </c>
       <c r="T14" s="41">
         <f t="shared" si="6"/>
-        <v>9265.4531419888881</v>
+        <v>6</v>
       </c>
       <c r="U14" s="41">
         <f t="shared" si="6"/>
-        <v>1809.3554287191737</v>
+        <v>162</v>
       </c>
       <c r="V14" s="41">
         <f t="shared" si="6"/>
-        <v>15153.585125974105</v>
+        <v>40</v>
       </c>
       <c r="W14" s="41">
         <f t="shared" si="6"/>
-        <v>2259.4064615133407</v>
+        <v>106</v>
       </c>
       <c r="X14" s="41">
         <f t="shared" si="6"/>
-        <v>1934.2188459947079</v>
+        <v>102</v>
       </c>
       <c r="Y14" s="41">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z14" s="41">
         <f t="shared" si="6"/>
-        <v>1596.7852418229681</v>
-      </c>
-    </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="41">
+        <f t="shared" si="6"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="C15" s="40">
-        <v>22852.400906529012</v>
+        <v>472</v>
       </c>
       <c r="D15" s="40">
-        <v>8056.0166205987771</v>
+        <v>10</v>
       </c>
       <c r="E15" s="40">
-        <v>240.04778715331315</v>
+        <v>14</v>
       </c>
       <c r="F15" s="40">
-        <v>1177.2766539057095</v>
+        <v>50</v>
       </c>
       <c r="G15" s="40">
-        <v>37859.50923913539</v>
+        <v>506</v>
       </c>
       <c r="H15" s="40">
-        <v>5016.4028925832881</v>
+        <v>134</v>
       </c>
       <c r="I15" s="40">
-        <v>12806.685587132732</v>
+        <v>318</v>
       </c>
       <c r="J15" s="40">
-        <v>16225.24210738745</v>
+        <v>330</v>
       </c>
       <c r="K15" s="40">
-        <v>5807.1093154851969</v>
+        <v>32</v>
       </c>
       <c r="L15" s="40">
-        <v>2103.2344747391844</v>
+        <v>14</v>
       </c>
       <c r="M15" s="40">
-        <v>14011.25300764967</v>
-      </c>
-      <c r="O15" t="s">
-        <v>23</v>
-      </c>
-      <c r="P15" s="41">
+        <v>624</v>
+      </c>
+      <c r="N15">
+        <v>2504</v>
+      </c>
+      <c r="P15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="41">
         <f>C17+C18</f>
-        <v>23723.806239734909</v>
-      </c>
-      <c r="Q15" s="41">
-        <f t="shared" ref="Q15:Z15" si="7">D17+D18</f>
-        <v>29.080196329243751</v>
+        <v>150</v>
       </c>
       <c r="R15" s="41">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" ref="R15:AA15" si="7">D17+D18</f>
+        <v>2</v>
       </c>
       <c r="S15" s="41">
         <f t="shared" si="7"/>
@@ -12743,630 +12779,762 @@
       </c>
       <c r="T15" s="41">
         <f t="shared" si="7"/>
-        <v>4100.5016279280508</v>
+        <v>4</v>
       </c>
       <c r="U15" s="41">
         <f t="shared" si="7"/>
-        <v>155.21592643606715</v>
+        <v>118</v>
       </c>
       <c r="V15" s="41">
         <f t="shared" si="7"/>
-        <v>12633.39366140982</v>
+        <v>22</v>
       </c>
       <c r="W15" s="41">
         <f t="shared" si="7"/>
-        <v>3225.6594773983147</v>
+        <v>86</v>
       </c>
       <c r="X15" s="41">
         <f t="shared" si="7"/>
-        <v>145.05566638992408</v>
+        <v>52</v>
       </c>
       <c r="Y15" s="41">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z15" s="41">
         <f t="shared" si="7"/>
-        <v>2442.6842184043094</v>
-      </c>
-    </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="AA15" s="41">
+        <f t="shared" si="7"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="C16" s="40">
-        <v>15173.922543247952</v>
-      </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
+        <v>218</v>
+      </c>
+      <c r="D16" s="40">
+        <v>0</v>
+      </c>
+      <c r="E16" s="40">
+        <v>8</v>
+      </c>
       <c r="F16" s="40">
-        <v>572.09215660538655</v>
+        <v>6</v>
       </c>
       <c r="G16" s="40">
-        <v>9265.4531419888881</v>
+        <v>162</v>
       </c>
       <c r="H16" s="40">
-        <v>1809.3554287191737</v>
+        <v>40</v>
       </c>
       <c r="I16" s="40">
-        <v>15153.585125974105</v>
+        <v>106</v>
       </c>
       <c r="J16" s="40">
-        <v>2259.4064615133407</v>
+        <v>102</v>
       </c>
       <c r="K16" s="40">
-        <v>1934.2188459947079</v>
-      </c>
-      <c r="L16" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="L16" s="40">
+        <v>2</v>
+      </c>
       <c r="M16" s="40">
-        <v>1596.7852418229681</v>
-      </c>
-      <c r="O16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P16" s="41">
+        <v>144</v>
+      </c>
+      <c r="N16">
+        <v>798</v>
+      </c>
+      <c r="P16" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="41">
         <f>C19+C24</f>
-        <v>36832.568496782624</v>
-      </c>
-      <c r="Q16" s="41">
-        <f t="shared" ref="Q16:Z16" si="8">D19+D24</f>
-        <v>408.82906881069198</v>
+        <v>626</v>
       </c>
       <c r="R16" s="41">
-        <f t="shared" si="8"/>
-        <v>67.646139532598127</v>
+        <f t="shared" ref="R16:AA16" si="8">D19+D24</f>
+        <v>14</v>
       </c>
       <c r="S16" s="41">
         <f t="shared" si="8"/>
-        <v>4576.320784945744</v>
+        <v>8</v>
       </c>
       <c r="T16" s="41">
         <f t="shared" si="8"/>
-        <v>58038.303389785586</v>
+        <v>62</v>
       </c>
       <c r="U16" s="41">
         <f t="shared" si="8"/>
-        <v>9475.9688005437529</v>
+        <v>1024</v>
       </c>
       <c r="V16" s="41">
         <f t="shared" si="8"/>
-        <v>16377.122775893489</v>
+        <v>236</v>
       </c>
       <c r="W16" s="41">
         <f t="shared" si="8"/>
-        <v>34176.386555284036</v>
+        <v>748</v>
       </c>
       <c r="X16" s="41">
         <f t="shared" si="8"/>
-        <v>3726.019126875748</v>
+        <v>686</v>
       </c>
       <c r="Y16" s="41">
         <f t="shared" si="8"/>
-        <v>2445.0694472386958</v>
+        <v>112</v>
       </c>
       <c r="Z16" s="41">
         <f t="shared" si="8"/>
-        <v>7901.9660427044219</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="AA16" s="41">
+        <f t="shared" si="8"/>
+        <v>798</v>
+      </c>
+    </row>
+    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="C17" s="40">
-        <v>11128.882166279645</v>
-      </c>
-      <c r="F17" s="40"/>
+        <v>86</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" s="40">
+        <v>4</v>
+      </c>
       <c r="G17" s="40">
-        <v>2102.8161762121258</v>
+        <v>62</v>
       </c>
       <c r="H17" s="40">
-        <v>75.568335824769221</v>
+        <v>6</v>
       </c>
       <c r="I17" s="40">
-        <v>2333.1597461812789</v>
+        <v>42</v>
       </c>
       <c r="J17" s="40">
-        <v>2898.4407232463568</v>
+        <v>38</v>
       </c>
       <c r="K17" s="40">
-        <v>13.162244927052551</v>
-      </c>
-      <c r="L17" s="40"/>
+        <v>4</v>
+      </c>
+      <c r="L17" s="40">
+        <v>0</v>
+      </c>
       <c r="M17" s="40">
-        <v>2442.6842184043094</v>
-      </c>
-      <c r="O17" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="41">
+        <v>34</v>
+      </c>
+      <c r="N17">
+        <v>276</v>
+      </c>
+      <c r="P17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="41">
         <f>C20+C25</f>
-        <v>33253.557269783269</v>
-      </c>
-      <c r="Q17" s="41">
-        <f t="shared" ref="Q17:Z17" si="9">D20+D25</f>
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="R17" s="41">
-        <f t="shared" si="9"/>
-        <v>172.69125107398773</v>
+        <f t="shared" ref="R17:AA17" si="9">D20+D25</f>
+        <v>2</v>
       </c>
       <c r="S17" s="41">
         <f t="shared" si="9"/>
-        <v>116.98119419120076</v>
+        <v>4</v>
       </c>
       <c r="T17" s="41">
         <f t="shared" si="9"/>
-        <v>15740.145805572667</v>
+        <v>14</v>
       </c>
       <c r="U17" s="41">
         <f t="shared" si="9"/>
-        <v>4272.2371743394579</v>
+        <v>372</v>
       </c>
       <c r="V17" s="41">
         <f t="shared" si="9"/>
-        <v>9734.7504697612931</v>
+        <v>72</v>
       </c>
       <c r="W17" s="41">
         <f t="shared" si="9"/>
-        <v>2690.7219342204935</v>
+        <v>312</v>
       </c>
       <c r="X17" s="41">
         <f t="shared" si="9"/>
-        <v>325.60741741873699</v>
+        <v>210</v>
       </c>
       <c r="Y17" s="41">
         <f t="shared" si="9"/>
-        <v>414.52628222720267</v>
+        <v>36</v>
       </c>
       <c r="Z17" s="41">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="AA17" s="41">
+        <f t="shared" si="9"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C18" s="42">
-        <v>12594.924073455264</v>
+        <v>64</v>
       </c>
       <c r="D18" s="42">
-        <v>29.080196329243751</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="42"/>
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="42">
+        <v>0</v>
+      </c>
       <c r="G18" s="42">
-        <v>1997.6854517159247</v>
+        <v>56</v>
       </c>
       <c r="H18" s="42">
-        <v>79.647590611297943</v>
+        <v>16</v>
       </c>
       <c r="I18" s="42">
-        <v>10300.23391522854</v>
+        <v>44</v>
       </c>
       <c r="J18" s="42">
-        <v>327.21875415195774</v>
+        <v>14</v>
       </c>
       <c r="K18" s="42">
-        <v>131.89342146287154</v>
-      </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="42"/>
-      <c r="O18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
+        <v>2</v>
+      </c>
+      <c r="M18" s="42">
         <v>26</v>
       </c>
-      <c r="P18" s="41">
+      <c r="N18">
+        <v>232</v>
+      </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="41">
         <f>C21+C26</f>
-        <v>15408.062173415274</v>
-      </c>
-      <c r="Q18" s="41">
-        <f t="shared" ref="Q18:Z18" si="10">D21+D26</f>
-        <v>7.0332117940253411</v>
+        <v>198</v>
       </c>
       <c r="R18" s="41">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" ref="R18:AA18" si="10">D21+D26</f>
+        <v>4</v>
       </c>
       <c r="S18" s="41">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T18" s="41">
         <f t="shared" si="10"/>
-        <v>3960.4025989131887</v>
+        <v>10</v>
       </c>
       <c r="U18" s="41">
         <f t="shared" si="10"/>
-        <v>2858.8122652294701</v>
+        <v>152</v>
       </c>
       <c r="V18" s="41">
         <f t="shared" si="10"/>
-        <v>3590.247026549062</v>
+        <v>42</v>
       </c>
       <c r="W18" s="41">
         <f t="shared" si="10"/>
-        <v>3790.0112570301171</v>
+        <v>108</v>
       </c>
       <c r="X18" s="41">
         <f t="shared" si="10"/>
-        <v>252.85205536577362</v>
+        <v>104</v>
       </c>
       <c r="Y18" s="41">
         <f t="shared" si="10"/>
-        <v>828.3346820397868</v>
+        <v>26</v>
       </c>
       <c r="Z18" s="41">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="AA18" s="41">
+        <f t="shared" si="10"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="C19" s="40">
-        <v>20632.582033404411</v>
+        <v>296</v>
       </c>
       <c r="D19" s="40">
-        <v>408.82906881069198</v>
-      </c>
-      <c r="E19" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="E19" s="40">
+        <v>6</v>
+      </c>
       <c r="F19" s="40">
-        <v>4142.0014070482657</v>
+        <v>36</v>
       </c>
       <c r="G19" s="40">
-        <v>43166.580158521421</v>
+        <v>582</v>
       </c>
       <c r="H19" s="40">
-        <v>5658.5427001945081</v>
+        <v>132</v>
       </c>
       <c r="I19" s="40">
-        <v>6286.4132837665729</v>
+        <v>420</v>
       </c>
       <c r="J19" s="40">
-        <v>21786.322207325407</v>
+        <v>376</v>
       </c>
       <c r="K19" s="40">
-        <v>1186.3294776207749</v>
+        <v>54</v>
       </c>
       <c r="L19" s="40">
-        <v>1593.1302375292121</v>
+        <v>20</v>
       </c>
       <c r="M19" s="40">
-        <v>6984.0913508478498</v>
-      </c>
-      <c r="O19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="41">
+        <v>522</v>
+      </c>
+      <c r="N19">
+        <v>2452</v>
+      </c>
+      <c r="P19" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="41">
         <f>C22+C23+C27+C28</f>
-        <v>9490.2512292787542</v>
-      </c>
-      <c r="Q19" s="41">
-        <f t="shared" ref="Q19:Z19" si="11">D22+D23+D27+D28</f>
-        <v>512.31483610226019</v>
+        <v>154</v>
       </c>
       <c r="R19" s="41">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" ref="R19:AA19" si="11">D22+D23+D27+D28</f>
+        <v>4</v>
       </c>
       <c r="S19" s="41">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T19" s="41">
         <f t="shared" si="11"/>
-        <v>3557.818822527991</v>
+        <v>6</v>
       </c>
       <c r="U19" s="41">
         <f t="shared" si="11"/>
-        <v>988.45778493702903</v>
+        <v>100</v>
       </c>
       <c r="V19" s="41">
         <f t="shared" si="11"/>
-        <v>4063.667303217534</v>
+        <v>42</v>
       </c>
       <c r="W19" s="41">
         <f t="shared" si="11"/>
-        <v>2717.8980833374176</v>
+        <v>98</v>
       </c>
       <c r="X19" s="41">
         <f t="shared" si="11"/>
-        <v>633.98507108513695</v>
+        <v>56</v>
       </c>
       <c r="Y19" s="41">
         <f t="shared" si="11"/>
-        <v>69.305911911520766</v>
+        <v>18</v>
       </c>
       <c r="Z19" s="41">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="AA19" s="41">
+        <f t="shared" si="11"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="C20" s="40">
-        <v>18195.484660710743</v>
-      </c>
-      <c r="D20" s="40"/>
+        <v>164</v>
+      </c>
+      <c r="D20" s="40">
+        <v>2</v>
+      </c>
       <c r="E20" s="40">
-        <v>172.69125107398773</v>
+        <v>4</v>
       </c>
       <c r="F20" s="40">
-        <v>116.98119419120076</v>
+        <v>6</v>
       </c>
       <c r="G20" s="40">
-        <v>10350.280557132945</v>
+        <v>186</v>
       </c>
       <c r="H20" s="40">
-        <v>1821.8271211249612</v>
+        <v>30</v>
       </c>
       <c r="I20" s="40">
-        <v>3654.7444093747404</v>
+        <v>142</v>
       </c>
       <c r="J20" s="40">
-        <v>1457.6655354597747</v>
+        <v>104</v>
       </c>
       <c r="K20" s="40">
-        <v>88.567819356222458</v>
+        <v>12</v>
       </c>
       <c r="L20" s="40">
-        <v>372.21969743910233</v>
-      </c>
-      <c r="M20" s="40"/>
-    </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="M20" s="40">
+        <v>274</v>
+      </c>
+      <c r="N20">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="40">
+        <v>104</v>
+      </c>
+      <c r="D21" s="40">
+        <v>2</v>
+      </c>
+      <c r="E21" s="40">
+        <v>2</v>
+      </c>
+      <c r="F21" s="40">
+        <v>10</v>
+      </c>
+      <c r="G21" s="40">
+        <v>76</v>
+      </c>
+      <c r="H21" s="40">
+        <v>22</v>
+      </c>
+      <c r="I21" s="40">
+        <v>62</v>
+      </c>
+      <c r="J21" s="40">
+        <v>62</v>
+      </c>
+      <c r="K21" s="40">
+        <v>18</v>
+      </c>
+      <c r="L21" s="40">
+        <v>4</v>
+      </c>
+      <c r="M21" s="40">
+        <v>8</v>
+      </c>
+      <c r="N21">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="40">
+        <v>28</v>
+      </c>
+      <c r="D22" s="40">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" s="40">
+        <v>18</v>
+      </c>
+      <c r="H22" s="40">
+        <v>14</v>
+      </c>
+      <c r="I22" s="40">
+        <v>14</v>
+      </c>
+      <c r="J22" s="40">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" s="40">
+        <v>24</v>
+      </c>
+      <c r="N22">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="42">
+        <v>30</v>
+      </c>
+      <c r="D23" s="42">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="42">
+        <v>2</v>
+      </c>
+      <c r="G23" s="42">
+        <v>30</v>
+      </c>
+      <c r="H23" s="42">
+        <v>6</v>
+      </c>
+      <c r="I23" s="42">
+        <v>30</v>
+      </c>
+      <c r="J23" s="42">
+        <v>12</v>
+      </c>
+      <c r="K23" s="42">
+        <v>4</v>
+      </c>
+      <c r="L23" s="42">
+        <v>2</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="42">
+        <v>330</v>
+      </c>
+      <c r="D24" s="42">
+        <v>6</v>
+      </c>
+      <c r="E24" s="42">
+        <v>2</v>
+      </c>
+      <c r="F24" s="42">
         <v>26</v>
       </c>
-      <c r="C21" s="40">
-        <v>2418.3467949899664</v>
-      </c>
-      <c r="D21" s="40">
-        <v>7.0332117940253411</v>
-      </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40">
-        <v>1777.5238782639997</v>
-      </c>
-      <c r="H21" s="40">
-        <v>1050.5089715450658</v>
-      </c>
-      <c r="I21" s="40">
-        <v>2098.935016646471</v>
-      </c>
-      <c r="J21" s="40">
-        <v>1310.012798125432</v>
-      </c>
-      <c r="K21" s="40">
-        <v>211.5265407838512</v>
-      </c>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-    </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="40">
-        <v>178.32885398780599</v>
-      </c>
-      <c r="D22" s="40">
-        <v>29.080196329243751</v>
-      </c>
-      <c r="G22" s="40">
-        <v>1755.2655064243309</v>
-      </c>
-      <c r="H22" s="40">
-        <v>907.58946631068841</v>
-      </c>
-      <c r="I22" s="40">
-        <v>156.54567657427734</v>
-      </c>
-      <c r="J22" s="40">
-        <v>2118.6389659216366</v>
-      </c>
-      <c r="M22" s="40"/>
-    </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="G24" s="42">
+        <v>442</v>
+      </c>
+      <c r="H24" s="42">
+        <v>104</v>
+      </c>
+      <c r="I24" s="42">
+        <v>328</v>
+      </c>
+      <c r="J24" s="42">
+        <v>310</v>
+      </c>
+      <c r="K24" s="42">
+        <v>58</v>
+      </c>
+      <c r="L24" s="42">
+        <v>10</v>
+      </c>
+      <c r="M24" s="42">
+        <v>276</v>
+      </c>
+      <c r="N24">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="42">
+        <v>174</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="42">
+        <v>0</v>
+      </c>
+      <c r="F25" s="42">
+        <v>8</v>
+      </c>
+      <c r="G25" s="42">
+        <v>186</v>
+      </c>
+      <c r="H25" s="42">
+        <v>42</v>
+      </c>
+      <c r="I25" s="42">
+        <v>170</v>
+      </c>
+      <c r="J25" s="42">
+        <v>106</v>
+      </c>
+      <c r="K25" s="42">
+        <v>24</v>
+      </c>
+      <c r="L25" s="42">
+        <v>8</v>
+      </c>
+      <c r="M25" s="42">
+        <v>116</v>
+      </c>
+      <c r="N25">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="42">
+        <v>94</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="42">
+        <v>76</v>
+      </c>
+      <c r="H26" s="42">
+        <v>20</v>
+      </c>
+      <c r="I26" s="42">
+        <v>46</v>
+      </c>
+      <c r="J26" s="42">
+        <v>42</v>
+      </c>
+      <c r="K26" s="42">
+        <v>8</v>
+      </c>
+      <c r="L26" s="42">
+        <v>6</v>
+      </c>
+      <c r="M26" s="42">
+        <v>24</v>
+      </c>
+      <c r="N26">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="42">
+        <v>40</v>
+      </c>
+      <c r="D27" s="42">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="42">
+        <v>26</v>
+      </c>
+      <c r="H27" s="42">
+        <v>8</v>
+      </c>
+      <c r="I27" s="42">
+        <v>32</v>
+      </c>
+      <c r="J27" s="42">
+        <v>16</v>
+      </c>
+      <c r="K27" s="42">
+        <v>6</v>
+      </c>
+      <c r="L27" s="1">
+        <v>4</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="42">
         <v>56</v>
       </c>
-      <c r="C23" s="42">
-        <v>1668.63177660064</v>
-      </c>
-      <c r="D23" s="42">
-        <v>12.974248138455877</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42">
-        <v>21.150601693344203</v>
-      </c>
-      <c r="H23" s="42">
-        <v>50.794807452924069</v>
-      </c>
-      <c r="I23" s="42">
-        <v>1767.2698930098345</v>
-      </c>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42">
-        <v>69.305911911520766</v>
-      </c>
-      <c r="M23" s="1"/>
-    </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="42">
-        <v>16199.986463378213</v>
-      </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42">
-        <v>67.646139532598127</v>
-      </c>
-      <c r="F24" s="42">
-        <v>434.31937789747838</v>
-      </c>
-      <c r="G24" s="42">
-        <v>14871.723231264163</v>
-      </c>
-      <c r="H24" s="42">
-        <v>3817.4261003492452</v>
-      </c>
-      <c r="I24" s="42">
-        <v>10090.709492126916</v>
-      </c>
-      <c r="J24" s="42">
-        <v>12390.064347958627</v>
-      </c>
-      <c r="K24" s="42">
-        <v>2539.6896492549731</v>
-      </c>
-      <c r="L24" s="42">
-        <v>851.93920970948352</v>
-      </c>
-      <c r="M24" s="42">
-        <v>917.87469185657199</v>
-      </c>
-    </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="42">
-        <v>15058.072609072527</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42">
-        <v>5389.8652484397226</v>
-      </c>
-      <c r="H25" s="42">
-        <v>2450.4100532144962</v>
-      </c>
-      <c r="I25" s="42">
-        <v>6080.0060603865531</v>
-      </c>
-      <c r="J25" s="42">
-        <v>1233.0563987607186</v>
-      </c>
-      <c r="K25" s="42">
-        <v>237.03959806251453</v>
-      </c>
-      <c r="L25" s="42">
-        <v>42.306584788100359</v>
-      </c>
-      <c r="M25" s="42"/>
-    </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="42">
-        <v>12989.715378425308</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="42">
-        <v>2182.8787206491888</v>
-      </c>
-      <c r="H26" s="42">
-        <v>1808.3032936844043</v>
-      </c>
-      <c r="I26" s="42">
-        <v>1491.3120099025907</v>
-      </c>
-      <c r="J26" s="42">
-        <v>2479.9984589046853</v>
-      </c>
-      <c r="K26" s="42">
-        <v>41.325514581922413</v>
-      </c>
-      <c r="L26" s="42">
-        <v>828.3346820397868</v>
-      </c>
-      <c r="M26" s="42"/>
-    </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="42">
-        <v>765.92383367125706</v>
-      </c>
-      <c r="D27" s="42">
-        <v>470.26039163456062</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="42">
-        <v>1507.3533500799108</v>
-      </c>
-      <c r="H27" s="42">
-        <v>30.073511173416584</v>
-      </c>
-      <c r="I27" s="42">
-        <v>2055.8534909905293</v>
-      </c>
-      <c r="J27" s="42">
-        <v>502.67834369599234</v>
-      </c>
-      <c r="K27" s="42">
-        <v>150.90389354209182</v>
-      </c>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-    </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="42">
-        <v>6877.3667650190509</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
       <c r="G28" s="42">
-        <v>274.04936433040541</v>
-      </c>
-      <c r="H28" s="42"/>
+        <v>26</v>
+      </c>
+      <c r="H28" s="42">
+        <v>14</v>
+      </c>
       <c r="I28" s="42">
-        <v>83.998242642892734</v>
+        <v>22</v>
       </c>
       <c r="J28" s="42">
-        <v>96.580773719788681</v>
+        <v>16</v>
       </c>
       <c r="K28" s="42">
-        <v>483.08117754304516</v>
-      </c>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-    </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="L28" s="42">
+        <v>2</v>
+      </c>
+      <c r="M28" s="42">
+        <v>26</v>
+      </c>
+      <c r="N28">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-    </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B31" s="63"/>
       <c r="C31" s="41"/>
       <c r="D31" s="41"/>
@@ -13379,7 +13547,6 @@
       <c r="K31" s="41"/>
       <c r="L31" s="41"/>
       <c r="M31" s="41"/>
-      <c r="O31" s="63"/>
       <c r="P31" s="63"/>
       <c r="Q31" s="63"/>
       <c r="R31" s="63"/>
@@ -13391,8 +13558,9 @@
       <c r="X31" s="63"/>
       <c r="Y31" s="63"/>
       <c r="Z31" s="63"/>
-    </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA31" s="63"/>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" s="63"/>
       <c r="C32" s="41"/>
       <c r="D32" s="41"/>
@@ -13405,7 +13573,6 @@
       <c r="K32" s="41"/>
       <c r="L32" s="41"/>
       <c r="M32" s="41"/>
-      <c r="O32" s="63"/>
       <c r="P32" s="63"/>
       <c r="Q32" s="63"/>
       <c r="R32" s="63"/>
@@ -13417,8 +13584,9 @@
       <c r="X32" s="63"/>
       <c r="Y32" s="63"/>
       <c r="Z32" s="63"/>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA32" s="63"/>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B33" s="63"/>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
@@ -13431,7 +13599,6 @@
       <c r="K33" s="41"/>
       <c r="L33" s="41"/>
       <c r="M33" s="41"/>
-      <c r="O33" s="63"/>
       <c r="P33" s="63"/>
       <c r="Q33" s="63"/>
       <c r="R33" s="63"/>
@@ -13443,8 +13610,9 @@
       <c r="X33" s="63"/>
       <c r="Y33" s="63"/>
       <c r="Z33" s="63"/>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA33" s="63"/>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" s="63"/>
       <c r="C34" s="41"/>
       <c r="D34" s="41"/>
@@ -13457,7 +13625,6 @@
       <c r="K34" s="41"/>
       <c r="L34" s="41"/>
       <c r="M34" s="41"/>
-      <c r="O34" s="63"/>
       <c r="P34" s="63"/>
       <c r="Q34" s="63"/>
       <c r="R34" s="63"/>
@@ -13469,8 +13636,9 @@
       <c r="X34" s="63"/>
       <c r="Y34" s="63"/>
       <c r="Z34" s="63"/>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA34" s="63"/>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" s="63"/>
       <c r="C35" s="41"/>
       <c r="D35" s="41"/>
@@ -13483,7 +13651,6 @@
       <c r="K35" s="41"/>
       <c r="L35" s="41"/>
       <c r="M35" s="41"/>
-      <c r="O35" s="63"/>
       <c r="P35" s="63"/>
       <c r="Q35" s="63"/>
       <c r="R35" s="63"/>
@@ -13495,10 +13662,10 @@
       <c r="X35" s="63"/>
       <c r="Y35" s="63"/>
       <c r="Z35" s="63"/>
-    </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA35" s="63"/>
+    </row>
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" s="63"/>
-      <c r="O36" s="63"/>
       <c r="P36" s="63"/>
       <c r="Q36" s="63"/>
       <c r="R36" s="63"/>
@@ -13510,8 +13677,9 @@
       <c r="X36" s="63"/>
       <c r="Y36" s="63"/>
       <c r="Z36" s="63"/>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA36" s="63"/>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B37" s="63"/>
       <c r="C37" s="41"/>
       <c r="D37" s="41"/>
@@ -13524,7 +13692,6 @@
       <c r="K37" s="41"/>
       <c r="L37" s="41"/>
       <c r="M37" s="41"/>
-      <c r="O37" s="63"/>
       <c r="P37" s="63"/>
       <c r="Q37" s="63"/>
       <c r="R37" s="63"/>
@@ -13536,8 +13703,9 @@
       <c r="X37" s="63"/>
       <c r="Y37" s="63"/>
       <c r="Z37" s="63"/>
-    </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA37" s="63"/>
+    </row>
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B38" s="63"/>
       <c r="C38" s="41"/>
       <c r="D38" s="41"/>
@@ -13550,7 +13718,6 @@
       <c r="K38" s="41"/>
       <c r="L38" s="41"/>
       <c r="M38" s="41"/>
-      <c r="O38" s="63"/>
       <c r="P38" s="63"/>
       <c r="Q38" s="63"/>
       <c r="R38" s="63"/>
@@ -13562,8 +13729,9 @@
       <c r="X38" s="63"/>
       <c r="Y38" s="63"/>
       <c r="Z38" s="63"/>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA38" s="63"/>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="63"/>
       <c r="C39" s="41"/>
       <c r="D39" s="41"/>
@@ -13576,7 +13744,6 @@
       <c r="K39" s="41"/>
       <c r="L39" s="41"/>
       <c r="M39" s="41"/>
-      <c r="O39" s="63"/>
       <c r="P39" s="63"/>
       <c r="Q39" s="63"/>
       <c r="R39" s="63"/>
@@ -13588,8 +13755,9 @@
       <c r="X39" s="63"/>
       <c r="Y39" s="63"/>
       <c r="Z39" s="63"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA39" s="63"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" s="63"/>
       <c r="C40" s="41"/>
       <c r="D40" s="41"/>
@@ -13602,7 +13770,6 @@
       <c r="K40" s="41"/>
       <c r="L40" s="41"/>
       <c r="M40" s="41"/>
-      <c r="O40" s="63"/>
       <c r="P40" s="63"/>
       <c r="Q40" s="63"/>
       <c r="R40" s="63"/>
@@ -13614,8 +13781,9 @@
       <c r="X40" s="63"/>
       <c r="Y40" s="63"/>
       <c r="Z40" s="63"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA40" s="63"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="63"/>
       <c r="C41" s="41"/>
       <c r="D41" s="41"/>
@@ -13628,7 +13796,6 @@
       <c r="K41" s="41"/>
       <c r="L41" s="41"/>
       <c r="M41" s="41"/>
-      <c r="O41" s="63"/>
       <c r="P41" s="63"/>
       <c r="Q41" s="63"/>
       <c r="R41" s="63"/>
@@ -13640,10 +13807,10 @@
       <c r="X41" s="63"/>
       <c r="Y41" s="63"/>
       <c r="Z41" s="63"/>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA41" s="63"/>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" s="63"/>
-      <c r="O42" s="63"/>
       <c r="P42" s="63"/>
       <c r="Q42" s="63"/>
       <c r="R42" s="63"/>
@@ -13655,8 +13822,9 @@
       <c r="X42" s="63"/>
       <c r="Y42" s="63"/>
       <c r="Z42" s="63"/>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA42" s="63"/>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="63"/>
       <c r="C43" s="41"/>
       <c r="D43" s="41"/>
@@ -13669,7 +13837,6 @@
       <c r="K43" s="41"/>
       <c r="L43" s="41"/>
       <c r="M43" s="41"/>
-      <c r="O43" s="63"/>
       <c r="P43" s="63"/>
       <c r="Q43" s="63"/>
       <c r="R43" s="63"/>
@@ -13681,8 +13848,9 @@
       <c r="X43" s="63"/>
       <c r="Y43" s="63"/>
       <c r="Z43" s="63"/>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA43" s="63"/>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" s="63"/>
       <c r="C44" s="41"/>
       <c r="D44" s="41"/>
@@ -13695,7 +13863,6 @@
       <c r="K44" s="41"/>
       <c r="L44" s="41"/>
       <c r="M44" s="41"/>
-      <c r="O44" s="63"/>
       <c r="P44" s="63"/>
       <c r="Q44" s="63"/>
       <c r="R44" s="63"/>
@@ -13707,8 +13874,9 @@
       <c r="X44" s="63"/>
       <c r="Y44" s="63"/>
       <c r="Z44" s="63"/>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA44" s="63"/>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="63"/>
       <c r="C45" s="41"/>
       <c r="D45" s="41"/>
@@ -13721,7 +13889,6 @@
       <c r="K45" s="41"/>
       <c r="L45" s="41"/>
       <c r="M45" s="41"/>
-      <c r="O45" s="63"/>
       <c r="P45" s="63"/>
       <c r="Q45" s="63"/>
       <c r="R45" s="63"/>
@@ -13733,8 +13900,9 @@
       <c r="X45" s="63"/>
       <c r="Y45" s="63"/>
       <c r="Z45" s="63"/>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA45" s="63"/>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="63"/>
       <c r="C46" s="41"/>
       <c r="D46" s="41"/>
@@ -13747,7 +13915,6 @@
       <c r="K46" s="41"/>
       <c r="L46" s="41"/>
       <c r="M46" s="41"/>
-      <c r="O46" s="63"/>
       <c r="P46" s="63"/>
       <c r="Q46" s="63"/>
       <c r="R46" s="63"/>
@@ -13759,8 +13926,9 @@
       <c r="X46" s="63"/>
       <c r="Y46" s="63"/>
       <c r="Z46" s="63"/>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA46" s="63"/>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="63"/>
       <c r="C47" s="41"/>
       <c r="D47" s="41"/>
@@ -13773,7 +13941,6 @@
       <c r="K47" s="41"/>
       <c r="L47" s="41"/>
       <c r="M47" s="41"/>
-      <c r="O47" s="63"/>
       <c r="P47" s="63"/>
       <c r="Q47" s="63"/>
       <c r="R47" s="63"/>
@@ -13785,8 +13952,9 @@
       <c r="X47" s="63"/>
       <c r="Y47" s="63"/>
       <c r="Z47" s="63"/>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA47" s="63"/>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="63"/>
       <c r="C48" s="41"/>
       <c r="D48" s="41"/>
@@ -13799,7 +13967,6 @@
       <c r="K48" s="41"/>
       <c r="L48" s="41"/>
       <c r="M48" s="41"/>
-      <c r="O48" s="63"/>
       <c r="P48" s="63"/>
       <c r="Q48" s="63"/>
       <c r="R48" s="63"/>
@@ -13811,8 +13978,9 @@
       <c r="X48" s="63"/>
       <c r="Y48" s="63"/>
       <c r="Z48" s="63"/>
-    </row>
-    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA48" s="63"/>
+    </row>
+    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" s="63"/>
       <c r="C49" s="41"/>
       <c r="D49" s="41"/>
@@ -13825,7 +13993,6 @@
       <c r="K49" s="41"/>
       <c r="L49" s="41"/>
       <c r="M49" s="41"/>
-      <c r="O49" s="63"/>
       <c r="P49" s="63"/>
       <c r="Q49" s="63"/>
       <c r="R49" s="63"/>
@@ -13837,8 +14004,9 @@
       <c r="X49" s="63"/>
       <c r="Y49" s="63"/>
       <c r="Z49" s="63"/>
-    </row>
-    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AA49" s="63"/>
+    </row>
+    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" s="63"/>
       <c r="C50" s="41"/>
       <c r="D50" s="41"/>
@@ -13851,7 +14019,6 @@
       <c r="K50" s="41"/>
       <c r="L50" s="41"/>
       <c r="M50" s="41"/>
-      <c r="O50" s="63"/>
       <c r="P50" s="63"/>
       <c r="Q50" s="63"/>
       <c r="R50" s="63"/>
@@ -13863,6 +14030,7 @@
       <c r="X50" s="63"/>
       <c r="Y50" s="63"/>
       <c r="Z50" s="63"/>
+      <c r="AA50" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/12_StopFrequency_2023_blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one-tm1.7_calibration\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F1795A-B00B-4A4D-B4B6-5A96D9418CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01C4DCCF-C262-47D6-BB31-528B2EF5906A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{1191E293-BD99-4EAF-97FD-32238A032A8E}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="2" r:id="rId1"/>
@@ -384,7 +384,7 @@
     <t>4 out, 4 in</t>
   </si>
   <si>
-    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/12_stop_freq_summary_BATS.csv</t>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261027/ctramp_2023/BATS_Summaries/12_stop_freq_summary_BATS.csv</t>
   </si>
 </sst>
 </file>
@@ -1172,47 +1172,47 @@
       </c>
       <c r="C4" s="43">
         <f>SUM('BATS 2023'!Q4:Q7)</f>
-        <v>19346</v>
+        <v>10704</v>
       </c>
       <c r="D4" s="44">
         <f>SUM('BATS 2023'!R4:R7)</f>
-        <v>440</v>
+        <v>234</v>
       </c>
       <c r="E4" s="44">
         <f>SUM('BATS 2023'!S4:S7)</f>
-        <v>2368</v>
+        <v>676</v>
       </c>
       <c r="F4" s="44">
         <f>SUM('BATS 2023'!T4:T7)</f>
-        <v>11754</v>
+        <v>3400</v>
       </c>
       <c r="G4" s="44">
         <f>SUM('BATS 2023'!U4:U7)</f>
-        <v>12910</v>
+        <v>4378</v>
       </c>
       <c r="H4" s="44">
         <f>SUM('BATS 2023'!V4:V7)</f>
-        <v>8324</v>
+        <v>3726</v>
       </c>
       <c r="I4" s="44">
         <f>SUM('BATS 2023'!W4:W7)</f>
-        <v>9598</v>
+        <v>3468</v>
       </c>
       <c r="J4" s="44">
         <f>SUM('BATS 2023'!X4:X7)</f>
-        <v>27932</v>
+        <v>11230</v>
       </c>
       <c r="K4" s="44">
         <f>SUM('BATS 2023'!Y4:Y7)</f>
-        <v>3450</v>
+        <v>1334</v>
       </c>
       <c r="L4" s="44">
         <f>SUM('BATS 2023'!Z4:Z7)</f>
-        <v>3560</v>
+        <v>2126</v>
       </c>
       <c r="M4" s="45">
         <f>SUM('BATS 2023'!AA4:AA7)</f>
-        <v>36074</v>
+        <v>7338</v>
       </c>
       <c r="O4" t="s">
         <v>31</v>
@@ -1266,47 +1266,47 @@
       </c>
       <c r="AC4" s="3">
         <f>P4-C4</f>
-        <v>-19346</v>
+        <v>-10704</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" ref="AD4:AM5" si="0">Q4-D4</f>
-        <v>-440</v>
+        <v>-234</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="0"/>
-        <v>-2368</v>
+        <v>-676</v>
       </c>
       <c r="AF4" s="4">
         <f t="shared" si="0"/>
-        <v>-11754</v>
+        <v>-3400</v>
       </c>
       <c r="AG4" s="4">
         <f t="shared" si="0"/>
-        <v>-12910</v>
+        <v>-4378</v>
       </c>
       <c r="AH4" s="4">
         <f t="shared" si="0"/>
-        <v>-8324</v>
+        <v>-3726</v>
       </c>
       <c r="AI4" s="4">
         <f t="shared" si="0"/>
-        <v>-9598</v>
+        <v>-3468</v>
       </c>
       <c r="AJ4" s="4">
         <f t="shared" si="0"/>
-        <v>-27932</v>
+        <v>-11230</v>
       </c>
       <c r="AK4" s="4">
         <f t="shared" si="0"/>
-        <v>-3450</v>
+        <v>-1334</v>
       </c>
       <c r="AL4" s="4">
         <f t="shared" si="0"/>
-        <v>-3560</v>
+        <v>-2126</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="0"/>
-        <v>-36074</v>
+        <v>-7338</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1315,47 +1315,47 @@
       </c>
       <c r="C5" s="46">
         <f>SUM('BATS 2023'!Q8:Q11)</f>
-        <v>4680</v>
+        <v>2452</v>
       </c>
       <c r="D5" s="47">
         <f>SUM('BATS 2023'!R8:R11)</f>
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="E5" s="47">
         <f>SUM('BATS 2023'!S8:S11)</f>
-        <v>222</v>
+        <v>60</v>
       </c>
       <c r="F5" s="47">
         <f>SUM('BATS 2023'!T8:T11)</f>
-        <v>896</v>
+        <v>282</v>
       </c>
       <c r="G5" s="47">
         <f>SUM('BATS 2023'!U8:U11)</f>
-        <v>4774</v>
+        <v>1532</v>
       </c>
       <c r="H5" s="47">
         <f>SUM('BATS 2023'!V8:V11)</f>
-        <v>1704</v>
+        <v>740</v>
       </c>
       <c r="I5" s="47">
         <f>SUM('BATS 2023'!W8:W11)</f>
-        <v>3174</v>
+        <v>1054</v>
       </c>
       <c r="J5" s="47">
         <f>SUM('BATS 2023'!X8:X11)</f>
-        <v>3548</v>
+        <v>1160</v>
       </c>
       <c r="K5" s="47">
         <f>SUM('BATS 2023'!Y8:Y11)</f>
-        <v>480</v>
+        <v>232</v>
       </c>
       <c r="L5" s="47">
         <f>SUM('BATS 2023'!Z8:Z11)</f>
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="M5" s="48">
         <f>SUM('BATS 2023'!AA8:AA11)</f>
-        <v>6942</v>
+        <v>1008</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
@@ -1409,47 +1409,47 @@
       </c>
       <c r="AC5" s="6">
         <f>P5-C5</f>
-        <v>-4680</v>
+        <v>-2452</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>-94</v>
+        <v>-68</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>-222</v>
+        <v>-60</v>
       </c>
       <c r="AF5">
         <f t="shared" si="0"/>
-        <v>-896</v>
+        <v>-282</v>
       </c>
       <c r="AG5">
         <f t="shared" si="0"/>
-        <v>-4774</v>
+        <v>-1532</v>
       </c>
       <c r="AH5">
         <f t="shared" si="0"/>
-        <v>-1704</v>
+        <v>-740</v>
       </c>
       <c r="AI5">
         <f t="shared" si="0"/>
-        <v>-3174</v>
+        <v>-1054</v>
       </c>
       <c r="AJ5">
         <f t="shared" si="0"/>
-        <v>-3548</v>
+        <v>-1160</v>
       </c>
       <c r="AK5">
         <f t="shared" si="0"/>
-        <v>-480</v>
+        <v>-232</v>
       </c>
       <c r="AL5">
         <f t="shared" si="0"/>
-        <v>-344</v>
+        <v>-196</v>
       </c>
       <c r="AM5" s="7">
         <f t="shared" si="0"/>
-        <v>-6942</v>
+        <v>-1008</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1458,47 +1458,47 @@
       </c>
       <c r="C6" s="46">
         <f>SUM('BATS 2023'!Q12:Q15)</f>
-        <v>1862</v>
+        <v>1004</v>
       </c>
       <c r="D6" s="47">
         <f>SUM('BATS 2023'!R12:R15)</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" s="47">
         <f>SUM('BATS 2023'!S12:S15)</f>
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F6" s="47">
         <f>SUM('BATS 2023'!T12:T15)</f>
-        <v>228</v>
+        <v>70</v>
       </c>
       <c r="G6" s="47">
         <f>SUM('BATS 2023'!U12:U15)</f>
-        <v>2048</v>
+        <v>594</v>
       </c>
       <c r="H6" s="47">
         <f>SUM('BATS 2023'!V12:V15)</f>
-        <v>598</v>
+        <v>206</v>
       </c>
       <c r="I6" s="47">
         <f>SUM('BATS 2023'!W12:W15)</f>
-        <v>1306</v>
+        <v>360</v>
       </c>
       <c r="J6" s="47">
         <f>SUM('BATS 2023'!X12:X15)</f>
-        <v>1756</v>
+        <v>502</v>
       </c>
       <c r="K6" s="47">
         <f>SUM('BATS 2023'!Y12:Y15)</f>
-        <v>212</v>
+        <v>114</v>
       </c>
       <c r="L6" s="47">
         <f>SUM('BATS 2023'!Z12:Z15)</f>
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="M6" s="48">
         <f>SUM('BATS 2023'!AA12:AA15)</f>
-        <v>2620</v>
+        <v>284</v>
       </c>
       <c r="O6" t="s">
         <v>33</v>
@@ -1552,47 +1552,47 @@
       </c>
       <c r="AC6" s="6">
         <f t="shared" ref="AC6:AC8" si="1">P6-C6</f>
-        <v>-1862</v>
+        <v>-1004</v>
       </c>
       <c r="AD6">
         <f t="shared" ref="AD6:AD8" si="2">Q6-D6</f>
-        <v>-24</v>
+        <v>-22</v>
       </c>
       <c r="AE6">
         <f t="shared" ref="AE6:AE8" si="3">R6-E6</f>
-        <v>-44</v>
+        <v>-8</v>
       </c>
       <c r="AF6">
         <f t="shared" ref="AF6:AF8" si="4">S6-F6</f>
-        <v>-228</v>
+        <v>-70</v>
       </c>
       <c r="AG6">
         <f t="shared" ref="AG6:AG8" si="5">T6-G6</f>
-        <v>-2048</v>
+        <v>-594</v>
       </c>
       <c r="AH6">
         <f t="shared" ref="AH6:AH8" si="6">U6-H6</f>
-        <v>-598</v>
+        <v>-206</v>
       </c>
       <c r="AI6">
         <f t="shared" ref="AI6:AI8" si="7">V6-I6</f>
-        <v>-1306</v>
+        <v>-360</v>
       </c>
       <c r="AJ6">
         <f t="shared" ref="AJ6:AJ8" si="8">W6-J6</f>
-        <v>-1756</v>
+        <v>-502</v>
       </c>
       <c r="AK6">
         <f t="shared" ref="AK6:AK8" si="9">X6-K6</f>
-        <v>-212</v>
+        <v>-114</v>
       </c>
       <c r="AL6">
         <f t="shared" ref="AL6:AL8" si="10">Y6-L6</f>
-        <v>-82</v>
+        <v>-40</v>
       </c>
       <c r="AM6" s="7">
         <f t="shared" ref="AM6:AM8" si="11">Z6-M6</f>
-        <v>-2620</v>
+        <v>-284</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1601,47 +1601,47 @@
       </c>
       <c r="C7" s="49">
         <f>SUM('BATS 2023'!Q16:Q19)</f>
-        <v>1316</v>
+        <v>640</v>
       </c>
       <c r="D7" s="50">
         <f>SUM('BATS 2023'!R16:R19)</f>
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E7" s="50">
         <f>SUM('BATS 2023'!S16:S19)</f>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F7" s="50">
         <f>SUM('BATS 2023'!T16:T19)</f>
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="G7" s="50">
         <f>SUM('BATS 2023'!U16:U19)</f>
-        <v>1648</v>
+        <v>484</v>
       </c>
       <c r="H7" s="50">
         <f>SUM('BATS 2023'!V16:V19)</f>
-        <v>392</v>
+        <v>134</v>
       </c>
       <c r="I7" s="50">
         <f>SUM('BATS 2023'!W16:W19)</f>
-        <v>1266</v>
+        <v>320</v>
       </c>
       <c r="J7" s="50">
         <f>SUM('BATS 2023'!X16:X19)</f>
-        <v>1056</v>
+        <v>282</v>
       </c>
       <c r="K7" s="50">
         <f>SUM('BATS 2023'!Y16:Y19)</f>
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="L7" s="50">
         <f>SUM('BATS 2023'!Z16:Z19)</f>
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="M7" s="51">
         <f>SUM('BATS 2023'!AA16:AA19)</f>
-        <v>1270</v>
+        <v>70</v>
       </c>
       <c r="O7" t="s">
         <v>34</v>
@@ -1695,47 +1695,47 @@
       </c>
       <c r="AC7" s="8">
         <f t="shared" si="1"/>
-        <v>-1316</v>
+        <v>-640</v>
       </c>
       <c r="AD7" s="9">
         <f t="shared" si="2"/>
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="AE7" s="9">
         <f t="shared" si="3"/>
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="AF7" s="9">
         <f t="shared" si="4"/>
-        <v>-92</v>
+        <v>-30</v>
       </c>
       <c r="AG7" s="9">
         <f t="shared" si="5"/>
-        <v>-1648</v>
+        <v>-484</v>
       </c>
       <c r="AH7" s="9">
         <f t="shared" si="6"/>
-        <v>-392</v>
+        <v>-134</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="7"/>
-        <v>-1266</v>
+        <v>-320</v>
       </c>
       <c r="AJ7" s="9">
         <f t="shared" si="8"/>
-        <v>-1056</v>
+        <v>-282</v>
       </c>
       <c r="AK7" s="9">
         <f t="shared" si="9"/>
-        <v>-192</v>
+        <v>-78</v>
       </c>
       <c r="AL7" s="9">
         <f t="shared" si="10"/>
-        <v>-62</v>
+        <v>-34</v>
       </c>
       <c r="AM7" s="10">
         <f t="shared" si="11"/>
-        <v>-1270</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1744,47 +1744,47 @@
       </c>
       <c r="C8" s="52">
         <f>SUM(C4:C7)</f>
-        <v>27204</v>
+        <v>14800</v>
       </c>
       <c r="D8" s="52">
         <f t="shared" ref="D8:M8" si="12">SUM(D4:D7)</f>
-        <v>582</v>
+        <v>338</v>
       </c>
       <c r="E8" s="52">
         <f t="shared" si="12"/>
-        <v>2650</v>
+        <v>746</v>
       </c>
       <c r="F8" s="52">
         <f t="shared" si="12"/>
-        <v>12970</v>
+        <v>3782</v>
       </c>
       <c r="G8" s="52">
         <f t="shared" si="12"/>
-        <v>21380</v>
+        <v>6988</v>
       </c>
       <c r="H8" s="52">
         <f t="shared" si="12"/>
-        <v>11018</v>
+        <v>4806</v>
       </c>
       <c r="I8" s="52">
         <f t="shared" si="12"/>
-        <v>15344</v>
+        <v>5202</v>
       </c>
       <c r="J8" s="52">
         <f t="shared" si="12"/>
-        <v>34292</v>
+        <v>13174</v>
       </c>
       <c r="K8" s="52">
         <f t="shared" si="12"/>
-        <v>4334</v>
+        <v>1758</v>
       </c>
       <c r="L8" s="52">
         <f t="shared" si="12"/>
-        <v>4048</v>
+        <v>2396</v>
       </c>
       <c r="M8" s="52">
         <f t="shared" si="12"/>
-        <v>46906</v>
+        <v>8700</v>
       </c>
       <c r="O8" t="s">
         <v>39</v>
@@ -1838,47 +1838,47 @@
       </c>
       <c r="AC8">
         <f t="shared" si="1"/>
-        <v>-27204</v>
+        <v>-14800</v>
       </c>
       <c r="AD8">
         <f t="shared" si="2"/>
-        <v>-582</v>
+        <v>-338</v>
       </c>
       <c r="AE8">
         <f t="shared" si="3"/>
-        <v>-2650</v>
+        <v>-746</v>
       </c>
       <c r="AF8">
         <f t="shared" si="4"/>
-        <v>-12970</v>
+        <v>-3782</v>
       </c>
       <c r="AG8">
         <f t="shared" si="5"/>
-        <v>-21380</v>
+        <v>-6988</v>
       </c>
       <c r="AH8">
         <f t="shared" si="6"/>
-        <v>-11018</v>
+        <v>-4806</v>
       </c>
       <c r="AI8">
         <f t="shared" si="7"/>
-        <v>-15344</v>
+        <v>-5202</v>
       </c>
       <c r="AJ8">
         <f t="shared" si="8"/>
-        <v>-34292</v>
+        <v>-13174</v>
       </c>
       <c r="AK8">
         <f t="shared" si="9"/>
-        <v>-4334</v>
+        <v>-1758</v>
       </c>
       <c r="AL8">
         <f t="shared" si="10"/>
-        <v>-4048</v>
+        <v>-2396</v>
       </c>
       <c r="AM8">
         <f t="shared" si="11"/>
-        <v>-46906</v>
+        <v>-8700</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1900,47 +1900,47 @@
       </c>
       <c r="C10" s="43">
         <f>SUM('BATS 2023'!Q4,'BATS 2023'!Q8,'BATS 2023'!Q12,'BATS 2023'!Q16)</f>
-        <v>17838</v>
+        <v>9876</v>
       </c>
       <c r="D10" s="44">
         <f>SUM('BATS 2023'!R4,'BATS 2023'!R8,'BATS 2023'!R12,'BATS 2023'!R16)</f>
-        <v>430</v>
+        <v>240</v>
       </c>
       <c r="E10" s="44">
         <f>SUM('BATS 2023'!S4,'BATS 2023'!S8,'BATS 2023'!S12,'BATS 2023'!S16)</f>
-        <v>2102</v>
+        <v>608</v>
       </c>
       <c r="F10" s="44">
         <f>SUM('BATS 2023'!T4,'BATS 2023'!T8,'BATS 2023'!T12,'BATS 2023'!T16)</f>
-        <v>11578</v>
+        <v>3414</v>
       </c>
       <c r="G10" s="44">
         <f>SUM('BATS 2023'!U4,'BATS 2023'!U8,'BATS 2023'!U12,'BATS 2023'!U16)</f>
-        <v>15402</v>
+        <v>5140</v>
       </c>
       <c r="H10" s="44">
         <f>SUM('BATS 2023'!V4,'BATS 2023'!V8,'BATS 2023'!V12,'BATS 2023'!V16)</f>
-        <v>7714</v>
+        <v>3366</v>
       </c>
       <c r="I10" s="44">
         <f>SUM('BATS 2023'!W4,'BATS 2023'!W8,'BATS 2023'!W12,'BATS 2023'!W16)</f>
-        <v>11286</v>
+        <v>4058</v>
       </c>
       <c r="J10" s="44">
         <f>SUM('BATS 2023'!X4,'BATS 2023'!X8,'BATS 2023'!X12,'BATS 2023'!X16)</f>
-        <v>29070</v>
+        <v>11512</v>
       </c>
       <c r="K10" s="44">
         <f>SUM('BATS 2023'!Y4,'BATS 2023'!Y8,'BATS 2023'!Y12,'BATS 2023'!Y16)</f>
-        <v>3536</v>
+        <v>1392</v>
       </c>
       <c r="L10" s="44">
         <f>SUM('BATS 2023'!Z4,'BATS 2023'!Z8,'BATS 2023'!Z12,'BATS 2023'!Z16)</f>
-        <v>3704</v>
+        <v>2200</v>
       </c>
       <c r="M10" s="45">
         <f>SUM('BATS 2023'!AA4,'BATS 2023'!AA8,'BATS 2023'!AA12,'BATS 2023'!AA16)</f>
-        <v>37348</v>
+        <v>7536</v>
       </c>
       <c r="O10" t="s">
         <v>27</v>
@@ -1994,47 +1994,47 @@
       </c>
       <c r="AC10" s="3">
         <f>P10-C10</f>
-        <v>-17838</v>
+        <v>-9876</v>
       </c>
       <c r="AD10" s="4">
         <f t="shared" ref="AD10:AD14" si="23">Q10-D10</f>
-        <v>-430</v>
+        <v>-240</v>
       </c>
       <c r="AE10" s="4">
         <f t="shared" ref="AE10:AE14" si="24">R10-E10</f>
-        <v>-2102</v>
+        <v>-608</v>
       </c>
       <c r="AF10" s="4">
         <f t="shared" ref="AF10:AF14" si="25">S10-F10</f>
-        <v>-11578</v>
+        <v>-3414</v>
       </c>
       <c r="AG10" s="4">
         <f t="shared" ref="AG10:AG14" si="26">T10-G10</f>
-        <v>-15402</v>
+        <v>-5140</v>
       </c>
       <c r="AH10" s="4">
         <f t="shared" ref="AH10:AH14" si="27">U10-H10</f>
-        <v>-7714</v>
+        <v>-3366</v>
       </c>
       <c r="AI10" s="4">
         <f t="shared" ref="AI10:AI14" si="28">V10-I10</f>
-        <v>-11286</v>
+        <v>-4058</v>
       </c>
       <c r="AJ10" s="4">
         <f t="shared" ref="AJ10:AJ14" si="29">W10-J10</f>
-        <v>-29070</v>
+        <v>-11512</v>
       </c>
       <c r="AK10" s="4">
         <f t="shared" ref="AK10:AK14" si="30">X10-K10</f>
-        <v>-3536</v>
+        <v>-1392</v>
       </c>
       <c r="AL10" s="4">
         <f t="shared" ref="AL10:AL14" si="31">Y10-L10</f>
-        <v>-3704</v>
+        <v>-2200</v>
       </c>
       <c r="AM10" s="5">
         <f t="shared" ref="AM10:AM14" si="32">Z10-M10</f>
-        <v>-37348</v>
+        <v>-7536</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -2043,47 +2043,47 @@
       </c>
       <c r="C11" s="46">
         <f>SUM('BATS 2023'!Q5,'BATS 2023'!Q9,'BATS 2023'!Q13,'BATS 2023'!Q17)</f>
-        <v>5898</v>
+        <v>3136</v>
       </c>
       <c r="D11" s="47">
         <f>SUM('BATS 2023'!R5,'BATS 2023'!R9,'BATS 2023'!R13,'BATS 2023'!R17)</f>
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="E11" s="47">
         <f>SUM('BATS 2023'!S5,'BATS 2023'!S9,'BATS 2023'!S13,'BATS 2023'!S17)</f>
-        <v>372</v>
+        <v>98</v>
       </c>
       <c r="F11" s="47">
         <f>SUM('BATS 2023'!T5,'BATS 2023'!T9,'BATS 2023'!T13,'BATS 2023'!T17)</f>
-        <v>1192</v>
+        <v>324</v>
       </c>
       <c r="G11" s="47">
         <f>SUM('BATS 2023'!U5,'BATS 2023'!U9,'BATS 2023'!U13,'BATS 2023'!U17)</f>
-        <v>4014</v>
+        <v>1266</v>
       </c>
       <c r="H11" s="47">
         <f>SUM('BATS 2023'!V5,'BATS 2023'!V9,'BATS 2023'!V13,'BATS 2023'!V17)</f>
-        <v>2246</v>
+        <v>976</v>
       </c>
       <c r="I11" s="47">
         <f>SUM('BATS 2023'!W5,'BATS 2023'!W9,'BATS 2023'!W13,'BATS 2023'!W17)</f>
-        <v>2636</v>
+        <v>800</v>
       </c>
       <c r="J11" s="47">
         <f>SUM('BATS 2023'!X5,'BATS 2023'!X9,'BATS 2023'!X13,'BATS 2023'!X17)</f>
-        <v>3682</v>
+        <v>1264</v>
       </c>
       <c r="K11" s="47">
         <f>SUM('BATS 2023'!Y5,'BATS 2023'!Y9,'BATS 2023'!Y13,'BATS 2023'!Y17)</f>
-        <v>552</v>
+        <v>248</v>
       </c>
       <c r="L11" s="47">
         <f>SUM('BATS 2023'!Z5,'BATS 2023'!Z9,'BATS 2023'!Z13,'BATS 2023'!Z17)</f>
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="M11" s="48">
         <f>SUM('BATS 2023'!AA5,'BATS 2023'!AA9,'BATS 2023'!AA13,'BATS 2023'!AA17)</f>
-        <v>7002</v>
+        <v>830</v>
       </c>
       <c r="O11" t="s">
         <v>28</v>
@@ -2137,47 +2137,47 @@
       </c>
       <c r="AC11" s="6">
         <f>P11-C11</f>
-        <v>-5898</v>
+        <v>-3136</v>
       </c>
       <c r="AD11">
         <f t="shared" si="23"/>
-        <v>-110</v>
+        <v>-68</v>
       </c>
       <c r="AE11">
         <f t="shared" si="24"/>
-        <v>-372</v>
+        <v>-98</v>
       </c>
       <c r="AF11">
         <f t="shared" si="25"/>
-        <v>-1192</v>
+        <v>-324</v>
       </c>
       <c r="AG11">
         <f t="shared" si="26"/>
-        <v>-4014</v>
+        <v>-1266</v>
       </c>
       <c r="AH11">
         <f t="shared" si="27"/>
-        <v>-2246</v>
+        <v>-976</v>
       </c>
       <c r="AI11">
         <f t="shared" si="28"/>
-        <v>-2636</v>
+        <v>-800</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="29"/>
-        <v>-3682</v>
+        <v>-1264</v>
       </c>
       <c r="AK11">
         <f t="shared" si="30"/>
-        <v>-552</v>
+        <v>-248</v>
       </c>
       <c r="AL11">
         <f t="shared" si="31"/>
-        <v>-274</v>
+        <v>-164</v>
       </c>
       <c r="AM11" s="7">
         <f t="shared" si="32"/>
-        <v>-7002</v>
+        <v>-830</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -2186,47 +2186,47 @@
       </c>
       <c r="C12" s="46">
         <f>SUM('BATS 2023'!Q6,'BATS 2023'!Q10,'BATS 2023'!Q14,'BATS 2023'!Q18)</f>
-        <v>2110</v>
+        <v>1104</v>
       </c>
       <c r="D12" s="47">
         <f>SUM('BATS 2023'!R6,'BATS 2023'!R10,'BATS 2023'!R14,'BATS 2023'!R18)</f>
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E12" s="47">
         <f>SUM('BATS 2023'!S6,'BATS 2023'!S10,'BATS 2023'!S14,'BATS 2023'!S18)</f>
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="F12" s="47">
         <f>SUM('BATS 2023'!T6,'BATS 2023'!T10,'BATS 2023'!T14,'BATS 2023'!T18)</f>
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="G12" s="47">
         <f>SUM('BATS 2023'!U6,'BATS 2023'!U10,'BATS 2023'!U14,'BATS 2023'!U18)</f>
-        <v>1260</v>
+        <v>394</v>
       </c>
       <c r="H12" s="47">
         <f>SUM('BATS 2023'!V6,'BATS 2023'!V10,'BATS 2023'!V14,'BATS 2023'!V18)</f>
-        <v>594</v>
+        <v>270</v>
       </c>
       <c r="I12" s="47">
         <f>SUM('BATS 2023'!W6,'BATS 2023'!W10,'BATS 2023'!W14,'BATS 2023'!W18)</f>
-        <v>800</v>
+        <v>202</v>
       </c>
       <c r="J12" s="47">
         <f>SUM('BATS 2023'!X6,'BATS 2023'!X10,'BATS 2023'!X14,'BATS 2023'!X18)</f>
-        <v>1022</v>
+        <v>276</v>
       </c>
       <c r="K12" s="47">
         <f>SUM('BATS 2023'!Y6,'BATS 2023'!Y10,'BATS 2023'!Y14,'BATS 2023'!Y18)</f>
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="L12" s="47">
         <f>SUM('BATS 2023'!Z6,'BATS 2023'!Z10,'BATS 2023'!Z14,'BATS 2023'!Z18)</f>
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="M12" s="48">
         <f>SUM('BATS 2023'!AA6,'BATS 2023'!AA10,'BATS 2023'!AA14,'BATS 2023'!AA18)</f>
-        <v>1854</v>
+        <v>274</v>
       </c>
       <c r="O12" t="s">
         <v>29</v>
@@ -2280,47 +2280,47 @@
       </c>
       <c r="AC12" s="6">
         <f t="shared" ref="AC12:AC14" si="33">P12-C12</f>
-        <v>-2110</v>
+        <v>-1104</v>
       </c>
       <c r="AD12">
         <f t="shared" si="23"/>
-        <v>-34</v>
+        <v>-22</v>
       </c>
       <c r="AE12">
         <f t="shared" si="24"/>
-        <v>-120</v>
+        <v>-26</v>
       </c>
       <c r="AF12">
         <f t="shared" si="25"/>
-        <v>-130</v>
+        <v>-24</v>
       </c>
       <c r="AG12">
         <f t="shared" si="26"/>
-        <v>-1260</v>
+        <v>-394</v>
       </c>
       <c r="AH12">
         <f t="shared" si="27"/>
-        <v>-594</v>
+        <v>-270</v>
       </c>
       <c r="AI12">
         <f t="shared" si="28"/>
-        <v>-800</v>
+        <v>-202</v>
       </c>
       <c r="AJ12">
         <f t="shared" si="29"/>
-        <v>-1022</v>
+        <v>-276</v>
       </c>
       <c r="AK12">
         <f t="shared" si="30"/>
-        <v>-144</v>
+        <v>-70</v>
       </c>
       <c r="AL12">
         <f t="shared" si="31"/>
-        <v>-46</v>
+        <v>-20</v>
       </c>
       <c r="AM12" s="7">
         <f t="shared" si="32"/>
-        <v>-1854</v>
+        <v>-274</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C13" s="49">
         <f>SUM('BATS 2023'!Q7,'BATS 2023'!Q11,'BATS 2023'!Q15,'BATS 2023'!Q19)</f>
-        <v>1358</v>
+        <v>684</v>
       </c>
       <c r="D13" s="50">
         <f>SUM('BATS 2023'!R7,'BATS 2023'!R11,'BATS 2023'!R15,'BATS 2023'!R19)</f>
@@ -2337,39 +2337,39 @@
       </c>
       <c r="E13" s="50">
         <f>SUM('BATS 2023'!S7,'BATS 2023'!S11,'BATS 2023'!S15,'BATS 2023'!S19)</f>
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F13" s="50">
         <f>SUM('BATS 2023'!T7,'BATS 2023'!T11,'BATS 2023'!T15,'BATS 2023'!T19)</f>
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G13" s="50">
         <f>SUM('BATS 2023'!U7,'BATS 2023'!U11,'BATS 2023'!U15,'BATS 2023'!U19)</f>
-        <v>704</v>
+        <v>188</v>
       </c>
       <c r="H13" s="50">
         <f>SUM('BATS 2023'!V7,'BATS 2023'!V11,'BATS 2023'!V15,'BATS 2023'!V19)</f>
-        <v>464</v>
+        <v>194</v>
       </c>
       <c r="I13" s="50">
         <f>SUM('BATS 2023'!W7,'BATS 2023'!W11,'BATS 2023'!W15,'BATS 2023'!W19)</f>
-        <v>622</v>
+        <v>142</v>
       </c>
       <c r="J13" s="50">
         <f>SUM('BATS 2023'!X7,'BATS 2023'!X11,'BATS 2023'!X15,'BATS 2023'!X19)</f>
-        <v>518</v>
+        <v>122</v>
       </c>
       <c r="K13" s="50">
         <f>SUM('BATS 2023'!Y7,'BATS 2023'!Y11,'BATS 2023'!Y15,'BATS 2023'!Y19)</f>
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="L13" s="50">
         <f>SUM('BATS 2023'!Z7,'BATS 2023'!Z11,'BATS 2023'!Z15,'BATS 2023'!Z19)</f>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M13" s="51">
         <f>SUM('BATS 2023'!AA7,'BATS 2023'!AA11,'BATS 2023'!AA15,'BATS 2023'!AA19)</f>
-        <v>702</v>
+        <v>60</v>
       </c>
       <c r="O13" t="s">
         <v>30</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AC13" s="8">
         <f t="shared" si="33"/>
-        <v>-1358</v>
+        <v>-684</v>
       </c>
       <c r="AD13" s="9">
         <f t="shared" si="23"/>
@@ -2431,39 +2431,39 @@
       </c>
       <c r="AE13" s="9">
         <f t="shared" si="24"/>
-        <v>-56</v>
+        <v>-14</v>
       </c>
       <c r="AF13" s="9">
         <f t="shared" si="25"/>
-        <v>-70</v>
+        <v>-20</v>
       </c>
       <c r="AG13" s="9">
         <f t="shared" si="26"/>
-        <v>-704</v>
+        <v>-188</v>
       </c>
       <c r="AH13" s="9">
         <f t="shared" si="27"/>
-        <v>-464</v>
+        <v>-194</v>
       </c>
       <c r="AI13" s="9">
         <f t="shared" si="28"/>
-        <v>-622</v>
+        <v>-142</v>
       </c>
       <c r="AJ13" s="9">
         <f t="shared" si="29"/>
-        <v>-518</v>
+        <v>-122</v>
       </c>
       <c r="AK13" s="9">
         <f t="shared" si="30"/>
-        <v>-102</v>
+        <v>-48</v>
       </c>
       <c r="AL13" s="9">
         <f t="shared" si="31"/>
-        <v>-24</v>
+        <v>-12</v>
       </c>
       <c r="AM13" s="10">
         <f t="shared" si="32"/>
-        <v>-702</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2472,47 +2472,47 @@
       </c>
       <c r="C14" s="52">
         <f>SUM(C10:C13)</f>
-        <v>27204</v>
+        <v>14800</v>
       </c>
       <c r="D14" s="52">
         <f t="shared" ref="D14:M14" si="34">SUM(D10:D13)</f>
-        <v>582</v>
+        <v>338</v>
       </c>
       <c r="E14" s="52">
         <f t="shared" si="34"/>
-        <v>2650</v>
+        <v>746</v>
       </c>
       <c r="F14" s="52">
         <f t="shared" si="34"/>
-        <v>12970</v>
+        <v>3782</v>
       </c>
       <c r="G14" s="52">
         <f t="shared" si="34"/>
-        <v>21380</v>
+        <v>6988</v>
       </c>
       <c r="H14" s="52">
         <f t="shared" si="34"/>
-        <v>11018</v>
+        <v>4806</v>
       </c>
       <c r="I14" s="52">
         <f t="shared" si="34"/>
-        <v>15344</v>
+        <v>5202</v>
       </c>
       <c r="J14" s="52">
         <f t="shared" si="34"/>
-        <v>34292</v>
+        <v>13174</v>
       </c>
       <c r="K14" s="52">
         <f t="shared" si="34"/>
-        <v>4334</v>
+        <v>1758</v>
       </c>
       <c r="L14" s="52">
         <f t="shared" si="34"/>
-        <v>4048</v>
+        <v>2396</v>
       </c>
       <c r="M14" s="52">
         <f t="shared" si="34"/>
-        <v>46906</v>
+        <v>8700</v>
       </c>
       <c r="O14" t="s">
         <v>39</v>
@@ -2566,47 +2566,47 @@
       </c>
       <c r="AC14">
         <f t="shared" si="33"/>
-        <v>-27204</v>
+        <v>-14800</v>
       </c>
       <c r="AD14">
         <f t="shared" si="23"/>
-        <v>-582</v>
+        <v>-338</v>
       </c>
       <c r="AE14">
         <f t="shared" si="24"/>
-        <v>-2650</v>
+        <v>-746</v>
       </c>
       <c r="AF14">
         <f t="shared" si="25"/>
-        <v>-12970</v>
+        <v>-3782</v>
       </c>
       <c r="AG14">
         <f t="shared" si="26"/>
-        <v>-21380</v>
+        <v>-6988</v>
       </c>
       <c r="AH14">
         <f t="shared" si="27"/>
-        <v>-11018</v>
+        <v>-4806</v>
       </c>
       <c r="AI14">
         <f t="shared" si="28"/>
-        <v>-15344</v>
+        <v>-5202</v>
       </c>
       <c r="AJ14">
         <f t="shared" si="29"/>
-        <v>-34292</v>
+        <v>-13174</v>
       </c>
       <c r="AK14">
         <f t="shared" si="30"/>
-        <v>-4334</v>
+        <v>-1758</v>
       </c>
       <c r="AL14">
         <f t="shared" si="31"/>
-        <v>-4048</v>
+        <v>-2396</v>
       </c>
       <c r="AM14">
         <f t="shared" si="32"/>
-        <v>-46906</v>
+        <v>-8700</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2639,47 +2639,47 @@
       </c>
       <c r="C16" s="43">
         <f>'BATS 2023'!Q4</f>
-        <v>13536</v>
+        <v>7548</v>
       </c>
       <c r="D16" s="44">
         <f>'BATS 2023'!R4</f>
-        <v>328</v>
+        <v>174</v>
       </c>
       <c r="E16" s="44">
         <f>'BATS 2023'!S4</f>
-        <v>1936</v>
+        <v>562</v>
       </c>
       <c r="F16" s="44">
         <f>'BATS 2023'!T4</f>
-        <v>10630</v>
+        <v>3106</v>
       </c>
       <c r="G16" s="44">
         <f>'BATS 2023'!U4</f>
-        <v>9868</v>
+        <v>3438</v>
       </c>
       <c r="H16" s="44">
         <f>'BATS 2023'!V4</f>
-        <v>6004</v>
+        <v>2660</v>
       </c>
       <c r="I16" s="44">
         <f>'BATS 2023'!W4</f>
-        <v>7624</v>
+        <v>2892</v>
       </c>
       <c r="J16" s="44">
         <f>'BATS 2023'!X4</f>
-        <v>24698</v>
+        <v>10138</v>
       </c>
       <c r="K16" s="44">
         <f>'BATS 2023'!Y4</f>
-        <v>2954</v>
+        <v>1126</v>
       </c>
       <c r="L16" s="44">
         <f>'BATS 2023'!Z4</f>
-        <v>3334</v>
+        <v>1982</v>
       </c>
       <c r="M16" s="45">
         <f>'BATS 2023'!AA4</f>
-        <v>29986</v>
+        <v>6484</v>
       </c>
       <c r="O16" t="s">
         <v>41</v>
@@ -2733,47 +2733,47 @@
       </c>
       <c r="AC16" s="3">
         <f>P16-C16</f>
-        <v>-13536</v>
+        <v>-7548</v>
       </c>
       <c r="AD16" s="4">
         <f t="shared" ref="AD16:AD20" si="45">Q16-D16</f>
-        <v>-328</v>
+        <v>-174</v>
       </c>
       <c r="AE16" s="4">
         <f t="shared" ref="AE16:AE20" si="46">R16-E16</f>
-        <v>-1936</v>
+        <v>-562</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" ref="AF16:AF20" si="47">S16-F16</f>
-        <v>-10630</v>
+        <v>-3106</v>
       </c>
       <c r="AG16" s="4">
         <f t="shared" ref="AG16:AG20" si="48">T16-G16</f>
-        <v>-9868</v>
+        <v>-3438</v>
       </c>
       <c r="AH16" s="4">
         <f t="shared" ref="AH16:AH20" si="49">U16-H16</f>
-        <v>-6004</v>
+        <v>-2660</v>
       </c>
       <c r="AI16" s="4">
         <f t="shared" ref="AI16:AI20" si="50">V16-I16</f>
-        <v>-7624</v>
+        <v>-2892</v>
       </c>
       <c r="AJ16" s="4">
         <f t="shared" ref="AJ16:AJ20" si="51">W16-J16</f>
-        <v>-24698</v>
+        <v>-10138</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" ref="AK16:AK20" si="52">X16-K16</f>
-        <v>-2954</v>
+        <v>-1126</v>
       </c>
       <c r="AL16" s="4">
         <f t="shared" ref="AL16:AL20" si="53">Y16-L16</f>
-        <v>-3334</v>
+        <v>-1982</v>
       </c>
       <c r="AM16" s="5">
         <f t="shared" ref="AM16:AM20" si="54">Z16-M16</f>
-        <v>-29986</v>
+        <v>-6484</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C17" s="46">
         <f>'BATS 2023'!Q5+'BATS 2023'!Q8</f>
-        <v>6512</v>
+        <v>3554</v>
       </c>
       <c r="D17" s="47">
         <f>'BATS 2023'!R5+'BATS 2023'!R8</f>
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="E17" s="47">
         <f>'BATS 2023'!S5+'BATS 2023'!S8</f>
-        <v>442</v>
+        <v>124</v>
       </c>
       <c r="F17" s="47">
         <f>'BATS 2023'!T5+'BATS 2023'!T8</f>
-        <v>1704</v>
+        <v>496</v>
       </c>
       <c r="G17" s="47">
         <f>'BATS 2023'!U5+'BATS 2023'!U8</f>
-        <v>5386</v>
+        <v>1732</v>
       </c>
       <c r="H17" s="47">
         <f>'BATS 2023'!V5+'BATS 2023'!V8</f>
-        <v>2674</v>
+        <v>1220</v>
       </c>
       <c r="I17" s="47">
         <f>'BATS 2023'!W5+'BATS 2023'!W8</f>
-        <v>3444</v>
+        <v>1172</v>
       </c>
       <c r="J17" s="47">
         <f>'BATS 2023'!X5+'BATS 2023'!X8</f>
-        <v>4744</v>
+        <v>1654</v>
       </c>
       <c r="K17" s="47">
         <f>'BATS 2023'!Y5+'BATS 2023'!Y8</f>
-        <v>676</v>
+        <v>294</v>
       </c>
       <c r="L17" s="47">
         <f>'BATS 2023'!Z5+'BATS 2023'!Z8</f>
-        <v>474</v>
+        <v>282</v>
       </c>
       <c r="M17" s="48">
         <f>'BATS 2023'!AA5+'BATS 2023'!AA8</f>
-        <v>9286</v>
+        <v>1412</v>
       </c>
       <c r="O17" t="s">
         <v>35</v>
@@ -2876,47 +2876,47 @@
       </c>
       <c r="AC17" s="6">
         <f>P17-C17</f>
-        <v>-6512</v>
+        <v>-3554</v>
       </c>
       <c r="AD17">
         <f t="shared" si="45"/>
-        <v>-166</v>
+        <v>-100</v>
       </c>
       <c r="AE17">
         <f t="shared" si="46"/>
-        <v>-442</v>
+        <v>-124</v>
       </c>
       <c r="AF17">
         <f t="shared" si="47"/>
-        <v>-1704</v>
+        <v>-496</v>
       </c>
       <c r="AG17">
         <f t="shared" si="48"/>
-        <v>-5386</v>
+        <v>-1732</v>
       </c>
       <c r="AH17">
         <f t="shared" si="49"/>
-        <v>-2674</v>
+        <v>-1220</v>
       </c>
       <c r="AI17">
         <f t="shared" si="50"/>
-        <v>-3444</v>
+        <v>-1172</v>
       </c>
       <c r="AJ17">
         <f t="shared" si="51"/>
-        <v>-4744</v>
+        <v>-1654</v>
       </c>
       <c r="AK17">
         <f t="shared" si="52"/>
-        <v>-676</v>
+        <v>-294</v>
       </c>
       <c r="AL17">
         <f t="shared" si="53"/>
-        <v>-474</v>
+        <v>-282</v>
       </c>
       <c r="AM17" s="7">
         <f t="shared" si="54"/>
-        <v>-9286</v>
+        <v>-1412</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2925,47 +2925,47 @@
       </c>
       <c r="C18" s="46">
         <f>SUM('BATS 2023'!Q6,'BATS 2023'!Q12,'BATS 2023'!Q9)</f>
-        <v>3440</v>
+        <v>1834</v>
       </c>
       <c r="D18" s="47">
         <f>SUM('BATS 2023'!R6,'BATS 2023'!R12,'BATS 2023'!R9)</f>
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E18" s="47">
         <f>SUM('BATS 2023'!S6,'BATS 2023'!S12,'BATS 2023'!S9)</f>
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="F18" s="47">
         <f>SUM('BATS 2023'!T6,'BATS 2023'!T12,'BATS 2023'!T9)</f>
-        <v>406</v>
+        <v>108</v>
       </c>
       <c r="G18" s="47">
         <f>SUM('BATS 2023'!U6,'BATS 2023'!U12,'BATS 2023'!U9)</f>
-        <v>2858</v>
+        <v>840</v>
       </c>
       <c r="H18" s="47">
         <f>SUM('BATS 2023'!V6,'BATS 2023'!V12,'BATS 2023'!V9)</f>
-        <v>1272</v>
+        <v>500</v>
       </c>
       <c r="I18" s="47">
         <f>SUM('BATS 2023'!W6,'BATS 2023'!W12,'BATS 2023'!W9)</f>
-        <v>1844</v>
+        <v>522</v>
       </c>
       <c r="J18" s="47">
         <f>SUM('BATS 2023'!X6,'BATS 2023'!X12,'BATS 2023'!X9)</f>
-        <v>2696</v>
+        <v>822</v>
       </c>
       <c r="K18" s="47">
         <f>SUM('BATS 2023'!Y6,'BATS 2023'!Y12,'BATS 2023'!Y9)</f>
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="L18" s="47">
         <f>SUM('BATS 2023'!Z6,'BATS 2023'!Z12,'BATS 2023'!Z9)</f>
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="M18" s="48">
         <f>SUM('BATS 2023'!AA6,'BATS 2023'!AA12,'BATS 2023'!AA9)</f>
-        <v>4416</v>
+        <v>556</v>
       </c>
       <c r="O18" t="s">
         <v>36</v>
@@ -3019,47 +3019,47 @@
       </c>
       <c r="AC18" s="6">
         <f t="shared" ref="AC18:AC20" si="55">P18-C18</f>
-        <v>-3440</v>
+        <v>-1834</v>
       </c>
       <c r="AD18">
         <f t="shared" si="45"/>
-        <v>-40</v>
+        <v>-26</v>
       </c>
       <c r="AE18">
         <f t="shared" si="46"/>
-        <v>-156</v>
+        <v>-34</v>
       </c>
       <c r="AF18">
         <f t="shared" si="47"/>
-        <v>-406</v>
+        <v>-108</v>
       </c>
       <c r="AG18">
         <f t="shared" si="48"/>
-        <v>-2858</v>
+        <v>-840</v>
       </c>
       <c r="AH18">
         <f t="shared" si="49"/>
-        <v>-1272</v>
+        <v>-500</v>
       </c>
       <c r="AI18">
         <f t="shared" si="50"/>
-        <v>-1844</v>
+        <v>-522</v>
       </c>
       <c r="AJ18">
         <f t="shared" si="51"/>
-        <v>-2696</v>
+        <v>-822</v>
       </c>
       <c r="AK18">
         <f t="shared" si="52"/>
-        <v>-350</v>
+        <v>-180</v>
       </c>
       <c r="AL18">
         <f t="shared" si="53"/>
-        <v>-132</v>
+        <v>-76</v>
       </c>
       <c r="AM18" s="7">
         <f t="shared" si="54"/>
-        <v>-4416</v>
+        <v>-556</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -3068,47 +3068,47 @@
       </c>
       <c r="C19" s="46">
         <f>SUM('BATS 2023'!Q7,'BATS 2023'!Q10,'BATS 2023'!Q13,'BATS 2023'!Q16)</f>
-        <v>2368</v>
+        <v>1216</v>
       </c>
       <c r="D19" s="47">
         <f>SUM('BATS 2023'!R7,'BATS 2023'!R10,'BATS 2023'!R13,'BATS 2023'!R16)</f>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E19" s="47">
         <f>SUM('BATS 2023'!S7,'BATS 2023'!S10,'BATS 2023'!S13,'BATS 2023'!S16)</f>
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F19" s="47">
         <f>SUM('BATS 2023'!T7,'BATS 2023'!T10,'BATS 2023'!T13,'BATS 2023'!T16)</f>
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="G19" s="47">
         <f>SUM('BATS 2023'!U7,'BATS 2023'!U10,'BATS 2023'!U13,'BATS 2023'!U16)</f>
-        <v>2184</v>
+        <v>656</v>
       </c>
       <c r="H19" s="47">
         <f>SUM('BATS 2023'!V7,'BATS 2023'!V10,'BATS 2023'!V13,'BATS 2023'!V16)</f>
-        <v>736</v>
+        <v>300</v>
       </c>
       <c r="I19" s="47">
         <f>SUM('BATS 2023'!W7,'BATS 2023'!W10,'BATS 2023'!W13,'BATS 2023'!W16)</f>
-        <v>1564</v>
+        <v>408</v>
       </c>
       <c r="J19" s="47">
         <f>SUM('BATS 2023'!X7,'BATS 2023'!X10,'BATS 2023'!X13,'BATS 2023'!X16)</f>
-        <v>1512</v>
+        <v>408</v>
       </c>
       <c r="K19" s="47">
         <f>SUM('BATS 2023'!Y7,'BATS 2023'!Y10,'BATS 2023'!Y13,'BATS 2023'!Y16)</f>
-        <v>240</v>
+        <v>94</v>
       </c>
       <c r="L19" s="47">
         <f>SUM('BATS 2023'!Z7,'BATS 2023'!Z10,'BATS 2023'!Z13,'BATS 2023'!Z16)</f>
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="M19" s="48">
         <f>SUM('BATS 2023'!AA7,'BATS 2023'!AA10,'BATS 2023'!AA13,'BATS 2023'!AA16)</f>
-        <v>2374</v>
+        <v>188</v>
       </c>
       <c r="O19" t="s">
         <v>37</v>
@@ -3162,47 +3162,47 @@
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="55"/>
-        <v>-2368</v>
+        <v>-1216</v>
       </c>
       <c r="AD19">
         <f t="shared" si="45"/>
-        <v>-36</v>
+        <v>-28</v>
       </c>
       <c r="AE19">
         <f t="shared" si="46"/>
-        <v>-86</v>
+        <v>-22</v>
       </c>
       <c r="AF19">
         <f t="shared" si="47"/>
-        <v>-172</v>
+        <v>-56</v>
       </c>
       <c r="AG19">
         <f t="shared" si="48"/>
-        <v>-2184</v>
+        <v>-656</v>
       </c>
       <c r="AH19">
         <f t="shared" si="49"/>
-        <v>-736</v>
+        <v>-300</v>
       </c>
       <c r="AI19">
         <f t="shared" si="50"/>
-        <v>-1564</v>
+        <v>-408</v>
       </c>
       <c r="AJ19">
         <f t="shared" si="51"/>
-        <v>-1512</v>
+        <v>-408</v>
       </c>
       <c r="AK19">
         <f t="shared" si="52"/>
-        <v>-240</v>
+        <v>-94</v>
       </c>
       <c r="AL19">
         <f t="shared" si="53"/>
-        <v>-66</v>
+        <v>-44</v>
       </c>
       <c r="AM19" s="7">
         <f t="shared" si="54"/>
-        <v>-2374</v>
+        <v>-188</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -3211,47 +3211,47 @@
       </c>
       <c r="C20" s="46">
         <f>SUM('BATS 2023'!Q11,'BATS 2023'!Q14,'BATS 2023'!Q17)</f>
-        <v>846</v>
+        <v>406</v>
       </c>
       <c r="D20" s="47">
         <f>SUM('BATS 2023'!R11,'BATS 2023'!R14,'BATS 2023'!R17)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="47">
         <f>SUM('BATS 2023'!S11,'BATS 2023'!S14,'BATS 2023'!S17)</f>
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F20" s="47">
         <f>SUM('BATS 2023'!T11,'BATS 2023'!T14,'BATS 2023'!T17)</f>
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G20" s="47">
         <f>SUM('BATS 2023'!U11,'BATS 2023'!U14,'BATS 2023'!U17)</f>
-        <v>714</v>
+        <v>228</v>
       </c>
       <c r="H20" s="47">
         <f>SUM('BATS 2023'!V11,'BATS 2023'!V14,'BATS 2023'!V17)</f>
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="I20" s="47">
         <f>SUM('BATS 2023'!W11,'BATS 2023'!W14,'BATS 2023'!W17)</f>
-        <v>576</v>
+        <v>134</v>
       </c>
       <c r="J20" s="47">
         <f>SUM('BATS 2023'!X11,'BATS 2023'!X14,'BATS 2023'!X17)</f>
-        <v>430</v>
+        <v>100</v>
       </c>
       <c r="K20" s="47">
         <f>SUM('BATS 2023'!Y11,'BATS 2023'!Y14,'BATS 2023'!Y17)</f>
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L20" s="47">
         <f>SUM('BATS 2023'!Z11,'BATS 2023'!Z14,'BATS 2023'!Z17)</f>
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M20" s="48">
         <f>SUM('BATS 2023'!AA11,'BATS 2023'!AA14,'BATS 2023'!AA17)</f>
-        <v>702</v>
+        <v>44</v>
       </c>
       <c r="O20" t="s">
         <v>42</v>
@@ -3305,47 +3305,47 @@
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="55"/>
-        <v>-846</v>
+        <v>-406</v>
       </c>
       <c r="AD20">
         <f t="shared" si="45"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE20">
         <f t="shared" si="46"/>
-        <v>-26</v>
+        <v>-4</v>
       </c>
       <c r="AF20">
         <f t="shared" si="47"/>
-        <v>-38</v>
+        <v>-16</v>
       </c>
       <c r="AG20">
         <f t="shared" si="48"/>
-        <v>-714</v>
+        <v>-228</v>
       </c>
       <c r="AH20">
         <f t="shared" si="49"/>
-        <v>-226</v>
+        <v>-102</v>
       </c>
       <c r="AI20">
         <f t="shared" si="50"/>
-        <v>-576</v>
+        <v>-134</v>
       </c>
       <c r="AJ20">
         <f t="shared" si="51"/>
-        <v>-430</v>
+        <v>-100</v>
       </c>
       <c r="AK20">
         <f t="shared" si="52"/>
-        <v>-58</v>
+        <v>-40</v>
       </c>
       <c r="AL20">
         <f t="shared" si="53"/>
-        <v>-22</v>
+        <v>-10</v>
       </c>
       <c r="AM20" s="7">
         <f t="shared" si="54"/>
-        <v>-702</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="C21" s="46">
         <f>SUM('BATS 2023'!Q15,'BATS 2023'!Q18)</f>
-        <v>348</v>
+        <v>170</v>
       </c>
       <c r="D21" s="47">
         <f>SUM('BATS 2023'!R15,'BATS 2023'!R18)</f>
@@ -3362,39 +3362,39 @@
       </c>
       <c r="E21" s="47">
         <f>SUM('BATS 2023'!S15,'BATS 2023'!S18)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="47">
         <f>SUM('BATS 2023'!T15,'BATS 2023'!T18)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G21" s="47">
         <f>SUM('BATS 2023'!U15,'BATS 2023'!U18)</f>
-        <v>270</v>
+        <v>66</v>
       </c>
       <c r="H21" s="47">
         <f>SUM('BATS 2023'!V15,'BATS 2023'!V18)</f>
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I21" s="47">
         <f>SUM('BATS 2023'!W15,'BATS 2023'!W18)</f>
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="J21" s="47">
         <f>SUM('BATS 2023'!X15,'BATS 2023'!X18)</f>
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="K21" s="47">
         <f>SUM('BATS 2023'!Y15,'BATS 2023'!Y18)</f>
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="L21" s="47">
         <f>SUM('BATS 2023'!Z15,'BATS 2023'!Z18)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M21" s="48">
         <f>SUM('BATS 2023'!AA15,'BATS 2023'!AA18)</f>
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="O21" t="s">
         <v>43</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC21" s="6">
         <f>P21-C21</f>
-        <v>-348</v>
+        <v>-170</v>
       </c>
       <c r="AD21">
         <f t="shared" ref="AD21:AD23" si="56">Q21-D21</f>
@@ -3456,39 +3456,39 @@
       </c>
       <c r="AE21">
         <f t="shared" ref="AE21:AE23" si="57">R21-E21</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF21">
         <f t="shared" ref="AF21:AF23" si="58">S21-F21</f>
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AG21">
         <f t="shared" ref="AG21:AG23" si="59">T21-G21</f>
-        <v>-270</v>
+        <v>-66</v>
       </c>
       <c r="AH21">
         <f t="shared" ref="AH21:AH23" si="60">U21-H21</f>
-        <v>-64</v>
+        <v>-20</v>
       </c>
       <c r="AI21">
         <f t="shared" ref="AI21:AI23" si="61">V21-I21</f>
-        <v>-194</v>
+        <v>-56</v>
       </c>
       <c r="AJ21">
         <f t="shared" ref="AJ21:AJ23" si="62">W21-J21</f>
-        <v>-156</v>
+        <v>-42</v>
       </c>
       <c r="AK21">
         <f t="shared" ref="AK21:AK23" si="63">X21-K21</f>
-        <v>-38</v>
+        <v>-14</v>
       </c>
       <c r="AL21">
         <f t="shared" ref="AL21:AL23" si="64">Y21-L21</f>
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AM21" s="7">
         <f t="shared" ref="AM21:AM23" si="65">Z21-M21</f>
-        <v>-92</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="C22" s="49">
         <f>'BATS 2023'!Q19</f>
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="D22" s="50">
         <f>'BATS 2023'!R19</f>
@@ -3505,39 +3505,39 @@
       </c>
       <c r="E22" s="50">
         <f>'BATS 2023'!S19</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="50">
         <f>'BATS 2023'!T19</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G22" s="50">
         <f>'BATS 2023'!U19</f>
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="H22" s="50">
         <f>'BATS 2023'!V19</f>
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="I22" s="50">
         <f>'BATS 2023'!W19</f>
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="J22" s="50">
         <f>'BATS 2023'!X19</f>
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="K22" s="50">
         <f>'BATS 2023'!Y19</f>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L22" s="50">
         <f>'BATS 2023'!Z19</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M22" s="51">
         <f>'BATS 2023'!AA19</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O22" t="s">
         <v>38</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC22" s="8">
         <f>P22-C22</f>
-        <v>-154</v>
+        <v>-72</v>
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="56"/>
@@ -3599,39 +3599,39 @@
       </c>
       <c r="AE22" s="9">
         <f t="shared" si="57"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="9">
         <f t="shared" si="58"/>
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="9">
         <f t="shared" si="59"/>
-        <v>-100</v>
+        <v>-28</v>
       </c>
       <c r="AH22" s="9">
         <f t="shared" si="60"/>
-        <v>-42</v>
+        <v>-4</v>
       </c>
       <c r="AI22" s="9">
         <f t="shared" si="61"/>
-        <v>-98</v>
+        <v>-18</v>
       </c>
       <c r="AJ22" s="9">
         <f t="shared" si="62"/>
-        <v>-56</v>
+        <v>-10</v>
       </c>
       <c r="AK22" s="9">
         <f t="shared" si="63"/>
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="AL22" s="9">
         <f t="shared" si="64"/>
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="AM22" s="10">
         <f t="shared" si="65"/>
-        <v>-50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -3640,47 +3640,47 @@
       </c>
       <c r="C23" s="52">
         <f>SUM(C16:C22)</f>
-        <v>27204</v>
+        <v>14800</v>
       </c>
       <c r="D23" s="52">
         <f t="shared" ref="D23:M23" si="66">SUM(D16:D22)</f>
-        <v>582</v>
+        <v>338</v>
       </c>
       <c r="E23" s="52">
         <f t="shared" si="66"/>
-        <v>2650</v>
+        <v>746</v>
       </c>
       <c r="F23" s="52">
         <f t="shared" si="66"/>
-        <v>12970</v>
+        <v>3782</v>
       </c>
       <c r="G23" s="52">
         <f t="shared" si="66"/>
-        <v>21380</v>
+        <v>6988</v>
       </c>
       <c r="H23" s="52">
         <f t="shared" si="66"/>
-        <v>11018</v>
+        <v>4806</v>
       </c>
       <c r="I23" s="52">
         <f t="shared" si="66"/>
-        <v>15344</v>
+        <v>5202</v>
       </c>
       <c r="J23" s="52">
         <f t="shared" si="66"/>
-        <v>34292</v>
+        <v>13174</v>
       </c>
       <c r="K23" s="52">
         <f t="shared" si="66"/>
-        <v>4334</v>
+        <v>1758</v>
       </c>
       <c r="L23" s="52">
         <f t="shared" si="66"/>
-        <v>4048</v>
+        <v>2396</v>
       </c>
       <c r="M23" s="52">
         <f t="shared" si="66"/>
-        <v>46906</v>
+        <v>8700</v>
       </c>
       <c r="O23" t="s">
         <v>39</v>
@@ -3734,47 +3734,47 @@
       </c>
       <c r="AC23">
         <f t="shared" ref="AC23" si="77">P23-C23</f>
-        <v>-27204</v>
+        <v>-14800</v>
       </c>
       <c r="AD23">
         <f t="shared" si="56"/>
-        <v>-582</v>
+        <v>-338</v>
       </c>
       <c r="AE23">
         <f t="shared" si="57"/>
-        <v>-2650</v>
+        <v>-746</v>
       </c>
       <c r="AF23">
         <f t="shared" si="58"/>
-        <v>-12970</v>
+        <v>-3782</v>
       </c>
       <c r="AG23">
         <f t="shared" si="59"/>
-        <v>-21380</v>
+        <v>-6988</v>
       </c>
       <c r="AH23">
         <f t="shared" si="60"/>
-        <v>-11018</v>
+        <v>-4806</v>
       </c>
       <c r="AI23">
         <f t="shared" si="61"/>
-        <v>-15344</v>
+        <v>-5202</v>
       </c>
       <c r="AJ23">
         <f t="shared" si="62"/>
-        <v>-34292</v>
+        <v>-13174</v>
       </c>
       <c r="AK23">
         <f t="shared" si="63"/>
-        <v>-4334</v>
+        <v>-1758</v>
       </c>
       <c r="AL23">
         <f t="shared" si="64"/>
-        <v>-4048</v>
+        <v>-2396</v>
       </c>
       <c r="AM23">
         <f t="shared" si="65"/>
-        <v>-46906</v>
+        <v>-8700</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3931,47 +3931,47 @@
       </c>
       <c r="C27" s="53">
         <f t="shared" ref="C27:M27" si="78">C4/C$8</f>
-        <v>0.71114541979120716</v>
+        <v>0.72324324324324329</v>
       </c>
       <c r="D27" s="54">
         <f t="shared" si="78"/>
-        <v>0.75601374570446733</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="E27" s="54">
         <f t="shared" si="78"/>
-        <v>0.8935849056603774</v>
+        <v>0.90616621983914214</v>
       </c>
       <c r="F27" s="54">
         <f t="shared" si="78"/>
-        <v>0.90624518118735542</v>
+        <v>0.89899524061343206</v>
       </c>
       <c r="G27" s="54">
         <f t="shared" si="78"/>
-        <v>0.60383536014967254</v>
+        <v>0.62650257584430458</v>
       </c>
       <c r="H27" s="54">
         <f t="shared" si="78"/>
-        <v>0.75549101470321289</v>
+        <v>0.7752808988764045</v>
       </c>
       <c r="I27" s="54">
         <f t="shared" si="78"/>
-        <v>0.62552137643378525</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J27" s="54">
         <f t="shared" si="78"/>
-        <v>0.81453400209961502</v>
+        <v>0.85243661758008193</v>
       </c>
       <c r="K27" s="54">
         <f t="shared" si="78"/>
-        <v>0.79603137978772498</v>
+        <v>0.75881683731513083</v>
       </c>
       <c r="L27" s="54">
         <f t="shared" si="78"/>
-        <v>0.87944664031620556</v>
+        <v>0.88731218697829717</v>
       </c>
       <c r="M27" s="55">
         <f t="shared" si="78"/>
-        <v>0.76907005500362424</v>
+        <v>0.84344827586206894</v>
       </c>
       <c r="O27" t="s">
         <v>31</v>
@@ -4074,47 +4074,47 @@
       </c>
       <c r="C28" s="56">
         <f t="shared" ref="C28:M28" si="90">C5/C$8</f>
-        <v>0.17203352448169387</v>
+        <v>0.16567567567567568</v>
       </c>
       <c r="D28" s="57">
         <f t="shared" si="90"/>
-        <v>0.16151202749140894</v>
+        <v>0.20118343195266272</v>
       </c>
       <c r="E28" s="57">
         <f t="shared" si="90"/>
-        <v>8.3773584905660378E-2</v>
+        <v>8.0428954423592491E-2</v>
       </c>
       <c r="F28" s="57">
         <f t="shared" si="90"/>
-        <v>6.9082498072474949E-2</v>
+        <v>7.4563722897937598E-2</v>
       </c>
       <c r="G28" s="57">
         <f t="shared" si="90"/>
-        <v>0.22329279700654817</v>
+        <v>0.21923297080709789</v>
       </c>
       <c r="H28" s="57">
         <f t="shared" si="90"/>
-        <v>0.15465601742603013</v>
+        <v>0.15397419891801914</v>
       </c>
       <c r="I28" s="57">
         <f t="shared" si="90"/>
-        <v>0.2068561001042753</v>
+        <v>0.20261437908496732</v>
       </c>
       <c r="J28" s="57">
         <f t="shared" si="90"/>
-        <v>0.10346436486644116</v>
+        <v>8.8052224077728863E-2</v>
       </c>
       <c r="K28" s="57">
         <f t="shared" si="90"/>
-        <v>0.11075219197046608</v>
+        <v>0.13196814562002276</v>
       </c>
       <c r="L28" s="57">
         <f t="shared" si="90"/>
-        <v>8.4980237154150193E-2</v>
+        <v>8.1803005008347252E-2</v>
       </c>
       <c r="M28" s="58">
         <f t="shared" si="90"/>
-        <v>0.14799812390738926</v>
+        <v>0.11586206896551725</v>
       </c>
       <c r="O28" t="s">
         <v>32</v>
@@ -4217,47 +4217,47 @@
       </c>
       <c r="C29" s="56">
         <f t="shared" ref="C29:M29" si="93">C6/C$8</f>
-        <v>6.8445816791648281E-2</v>
+        <v>6.7837837837837839E-2</v>
       </c>
       <c r="D29" s="57">
         <f t="shared" si="93"/>
-        <v>4.1237113402061855E-2</v>
+        <v>6.5088757396449703E-2</v>
       </c>
       <c r="E29" s="57">
         <f t="shared" si="93"/>
-        <v>1.6603773584905661E-2</v>
+        <v>1.0723860589812333E-2</v>
       </c>
       <c r="F29" s="57">
         <f t="shared" si="93"/>
-        <v>1.7579028527370855E-2</v>
+        <v>1.8508725542041249E-2</v>
       </c>
       <c r="G29" s="57">
         <f t="shared" si="93"/>
-        <v>9.5790458372310566E-2</v>
+        <v>8.5002862049227246E-2</v>
       </c>
       <c r="H29" s="57">
         <f t="shared" si="93"/>
-        <v>5.4274823016881468E-2</v>
+        <v>4.2863087806908035E-2</v>
       </c>
       <c r="I29" s="57">
         <f t="shared" si="93"/>
-        <v>8.5114702815432736E-2</v>
+        <v>6.9204152249134954E-2</v>
       </c>
       <c r="J29" s="57">
         <f t="shared" si="93"/>
-        <v>5.1207278665577977E-2</v>
+        <v>3.8105359040534387E-2</v>
       </c>
       <c r="K29" s="57">
         <f t="shared" si="93"/>
-        <v>4.8915551453622523E-2</v>
+        <v>6.4846416382252553E-2</v>
       </c>
       <c r="L29" s="57">
         <f t="shared" si="93"/>
-        <v>2.0256916996047432E-2</v>
+        <v>1.6694490818030049E-2</v>
       </c>
       <c r="M29" s="58">
         <f t="shared" si="93"/>
-        <v>5.585639363834051E-2</v>
+        <v>3.2643678160919537E-2</v>
       </c>
       <c r="O29" t="s">
         <v>33</v>
@@ -4360,47 +4360,47 @@
       </c>
       <c r="C30" s="59">
         <f t="shared" ref="C30:M30" si="96">C7/C$8</f>
-        <v>4.8375238935450669E-2</v>
+        <v>4.3243243243243246E-2</v>
       </c>
       <c r="D30" s="60">
         <f t="shared" si="96"/>
-        <v>4.1237113402061855E-2</v>
+        <v>4.142011834319527E-2</v>
       </c>
       <c r="E30" s="60">
         <f t="shared" si="96"/>
-        <v>6.0377358490566035E-3</v>
+        <v>2.6809651474530832E-3</v>
       </c>
       <c r="F30" s="60">
         <f t="shared" si="96"/>
-        <v>7.0932922127987666E-3</v>
+        <v>7.9323109465891072E-3</v>
       </c>
       <c r="G30" s="60">
         <f t="shared" si="96"/>
-        <v>7.7081384471468659E-2</v>
+        <v>6.9261591299370345E-2</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="96"/>
-        <v>3.5578144853875476E-2</v>
+        <v>2.7881814398668332E-2</v>
       </c>
       <c r="I30" s="60">
         <f t="shared" si="96"/>
-        <v>8.2507820646506774E-2</v>
+        <v>6.1514801999231067E-2</v>
       </c>
       <c r="J30" s="60">
         <f t="shared" si="96"/>
-        <v>3.0794354368365799E-2</v>
+        <v>2.1405799301654774E-2</v>
       </c>
       <c r="K30" s="60">
         <f t="shared" si="96"/>
-        <v>4.4300876788186436E-2</v>
+        <v>4.4368600682593858E-2</v>
       </c>
       <c r="L30" s="60">
         <f t="shared" si="96"/>
-        <v>1.5316205533596838E-2</v>
+        <v>1.4190317195325543E-2</v>
       </c>
       <c r="M30" s="61">
         <f t="shared" si="96"/>
-        <v>2.7075427450645971E-2</v>
+        <v>8.0459770114942528E-3</v>
       </c>
       <c r="O30" t="s">
         <v>34</v>
@@ -4681,47 +4681,47 @@
       </c>
       <c r="C33" s="53">
         <f t="shared" ref="C33:M33" si="100">C10/C$14</f>
-        <v>0.65571239523599467</v>
+        <v>0.66729729729729725</v>
       </c>
       <c r="D33" s="54">
         <f t="shared" si="100"/>
-        <v>0.73883161512027495</v>
+        <v>0.7100591715976331</v>
       </c>
       <c r="E33" s="54">
         <f t="shared" si="100"/>
-        <v>0.79320754716981134</v>
+        <v>0.81501340482573725</v>
       </c>
       <c r="F33" s="54">
         <f t="shared" si="100"/>
-        <v>0.89267540478026219</v>
+        <v>0.90269698572184032</v>
       </c>
       <c r="G33" s="54">
         <f t="shared" si="100"/>
-        <v>0.72039289055191769</v>
+        <v>0.73554665140240416</v>
       </c>
       <c r="H33" s="54">
         <f t="shared" si="100"/>
-        <v>0.70012706480304954</v>
+        <v>0.70037453183520604</v>
       </c>
       <c r="I33" s="54">
         <f t="shared" si="100"/>
-        <v>0.73553180396246087</v>
+        <v>0.78008458285274895</v>
       </c>
       <c r="J33" s="54">
         <f t="shared" si="100"/>
-        <v>0.84771958474279718</v>
+        <v>0.87384241688173681</v>
       </c>
       <c r="K33" s="54">
         <f t="shared" si="100"/>
-        <v>0.81587448084910019</v>
+        <v>0.79180887372013653</v>
       </c>
       <c r="L33" s="54">
         <f t="shared" si="100"/>
-        <v>0.91501976284584985</v>
+        <v>0.91819699499165275</v>
       </c>
       <c r="M33" s="55">
         <f t="shared" si="100"/>
-        <v>0.79623075939112264</v>
+        <v>0.86620689655172411</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
@@ -4824,47 +4824,47 @@
       </c>
       <c r="C34" s="56">
         <f t="shared" ref="C34:M34" si="112">C11/C$14</f>
-        <v>0.21680635200705778</v>
+        <v>0.21189189189189189</v>
       </c>
       <c r="D34" s="57">
         <f t="shared" si="112"/>
-        <v>0.18900343642611683</v>
+        <v>0.20118343195266272</v>
       </c>
       <c r="E34" s="57">
         <f t="shared" si="112"/>
-        <v>0.14037735849056604</v>
+        <v>0.13136729222520108</v>
       </c>
       <c r="F34" s="57">
         <f t="shared" si="112"/>
-        <v>9.1904394757131844E-2</v>
+        <v>8.5668958223162353E-2</v>
       </c>
       <c r="G34" s="57">
         <f t="shared" si="112"/>
-        <v>0.18774555659494854</v>
+        <v>0.18116771608471666</v>
       </c>
       <c r="H34" s="57">
         <f t="shared" si="112"/>
-        <v>0.20384824832092938</v>
+        <v>0.20307948397836037</v>
       </c>
       <c r="I34" s="57">
         <f t="shared" si="112"/>
-        <v>0.17179353493222108</v>
+        <v>0.15378700499807765</v>
       </c>
       <c r="J34" s="57">
         <f t="shared" si="112"/>
-        <v>0.10737198180333606</v>
+        <v>9.594656140883559E-2</v>
       </c>
       <c r="K34" s="57">
         <f t="shared" si="112"/>
-        <v>0.12736502076603601</v>
+        <v>0.14106939704209329</v>
       </c>
       <c r="L34" s="57">
         <f t="shared" si="112"/>
-        <v>6.768774703557312E-2</v>
+        <v>6.8447412353923209E-2</v>
       </c>
       <c r="M34" s="58">
         <f t="shared" si="112"/>
-        <v>0.14927727796017567</v>
+        <v>9.5402298850574718E-2</v>
       </c>
       <c r="O34" t="s">
         <v>28</v>
@@ -4967,47 +4967,47 @@
       </c>
       <c r="C35" s="56">
         <f t="shared" ref="C35:M35" si="115">C12/C$14</f>
-        <v>7.7562123217173942E-2</v>
+        <v>7.4594594594594596E-2</v>
       </c>
       <c r="D35" s="57">
         <f t="shared" si="115"/>
-        <v>5.8419243986254296E-2</v>
+        <v>6.5088757396449703E-2</v>
       </c>
       <c r="E35" s="57">
         <f t="shared" si="115"/>
-        <v>4.5283018867924525E-2</v>
+        <v>3.4852546916890083E-2</v>
       </c>
       <c r="F35" s="57">
         <f t="shared" si="115"/>
-        <v>1.0023130300693909E-2</v>
+        <v>6.345848757271285E-3</v>
       </c>
       <c r="G35" s="57">
         <f t="shared" si="115"/>
-        <v>5.8933582787652011E-2</v>
+        <v>5.6382369776760158E-2</v>
       </c>
       <c r="H35" s="57">
         <f t="shared" si="115"/>
-        <v>5.3911780722454165E-2</v>
+        <v>5.6179775280898875E-2</v>
       </c>
       <c r="I35" s="57">
         <f t="shared" si="115"/>
-        <v>5.213764337851929E-2</v>
+        <v>3.8831218762014612E-2</v>
       </c>
       <c r="J35" s="57">
         <f t="shared" si="115"/>
-        <v>2.980286947392978E-2</v>
+        <v>2.0950356763321694E-2</v>
       </c>
       <c r="K35" s="57">
         <f t="shared" si="115"/>
-        <v>3.3225657591139823E-2</v>
+        <v>3.981797497155859E-2</v>
       </c>
       <c r="L35" s="57">
         <f t="shared" si="115"/>
-        <v>1.1363636363636364E-2</v>
+        <v>8.3472454090150246E-3</v>
       </c>
       <c r="M35" s="58">
         <f t="shared" si="115"/>
-        <v>3.9525860231100496E-2</v>
+        <v>3.1494252873563215E-2</v>
       </c>
       <c r="O35" t="s">
         <v>29</v>
@@ -5110,47 +5110,47 @@
       </c>
       <c r="C36" s="59">
         <f t="shared" ref="C36:M36" si="118">C13/C$14</f>
-        <v>4.9919129539773566E-2</v>
+        <v>4.6216216216216216E-2</v>
       </c>
       <c r="D36" s="60">
         <f t="shared" si="118"/>
-        <v>1.3745704467353952E-2</v>
+        <v>2.3668639053254437E-2</v>
       </c>
       <c r="E36" s="60">
         <f t="shared" si="118"/>
-        <v>2.1132075471698115E-2</v>
+        <v>1.876675603217158E-2</v>
       </c>
       <c r="F36" s="60">
         <f t="shared" si="118"/>
-        <v>5.3970701619121047E-3</v>
+        <v>5.2882072977260709E-3</v>
       </c>
       <c r="G36" s="60">
         <f t="shared" si="118"/>
-        <v>3.292797006548176E-2</v>
+        <v>2.6903262736119062E-2</v>
       </c>
       <c r="H36" s="60">
         <f t="shared" si="118"/>
-        <v>4.2112906153566894E-2</v>
+        <v>4.0366208905534745E-2</v>
       </c>
       <c r="I36" s="60">
         <f t="shared" si="118"/>
-        <v>4.0537017726798748E-2</v>
+        <v>2.7297193387158785E-2</v>
       </c>
       <c r="J36" s="60">
         <f t="shared" si="118"/>
-        <v>1.5105563979937012E-2</v>
+        <v>9.2606649461059662E-3</v>
       </c>
       <c r="K36" s="60">
         <f t="shared" si="118"/>
-        <v>2.3534840793724043E-2</v>
+        <v>2.7303754266211604E-2</v>
       </c>
       <c r="L36" s="60">
         <f t="shared" si="118"/>
-        <v>5.9288537549407111E-3</v>
+        <v>5.008347245409015E-3</v>
       </c>
       <c r="M36" s="61">
         <f t="shared" si="118"/>
-        <v>1.496610241760116E-2</v>
+        <v>6.8965517241379309E-3</v>
       </c>
       <c r="O36" t="s">
         <v>30</v>
@@ -5431,47 +5431,47 @@
       </c>
       <c r="C39" s="53">
         <f t="shared" ref="C39:M39" si="122">C16/C$23</f>
-        <v>0.49757388619320686</v>
+        <v>0.51</v>
       </c>
       <c r="D39" s="54">
         <f t="shared" si="122"/>
-        <v>0.56357388316151202</v>
+        <v>0.51479289940828399</v>
       </c>
       <c r="E39" s="54">
         <f t="shared" si="122"/>
-        <v>0.73056603773584905</v>
+        <v>0.7533512064343163</v>
       </c>
       <c r="F39" s="54">
         <f t="shared" si="122"/>
-        <v>0.81958365458750959</v>
+        <v>0.8212585933368588</v>
       </c>
       <c r="G39" s="54">
         <f t="shared" si="122"/>
-        <v>0.46155285313376987</v>
+        <v>0.49198626216370922</v>
       </c>
       <c r="H39" s="54">
         <f t="shared" si="122"/>
-        <v>0.54492648393537846</v>
+        <v>0.55347482313774443</v>
       </c>
       <c r="I39" s="54">
         <f t="shared" si="122"/>
-        <v>0.49687174139728885</v>
+        <v>0.55594002306805079</v>
       </c>
       <c r="J39" s="54">
         <f t="shared" si="122"/>
-        <v>0.72022629184649478</v>
+        <v>0.76954607560346133</v>
       </c>
       <c r="K39" s="54">
         <f t="shared" si="122"/>
-        <v>0.68158744808491001</v>
+        <v>0.64050056882821393</v>
       </c>
       <c r="L39" s="54">
         <f t="shared" si="122"/>
-        <v>0.8236166007905138</v>
+        <v>0.82721202003338901</v>
       </c>
       <c r="M39" s="55">
         <f t="shared" si="122"/>
-        <v>0.63927855711422843</v>
+        <v>0.74528735632183907</v>
       </c>
       <c r="O39" t="s">
         <v>41</v>
@@ -5574,47 +5574,47 @@
       </c>
       <c r="C40" s="56">
         <f t="shared" ref="C40:M40" si="134">C17/C$23</f>
-        <v>0.23937656227025436</v>
+        <v>0.24013513513513512</v>
       </c>
       <c r="D40" s="57">
         <f t="shared" si="134"/>
-        <v>0.28522336769759449</v>
+        <v>0.29585798816568049</v>
       </c>
       <c r="E40" s="57">
         <f t="shared" si="134"/>
-        <v>0.16679245283018868</v>
+        <v>0.16621983914209115</v>
       </c>
       <c r="F40" s="57">
         <f t="shared" si="134"/>
-        <v>0.13138010794140323</v>
+        <v>0.13114754098360656</v>
       </c>
       <c r="G40" s="57">
         <f t="shared" si="134"/>
-        <v>0.25191768007483628</v>
+        <v>0.24785346307956496</v>
       </c>
       <c r="H40" s="57">
         <f t="shared" si="134"/>
-        <v>0.24269377382465057</v>
+        <v>0.25384935497295047</v>
       </c>
       <c r="I40" s="57">
         <f t="shared" si="134"/>
-        <v>0.22445255474452555</v>
+        <v>0.22529796232218377</v>
       </c>
       <c r="J40" s="57">
         <f t="shared" si="134"/>
-        <v>0.13834130409424938</v>
+        <v>0.1255503264004858</v>
       </c>
       <c r="K40" s="57">
         <f t="shared" si="134"/>
-        <v>0.15597600369173972</v>
+        <v>0.16723549488054607</v>
       </c>
       <c r="L40" s="57">
         <f t="shared" si="134"/>
-        <v>0.11709486166007906</v>
+        <v>0.11769616026711185</v>
       </c>
       <c r="M40" s="58">
         <f t="shared" si="134"/>
-        <v>0.1979704089029122</v>
+        <v>0.16229885057471263</v>
       </c>
       <c r="O40" t="s">
         <v>35</v>
@@ -5717,47 +5717,47 @@
       </c>
       <c r="C41" s="56">
         <f t="shared" ref="C41:M41" si="137">C18/C$23</f>
-        <v>0.12645199235406557</v>
+        <v>0.12391891891891892</v>
       </c>
       <c r="D41" s="57">
         <f t="shared" si="137"/>
-        <v>6.8728522336769765E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="E41" s="57">
         <f t="shared" si="137"/>
-        <v>5.8867924528301883E-2</v>
+        <v>4.5576407506702415E-2</v>
       </c>
       <c r="F41" s="57">
         <f t="shared" si="137"/>
-        <v>3.130300693909021E-2</v>
+        <v>2.8556319407720784E-2</v>
       </c>
       <c r="G41" s="57">
         <f t="shared" si="137"/>
-        <v>0.13367633302151544</v>
+        <v>0.12020606754436176</v>
       </c>
       <c r="H41" s="57">
         <f t="shared" si="137"/>
-        <v>0.11544744962788164</v>
+        <v>0.10403662089055347</v>
       </c>
       <c r="I41" s="57">
         <f t="shared" si="137"/>
-        <v>0.12017726798748697</v>
+        <v>0.10034602076124567</v>
       </c>
       <c r="J41" s="57">
         <f t="shared" si="137"/>
-        <v>7.8618919864691467E-2</v>
+        <v>6.2395627751632002E-2</v>
       </c>
       <c r="K41" s="57">
         <f t="shared" si="137"/>
-        <v>8.0756806645131518E-2</v>
+        <v>0.10238907849829351</v>
       </c>
       <c r="L41" s="57">
         <f t="shared" si="137"/>
-        <v>3.2608695652173912E-2</v>
+        <v>3.1719532554257093E-2</v>
       </c>
       <c r="M41" s="58">
         <f t="shared" si="137"/>
-        <v>9.4145738285080799E-2</v>
+        <v>6.3908045977011496E-2</v>
       </c>
       <c r="O41" t="s">
         <v>36</v>
@@ -5860,47 +5860,47 @@
       </c>
       <c r="C42" s="56">
         <f t="shared" ref="C42:M42" si="140">C19/C$23</f>
-        <v>8.7046022643728863E-2</v>
+        <v>8.2162162162162156E-2</v>
       </c>
       <c r="D42" s="57">
         <f t="shared" si="140"/>
-        <v>6.1855670103092786E-2</v>
+        <v>8.2840236686390539E-2</v>
       </c>
       <c r="E42" s="57">
         <f t="shared" si="140"/>
-        <v>3.2452830188679248E-2</v>
+        <v>2.9490616621983913E-2</v>
       </c>
       <c r="F42" s="57">
         <f t="shared" si="140"/>
-        <v>1.3261372397841172E-2</v>
+        <v>1.4806980433632998E-2</v>
       </c>
       <c r="G42" s="57">
         <f t="shared" si="140"/>
-        <v>0.10215154349859681</v>
+        <v>9.3875214653692043E-2</v>
       </c>
       <c r="H42" s="57">
         <f t="shared" si="140"/>
-        <v>6.6799782174623346E-2</v>
+        <v>6.2421972534332085E-2</v>
       </c>
       <c r="I42" s="57">
         <f t="shared" si="140"/>
-        <v>0.10192909280500521</v>
+        <v>7.8431372549019607E-2</v>
       </c>
       <c r="J42" s="57">
         <f t="shared" si="140"/>
-        <v>4.4091916481978306E-2</v>
+        <v>3.0970092606649461E-2</v>
       </c>
       <c r="K42" s="57">
         <f t="shared" si="140"/>
-        <v>5.5376095985233041E-2</v>
+        <v>5.3469852104664393E-2</v>
       </c>
       <c r="L42" s="57">
         <f t="shared" si="140"/>
-        <v>1.6304347826086956E-2</v>
+        <v>1.8363939899833055E-2</v>
       </c>
       <c r="M42" s="58">
         <f t="shared" si="140"/>
-        <v>5.0611862021916171E-2</v>
+        <v>2.1609195402298852E-2</v>
       </c>
       <c r="O42" t="s">
         <v>37</v>
@@ -6003,47 +6003,47 @@
       </c>
       <c r="C43" s="56">
         <f t="shared" ref="C43:M43" si="142">C20/C$23</f>
-        <v>3.1098367887075429E-2</v>
+        <v>2.7432432432432433E-2</v>
       </c>
       <c r="D43" s="57">
         <f t="shared" si="142"/>
-        <v>3.4364261168384879E-3</v>
+        <v>0</v>
       </c>
       <c r="E43" s="57">
         <f t="shared" si="142"/>
-        <v>9.8113207547169817E-3</v>
+        <v>5.3619302949061663E-3</v>
       </c>
       <c r="F43" s="57">
         <f t="shared" si="142"/>
-        <v>2.9298380878951427E-3</v>
+        <v>4.2305658381808567E-3</v>
       </c>
       <c r="G43" s="57">
         <f t="shared" si="142"/>
-        <v>3.3395696913002808E-2</v>
+        <v>3.2627361190612478E-2</v>
       </c>
       <c r="H43" s="57">
         <f t="shared" si="142"/>
-        <v>2.0511889635142493E-2</v>
+        <v>2.1223470661672909E-2</v>
       </c>
       <c r="I43" s="57">
         <f t="shared" si="142"/>
-        <v>3.7539103232533892E-2</v>
+        <v>2.5759323337178008E-2</v>
       </c>
       <c r="J43" s="57">
         <f t="shared" si="142"/>
-        <v>1.2539367782573195E-2</v>
+        <v>7.5907089722180056E-3</v>
       </c>
       <c r="K43" s="57">
         <f t="shared" si="142"/>
-        <v>1.3382556529764651E-2</v>
+        <v>2.2753128555176336E-2</v>
       </c>
       <c r="L43" s="57">
         <f t="shared" si="142"/>
-        <v>5.434782608695652E-3</v>
+        <v>4.1736227045075123E-3</v>
       </c>
       <c r="M43" s="58">
         <f t="shared" si="142"/>
-        <v>1.496610241760116E-2</v>
+        <v>5.0574712643678158E-3</v>
       </c>
       <c r="O43" t="s">
         <v>42</v>
@@ -6146,47 +6146,47 @@
       </c>
       <c r="C44" s="56">
         <f t="shared" ref="C44:M44" si="144">C21/C$23</f>
-        <v>1.2792236435818262E-2</v>
+        <v>1.1486486486486487E-2</v>
       </c>
       <c r="D44" s="57">
         <f t="shared" si="144"/>
-        <v>1.0309278350515464E-2</v>
+        <v>1.7751479289940829E-2</v>
       </c>
       <c r="E44" s="57">
         <f t="shared" si="144"/>
-        <v>7.5471698113207543E-4</v>
+        <v>0</v>
       </c>
       <c r="F44" s="57">
         <f t="shared" si="144"/>
-        <v>1.0794140323824211E-3</v>
+        <v>0</v>
       </c>
       <c r="G44" s="57">
         <f t="shared" si="144"/>
-        <v>1.2628624883068288E-2</v>
+        <v>9.4447624499141378E-3</v>
       </c>
       <c r="H44" s="57">
         <f t="shared" si="144"/>
-        <v>5.8086767108368126E-3</v>
+        <v>4.1614648356221393E-3</v>
       </c>
       <c r="I44" s="57">
         <f t="shared" si="144"/>
-        <v>1.2643378519290928E-2</v>
+        <v>1.0765090349865437E-2</v>
       </c>
       <c r="J44" s="57">
         <f t="shared" si="144"/>
-        <v>4.5491659862358568E-3</v>
+        <v>3.188097768331562E-3</v>
       </c>
       <c r="K44" s="57">
         <f t="shared" si="144"/>
-        <v>8.7678818643285653E-3</v>
+        <v>7.9635949943117172E-3</v>
       </c>
       <c r="L44" s="57">
         <f t="shared" si="144"/>
-        <v>2.9644268774703555E-3</v>
+        <v>0</v>
       </c>
       <c r="M44" s="58">
         <f t="shared" si="144"/>
-        <v>1.9613695476058501E-3</v>
+        <v>1.8390804597701149E-3</v>
       </c>
       <c r="O44" t="s">
         <v>43</v>
@@ -6289,47 +6289,47 @@
       </c>
       <c r="C45" s="59">
         <f t="shared" ref="C45:M45" si="146">C22/C$23</f>
-        <v>5.6609322158506104E-3</v>
+        <v>4.8648648648648646E-3</v>
       </c>
       <c r="D45" s="60">
         <f t="shared" si="146"/>
-        <v>6.8728522336769758E-3</v>
+        <v>1.1834319526627219E-2</v>
       </c>
       <c r="E45" s="60">
         <f t="shared" si="146"/>
-        <v>7.5471698113207543E-4</v>
+        <v>0</v>
       </c>
       <c r="F45" s="60">
         <f t="shared" si="146"/>
-        <v>4.6260601387818041E-4</v>
+        <v>0</v>
       </c>
       <c r="G45" s="60">
         <f t="shared" si="146"/>
-        <v>4.6772684752104769E-3</v>
+        <v>4.0068689181453924E-3</v>
       </c>
       <c r="H45" s="60">
         <f t="shared" si="146"/>
-        <v>3.8119440914866584E-3</v>
+        <v>8.3229296712442784E-4</v>
       </c>
       <c r="I45" s="60">
         <f t="shared" si="146"/>
-        <v>6.3868613138686131E-3</v>
+        <v>3.4602076124567475E-3</v>
       </c>
       <c r="J45" s="60">
         <f t="shared" si="146"/>
-        <v>1.6330339437769742E-3</v>
+        <v>7.5907089722180047E-4</v>
       </c>
       <c r="K45" s="60">
         <f t="shared" si="146"/>
-        <v>4.1532071988924779E-3</v>
+        <v>5.6882821387940841E-3</v>
       </c>
       <c r="L45" s="60">
         <f t="shared" si="146"/>
-        <v>1.976284584980237E-3</v>
+        <v>8.3472454090150253E-4</v>
       </c>
       <c r="M45" s="61">
         <f t="shared" si="146"/>
-        <v>1.0659617106553532E-3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="s">
         <v>38</v>
@@ -11759,87 +11759,87 @@
         <v>81</v>
       </c>
       <c r="C4" s="40">
-        <v>13536</v>
+        <v>7548</v>
       </c>
       <c r="D4" s="40">
-        <v>328</v>
+        <v>174</v>
       </c>
       <c r="E4" s="40">
-        <v>1936</v>
+        <v>562</v>
       </c>
       <c r="F4" s="40">
-        <v>10630</v>
+        <v>3106</v>
       </c>
       <c r="G4" s="40">
-        <v>9868</v>
+        <v>3438</v>
       </c>
       <c r="H4" s="40">
-        <v>6004</v>
+        <v>2660</v>
       </c>
       <c r="I4" s="40">
-        <v>7624</v>
+        <v>2892</v>
       </c>
       <c r="J4" s="40">
-        <v>24698</v>
+        <v>10138</v>
       </c>
       <c r="K4" s="40">
-        <v>2954</v>
+        <v>1126</v>
       </c>
       <c r="L4" s="40">
-        <v>3334</v>
+        <v>1982</v>
       </c>
       <c r="M4" s="40">
-        <v>29986</v>
+        <v>6484</v>
       </c>
       <c r="N4">
-        <v>110898</v>
+        <v>40110</v>
       </c>
       <c r="P4" t="s">
         <v>11</v>
       </c>
       <c r="Q4" s="41">
         <f>C4</f>
-        <v>13536</v>
+        <v>7548</v>
       </c>
       <c r="R4" s="41">
         <f t="shared" ref="R4:AA6" si="0">D4</f>
-        <v>328</v>
+        <v>174</v>
       </c>
       <c r="S4" s="41">
         <f t="shared" si="0"/>
-        <v>1936</v>
+        <v>562</v>
       </c>
       <c r="T4" s="41">
         <f t="shared" si="0"/>
-        <v>10630</v>
+        <v>3106</v>
       </c>
       <c r="U4" s="41">
         <f t="shared" si="0"/>
-        <v>9868</v>
+        <v>3438</v>
       </c>
       <c r="V4" s="41">
         <f t="shared" si="0"/>
-        <v>6004</v>
+        <v>2660</v>
       </c>
       <c r="W4" s="41">
         <f t="shared" si="0"/>
-        <v>7624</v>
+        <v>2892</v>
       </c>
       <c r="X4" s="41">
         <f t="shared" si="0"/>
-        <v>24698</v>
+        <v>10138</v>
       </c>
       <c r="Y4" s="41">
         <f t="shared" si="0"/>
-        <v>2954</v>
+        <v>1126</v>
       </c>
       <c r="Z4" s="41">
         <f t="shared" si="0"/>
-        <v>3334</v>
+        <v>1982</v>
       </c>
       <c r="AA4" s="41">
         <f t="shared" si="0"/>
-        <v>29986</v>
+        <v>6484</v>
       </c>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.25">
@@ -11847,87 +11847,87 @@
         <v>82</v>
       </c>
       <c r="C5" s="40">
-        <v>3858</v>
+        <v>2112</v>
       </c>
       <c r="D5" s="40">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="E5" s="40">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="F5" s="40">
-        <v>986</v>
+        <v>266</v>
       </c>
       <c r="G5" s="40">
-        <v>2138</v>
+        <v>700</v>
       </c>
       <c r="H5" s="40">
-        <v>1602</v>
+        <v>738</v>
       </c>
       <c r="I5" s="40">
-        <v>1326</v>
+        <v>432</v>
       </c>
       <c r="J5" s="40">
-        <v>2330</v>
+        <v>868</v>
       </c>
       <c r="K5" s="40">
-        <v>364</v>
+        <v>154</v>
       </c>
       <c r="L5" s="40">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="M5" s="40">
-        <v>4514</v>
+        <v>632</v>
       </c>
       <c r="N5">
-        <v>17712</v>
+        <v>6154</v>
       </c>
       <c r="P5" t="s">
         <v>12</v>
       </c>
       <c r="Q5" s="41">
         <f>C5</f>
-        <v>3858</v>
+        <v>2112</v>
       </c>
       <c r="R5" s="41">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="S5" s="41">
         <f t="shared" si="0"/>
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="T5" s="41">
         <f t="shared" si="0"/>
-        <v>986</v>
+        <v>266</v>
       </c>
       <c r="U5" s="41">
         <f t="shared" si="0"/>
-        <v>2138</v>
+        <v>700</v>
       </c>
       <c r="V5" s="41">
         <f t="shared" si="0"/>
-        <v>1602</v>
+        <v>738</v>
       </c>
       <c r="W5" s="41">
         <f t="shared" si="0"/>
-        <v>1326</v>
+        <v>432</v>
       </c>
       <c r="X5" s="41">
         <f t="shared" si="0"/>
-        <v>2330</v>
+        <v>868</v>
       </c>
       <c r="Y5" s="41">
         <f t="shared" si="0"/>
-        <v>364</v>
+        <v>154</v>
       </c>
       <c r="Z5" s="41">
         <f t="shared" si="0"/>
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="AA5" s="41">
         <f t="shared" si="0"/>
-        <v>4514</v>
+        <v>632</v>
       </c>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.25">
@@ -11935,87 +11935,87 @@
         <v>83</v>
       </c>
       <c r="C6" s="40">
-        <v>1188</v>
+        <v>654</v>
       </c>
       <c r="D6" s="40">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" s="40">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="F6" s="40">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="G6" s="40">
-        <v>598</v>
+        <v>172</v>
       </c>
       <c r="H6" s="40">
-        <v>432</v>
+        <v>202</v>
       </c>
       <c r="I6" s="40">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="J6" s="40">
-        <v>612</v>
+        <v>152</v>
       </c>
       <c r="K6" s="40">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="L6" s="40">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M6" s="40">
-        <v>1150</v>
+        <v>196</v>
       </c>
       <c r="N6">
-        <v>4642</v>
+        <v>1546</v>
       </c>
       <c r="P6" t="s">
         <v>13</v>
       </c>
       <c r="Q6" s="41">
         <f>C6</f>
-        <v>1188</v>
+        <v>654</v>
       </c>
       <c r="R6" s="41">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S6" s="41">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="T6" s="41">
         <f t="shared" si="0"/>
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="U6" s="41">
         <f t="shared" si="0"/>
-        <v>598</v>
+        <v>172</v>
       </c>
       <c r="V6" s="41">
         <f t="shared" si="0"/>
-        <v>432</v>
+        <v>202</v>
       </c>
       <c r="W6" s="41">
         <f t="shared" si="0"/>
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="X6" s="41">
         <f t="shared" si="0"/>
-        <v>612</v>
+        <v>152</v>
       </c>
       <c r="Y6" s="41">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="Z6" s="41">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA6" s="41">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
@@ -12023,47 +12023,47 @@
         <v>84</v>
       </c>
       <c r="C7" s="40">
-        <v>440</v>
+        <v>232</v>
       </c>
       <c r="D7" s="40">
         <v>2</v>
       </c>
       <c r="E7" s="40">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F7" s="40">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G7" s="40">
-        <v>198</v>
+        <v>48</v>
       </c>
       <c r="H7" s="40">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="I7" s="40">
-        <v>176</v>
+        <v>42</v>
       </c>
       <c r="J7" s="40">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="K7" s="40">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="L7" s="40">
         <v>4</v>
       </c>
       <c r="M7" s="40">
-        <v>314</v>
+        <v>26</v>
       </c>
       <c r="N7">
-        <v>1576</v>
+        <v>500</v>
       </c>
       <c r="P7" t="s">
         <v>14</v>
       </c>
       <c r="Q7" s="41">
         <f>C7+C8</f>
-        <v>764</v>
+        <v>390</v>
       </c>
       <c r="R7" s="41">
         <f t="shared" ref="R7:AA7" si="1">D7+D8</f>
@@ -12071,39 +12071,39 @@
       </c>
       <c r="S7" s="41">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="T7" s="41">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="U7" s="41">
         <f t="shared" si="1"/>
-        <v>306</v>
+        <v>68</v>
       </c>
       <c r="V7" s="41">
         <f t="shared" si="1"/>
-        <v>286</v>
+        <v>126</v>
       </c>
       <c r="W7" s="41">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>64</v>
       </c>
       <c r="X7" s="41">
         <f t="shared" si="1"/>
-        <v>292</v>
+        <v>72</v>
       </c>
       <c r="Y7" s="41">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="Z7" s="41">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="41">
         <f t="shared" si="1"/>
-        <v>424</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.25">
@@ -12111,87 +12111,87 @@
         <v>85</v>
       </c>
       <c r="C8" s="42">
-        <v>324</v>
+        <v>158</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="42">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F8" s="42">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G8" s="42">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="H8" s="42">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="I8" s="42">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J8" s="42">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="K8" s="42">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L8" s="42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8" s="42">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>928</v>
+        <v>304</v>
       </c>
       <c r="P8" t="s">
         <v>15</v>
       </c>
       <c r="Q8" s="41">
         <f>C9</f>
-        <v>2654</v>
+        <v>1442</v>
       </c>
       <c r="R8" s="41">
         <f t="shared" ref="R8:AA10" si="2">D9</f>
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="S8" s="41">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="T8" s="41">
         <f t="shared" si="2"/>
-        <v>718</v>
+        <v>230</v>
       </c>
       <c r="U8" s="41">
         <f t="shared" si="2"/>
-        <v>3248</v>
+        <v>1032</v>
       </c>
       <c r="V8" s="41">
         <f t="shared" si="2"/>
-        <v>1072</v>
+        <v>482</v>
       </c>
       <c r="W8" s="41">
         <f t="shared" si="2"/>
-        <v>2118</v>
+        <v>740</v>
       </c>
       <c r="X8" s="41">
         <f t="shared" si="2"/>
-        <v>2414</v>
+        <v>786</v>
       </c>
       <c r="Y8" s="41">
         <f t="shared" si="2"/>
-        <v>312</v>
+        <v>140</v>
       </c>
       <c r="Z8" s="41">
         <f t="shared" si="2"/>
-        <v>276</v>
+        <v>160</v>
       </c>
       <c r="AA8" s="41">
         <f t="shared" si="2"/>
-        <v>4772</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.25">
@@ -12199,47 +12199,47 @@
         <v>86</v>
       </c>
       <c r="C9" s="40">
-        <v>2654</v>
+        <v>1442</v>
       </c>
       <c r="D9" s="40">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E9" s="40">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="F9" s="40">
-        <v>718</v>
+        <v>230</v>
       </c>
       <c r="G9" s="40">
-        <v>3248</v>
+        <v>1032</v>
       </c>
       <c r="H9" s="40">
-        <v>1072</v>
+        <v>482</v>
       </c>
       <c r="I9" s="40">
-        <v>2118</v>
+        <v>740</v>
       </c>
       <c r="J9" s="40">
-        <v>2414</v>
+        <v>786</v>
       </c>
       <c r="K9" s="40">
-        <v>312</v>
+        <v>140</v>
       </c>
       <c r="L9" s="40">
-        <v>276</v>
+        <v>160</v>
       </c>
       <c r="M9" s="40">
-        <v>4772</v>
+        <v>780</v>
       </c>
       <c r="N9">
-        <v>17796</v>
+        <v>5886</v>
       </c>
       <c r="P9" t="s">
         <v>16</v>
       </c>
       <c r="Q9" s="41">
         <f>C10</f>
-        <v>1230</v>
+        <v>624</v>
       </c>
       <c r="R9" s="41">
         <f t="shared" si="2"/>
@@ -12247,39 +12247,39 @@
       </c>
       <c r="S9" s="41">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="T9" s="41">
         <f t="shared" si="2"/>
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="U9" s="41">
         <f t="shared" si="2"/>
-        <v>998</v>
+        <v>302</v>
       </c>
       <c r="V9" s="41">
         <f t="shared" si="2"/>
-        <v>438</v>
+        <v>158</v>
       </c>
       <c r="W9" s="41">
         <f t="shared" si="2"/>
-        <v>680</v>
+        <v>218</v>
       </c>
       <c r="X9" s="41">
         <f t="shared" si="2"/>
-        <v>812</v>
+        <v>282</v>
       </c>
       <c r="Y9" s="41">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="Z9" s="41">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" si="2"/>
-        <v>1474</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.25">
@@ -12287,87 +12287,87 @@
         <v>87</v>
       </c>
       <c r="C10" s="40">
-        <v>1230</v>
+        <v>624</v>
       </c>
       <c r="D10" s="40">
         <v>8</v>
       </c>
       <c r="E10" s="40">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F10" s="40">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="G10" s="40">
-        <v>998</v>
+        <v>302</v>
       </c>
       <c r="H10" s="40">
-        <v>438</v>
+        <v>158</v>
       </c>
       <c r="I10" s="40">
-        <v>680</v>
+        <v>218</v>
       </c>
       <c r="J10" s="40">
-        <v>812</v>
+        <v>282</v>
       </c>
       <c r="K10" s="40">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="L10" s="40">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="M10" s="40">
-        <v>1474</v>
+        <v>132</v>
       </c>
       <c r="N10">
-        <v>5998</v>
+        <v>1862</v>
       </c>
       <c r="P10" t="s">
         <v>17</v>
       </c>
       <c r="Q10" s="41">
         <f>C11</f>
-        <v>506</v>
+        <v>248</v>
       </c>
       <c r="R10" s="41">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S10" s="41">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="T10" s="41">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U10" s="41">
         <f t="shared" si="2"/>
-        <v>348</v>
+        <v>138</v>
       </c>
       <c r="V10" s="41">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W10" s="41">
         <f t="shared" si="2"/>
-        <v>218</v>
+        <v>60</v>
       </c>
       <c r="X10" s="41">
         <f t="shared" si="2"/>
-        <v>204</v>
+        <v>66</v>
       </c>
       <c r="Y10" s="41">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="Z10" s="41">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="2"/>
-        <v>528</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.25">
@@ -12375,47 +12375,47 @@
         <v>88</v>
       </c>
       <c r="C11" s="40">
-        <v>506</v>
+        <v>248</v>
       </c>
       <c r="D11" s="40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="40">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F11" s="40">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G11" s="40">
-        <v>348</v>
+        <v>138</v>
       </c>
       <c r="H11" s="40">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I11" s="40">
-        <v>218</v>
+        <v>60</v>
       </c>
       <c r="J11" s="40">
-        <v>204</v>
+        <v>66</v>
       </c>
       <c r="K11" s="40">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="L11" s="40">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M11" s="40">
-        <v>528</v>
+        <v>78</v>
       </c>
       <c r="N11">
-        <v>1986</v>
+        <v>674</v>
       </c>
       <c r="P11" t="s">
         <v>18</v>
       </c>
       <c r="Q11" s="41">
         <f>C12+C13</f>
-        <v>290</v>
+        <v>138</v>
       </c>
       <c r="R11" s="41">
         <f t="shared" ref="R11:AA11" si="3">D12+D13</f>
@@ -12423,39 +12423,39 @@
       </c>
       <c r="S11" s="41">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T11" s="41">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="U11" s="41">
         <f t="shared" si="3"/>
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="V11" s="41">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="W11" s="41">
         <f t="shared" si="3"/>
-        <v>158</v>
+        <v>36</v>
       </c>
       <c r="X11" s="41">
         <f t="shared" si="3"/>
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="Y11" s="41">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z11" s="41">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="3"/>
-        <v>168</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
@@ -12463,87 +12463,87 @@
         <v>89</v>
       </c>
       <c r="C12" s="40">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" s="40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G12" s="40">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="H12" s="40">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="I12" s="40">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="J12" s="40">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="K12" s="40">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L12" s="40">
         <v>2</v>
       </c>
       <c r="M12" s="40">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="N12">
-        <v>636</v>
+        <v>202</v>
       </c>
       <c r="P12" t="s">
         <v>19</v>
       </c>
       <c r="Q12" s="41">
         <f>C14</f>
-        <v>1022</v>
+        <v>556</v>
       </c>
       <c r="R12" s="41">
         <f t="shared" ref="R12:AA12" si="4">D14</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S12" s="41">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="T12" s="41">
         <f t="shared" si="4"/>
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="U12" s="41">
         <f t="shared" si="4"/>
-        <v>1262</v>
+        <v>366</v>
       </c>
       <c r="V12" s="41">
         <f t="shared" si="4"/>
-        <v>402</v>
+        <v>140</v>
       </c>
       <c r="W12" s="41">
         <f t="shared" si="4"/>
-        <v>796</v>
+        <v>224</v>
       </c>
       <c r="X12" s="41">
         <f t="shared" si="4"/>
-        <v>1272</v>
+        <v>388</v>
       </c>
       <c r="Y12" s="41">
         <f t="shared" si="4"/>
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="Z12" s="41">
         <f t="shared" si="4"/>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>1792</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
@@ -12551,87 +12551,87 @@
         <v>90</v>
       </c>
       <c r="C13" s="42">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F13" s="42">
         <v>2</v>
       </c>
       <c r="G13" s="42">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="H13" s="42">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I13" s="42">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="J13" s="42">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="K13" s="42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L13" s="42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M13" s="42">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>442</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s">
         <v>20</v>
       </c>
       <c r="Q13" s="41">
         <f>C15</f>
-        <v>472</v>
+        <v>248</v>
       </c>
       <c r="R13" s="41">
         <f t="shared" ref="R13:AA13" si="5">D15</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S13" s="41">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="T13" s="41">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="U13" s="41">
         <f t="shared" si="5"/>
-        <v>506</v>
+        <v>146</v>
       </c>
       <c r="V13" s="41">
         <f t="shared" si="5"/>
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="W13" s="41">
         <f t="shared" si="5"/>
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="X13" s="41">
         <f t="shared" si="5"/>
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="Y13" s="41">
         <f t="shared" si="5"/>
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="Z13" s="41">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="5"/>
-        <v>624</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
@@ -12639,47 +12639,47 @@
         <v>91</v>
       </c>
       <c r="C14" s="40">
-        <v>1022</v>
+        <v>556</v>
       </c>
       <c r="D14" s="40">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" s="40">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F14" s="40">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="G14" s="40">
-        <v>1262</v>
+        <v>366</v>
       </c>
       <c r="H14" s="40">
-        <v>402</v>
+        <v>140</v>
       </c>
       <c r="I14" s="40">
-        <v>796</v>
+        <v>224</v>
       </c>
       <c r="J14" s="40">
-        <v>1272</v>
+        <v>388</v>
       </c>
       <c r="K14" s="40">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="L14" s="40">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="M14" s="40">
-        <v>1792</v>
+        <v>228</v>
       </c>
       <c r="N14">
-        <v>6970</v>
+        <v>2090</v>
       </c>
       <c r="P14" t="s">
         <v>21</v>
       </c>
       <c r="Q14" s="41">
         <f>C16</f>
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="R14" s="41">
         <f t="shared" ref="R14:AA14" si="6">D16</f>
@@ -12687,27 +12687,27 @@
       </c>
       <c r="S14" s="41">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T14" s="41">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U14" s="41">
         <f t="shared" si="6"/>
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="V14" s="41">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="W14" s="41">
         <f t="shared" si="6"/>
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="X14" s="41">
         <f t="shared" si="6"/>
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="Y14" s="41">
         <f t="shared" si="6"/>
@@ -12715,11 +12715,11 @@
       </c>
       <c r="Z14" s="41">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="41">
         <f t="shared" si="6"/>
-        <v>144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
@@ -12727,47 +12727,47 @@
         <v>92</v>
       </c>
       <c r="C15" s="40">
-        <v>472</v>
+        <v>248</v>
       </c>
       <c r="D15" s="40">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E15" s="40">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F15" s="40">
+        <v>16</v>
+      </c>
+      <c r="G15" s="40">
+        <v>146</v>
+      </c>
+      <c r="H15" s="40">
         <v>50</v>
       </c>
-      <c r="G15" s="40">
-        <v>506</v>
-      </c>
-      <c r="H15" s="40">
-        <v>134</v>
-      </c>
       <c r="I15" s="40">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="J15" s="40">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="K15" s="40">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="L15" s="40">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M15" s="40">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="N15">
-        <v>2504</v>
+        <v>686</v>
       </c>
       <c r="P15" t="s">
         <v>22</v>
       </c>
       <c r="Q15" s="41">
         <f>C17+C18</f>
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="R15" s="41">
         <f t="shared" ref="R15:AA15" si="7">D17+D18</f>
@@ -12779,35 +12779,35 @@
       </c>
       <c r="T15" s="41">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U15" s="41">
         <f t="shared" si="7"/>
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="V15" s="41">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="W15" s="41">
         <f t="shared" si="7"/>
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="X15" s="41">
         <f t="shared" si="7"/>
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="Y15" s="41">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="41">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="41">
         <f t="shared" si="7"/>
-        <v>60</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
@@ -12815,87 +12815,87 @@
         <v>93</v>
       </c>
       <c r="C16" s="40">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="D16" s="40">
         <v>0</v>
       </c>
       <c r="E16" s="40">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F16" s="40">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16" s="40">
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="H16" s="40">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I16" s="40">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="J16" s="40">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="K16" s="40">
         <v>10</v>
       </c>
       <c r="L16" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="40">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>798</v>
+        <v>250</v>
       </c>
       <c r="P16" t="s">
         <v>23</v>
       </c>
       <c r="Q16" s="41">
         <f>C19+C24</f>
-        <v>626</v>
+        <v>330</v>
       </c>
       <c r="R16" s="41">
         <f t="shared" ref="R16:AA16" si="8">D19+D24</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S16" s="41">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T16" s="41">
         <f t="shared" si="8"/>
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="U16" s="41">
         <f t="shared" si="8"/>
-        <v>1024</v>
+        <v>304</v>
       </c>
       <c r="V16" s="41">
         <f t="shared" si="8"/>
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="W16" s="41">
         <f t="shared" si="8"/>
-        <v>748</v>
+        <v>202</v>
       </c>
       <c r="X16" s="41">
         <f t="shared" si="8"/>
-        <v>686</v>
+        <v>200</v>
       </c>
       <c r="Y16" s="41">
         <f t="shared" si="8"/>
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="Z16" s="41">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA16" s="41">
         <f t="shared" si="8"/>
-        <v>798</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.25">
@@ -12903,7 +12903,7 @@
         <v>94</v>
       </c>
       <c r="C17" s="40">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -12912,78 +12912,78 @@
         <v>0</v>
       </c>
       <c r="F17" s="40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="40">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="H17" s="40">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I17" s="40">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="J17" s="40">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K17" s="40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L17" s="40">
         <v>0</v>
       </c>
       <c r="M17" s="40">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="N17">
-        <v>276</v>
+        <v>112</v>
       </c>
       <c r="P17" t="s">
         <v>24</v>
       </c>
       <c r="Q17" s="41">
         <f>C20+C25</f>
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="R17" s="41">
         <f t="shared" ref="R17:AA17" si="9">D20+D25</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" s="41">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T17" s="41">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="U17" s="41">
         <f t="shared" si="9"/>
-        <v>372</v>
+        <v>118</v>
       </c>
       <c r="V17" s="41">
         <f t="shared" si="9"/>
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="W17" s="41">
         <f t="shared" si="9"/>
-        <v>312</v>
+        <v>68</v>
       </c>
       <c r="X17" s="41">
         <f t="shared" si="9"/>
-        <v>210</v>
+        <v>44</v>
       </c>
       <c r="Y17" s="41">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="Z17" s="41">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AA17" s="41">
         <f t="shared" si="9"/>
-        <v>390</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.25">
@@ -12991,7 +12991,7 @@
         <v>95</v>
       </c>
       <c r="C18" s="42">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D18" s="42">
         <v>2</v>
@@ -13003,35 +13003,35 @@
         <v>0</v>
       </c>
       <c r="G18" s="42">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="H18" s="42">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I18" s="42">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="J18" s="42">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="42">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="42">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>232</v>
+        <v>66</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
       </c>
       <c r="Q18" s="41">
         <f>C21+C26</f>
-        <v>198</v>
+        <v>86</v>
       </c>
       <c r="R18" s="41">
         <f t="shared" ref="R18:AA18" si="10">D21+D26</f>
@@ -13039,39 +13039,39 @@
       </c>
       <c r="S18" s="41">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" s="41">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U18" s="41">
         <f t="shared" si="10"/>
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="V18" s="41">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="W18" s="41">
         <f t="shared" si="10"/>
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="X18" s="41">
         <f t="shared" si="10"/>
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="Y18" s="41">
         <f t="shared" si="10"/>
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Z18" s="41">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="41">
         <f t="shared" si="10"/>
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.25">
@@ -13079,47 +13079,47 @@
         <v>96</v>
       </c>
       <c r="C19" s="40">
-        <v>296</v>
+        <v>146</v>
       </c>
       <c r="D19" s="40">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" s="40">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G19" s="40">
-        <v>582</v>
+        <v>192</v>
       </c>
       <c r="H19" s="40">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="I19" s="40">
-        <v>420</v>
+        <v>114</v>
       </c>
       <c r="J19" s="40">
-        <v>376</v>
+        <v>104</v>
       </c>
       <c r="K19" s="40">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="L19" s="40">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M19" s="40">
-        <v>522</v>
+        <v>28</v>
       </c>
       <c r="N19">
-        <v>2452</v>
+        <v>688</v>
       </c>
       <c r="P19" t="s">
         <v>26</v>
       </c>
       <c r="Q19" s="41">
         <f>C22+C23+C27+C28</f>
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="R19" s="41">
         <f t="shared" ref="R19:AA19" si="11">D22+D23+D27+D28</f>
@@ -13127,39 +13127,39 @@
       </c>
       <c r="S19" s="41">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T19" s="41">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U19" s="41">
         <f t="shared" si="11"/>
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="V19" s="41">
         <f t="shared" si="11"/>
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="W19" s="41">
         <f t="shared" si="11"/>
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="X19" s="41">
         <f t="shared" si="11"/>
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="Y19" s="41">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Z19" s="41">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="41">
         <f t="shared" si="11"/>
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.25">
@@ -13167,40 +13167,40 @@
         <v>97</v>
       </c>
       <c r="C20" s="40">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="D20" s="40">
+        <v>0</v>
+      </c>
+      <c r="E20" s="40">
         <v>2</v>
       </c>
-      <c r="E20" s="40">
+      <c r="F20" s="40">
         <v>4</v>
       </c>
-      <c r="F20" s="40">
+      <c r="G20" s="40">
+        <v>58</v>
+      </c>
+      <c r="H20" s="40">
         <v>6</v>
       </c>
-      <c r="G20" s="40">
-        <v>186</v>
-      </c>
-      <c r="H20" s="40">
-        <v>30</v>
-      </c>
       <c r="I20" s="40">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="J20" s="40">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="K20" s="40">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L20" s="40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M20" s="40">
-        <v>274</v>
+        <v>26</v>
       </c>
       <c r="N20">
-        <v>930</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.25">
@@ -13208,40 +13208,40 @@
         <v>98</v>
       </c>
       <c r="C21" s="40">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="D21" s="40">
         <v>2</v>
       </c>
       <c r="E21" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="40">
+        <v>0</v>
+      </c>
+      <c r="G21" s="40">
+        <v>22</v>
+      </c>
+      <c r="H21" s="40">
         <v>10</v>
       </c>
-      <c r="G21" s="40">
-        <v>76</v>
-      </c>
-      <c r="H21" s="40">
+      <c r="I21" s="40">
         <v>22</v>
       </c>
-      <c r="I21" s="40">
-        <v>62</v>
-      </c>
       <c r="J21" s="40">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="K21" s="40">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L21" s="40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M21" s="40">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>370</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.25">
@@ -13249,28 +13249,28 @@
         <v>99</v>
       </c>
       <c r="C22" s="40">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D22" s="40">
         <v>2</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="40">
+        <v>10</v>
+      </c>
+      <c r="H22" s="40">
         <v>2</v>
       </c>
-      <c r="F22">
+      <c r="I22" s="40">
+        <v>2</v>
+      </c>
+      <c r="J22" s="40">
         <v>4</v>
-      </c>
-      <c r="G22" s="40">
-        <v>18</v>
-      </c>
-      <c r="H22" s="40">
-        <v>14</v>
-      </c>
-      <c r="I22" s="40">
-        <v>14</v>
-      </c>
-      <c r="J22" s="40">
-        <v>12</v>
       </c>
       <c r="K22">
         <v>2</v>
@@ -13279,10 +13279,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="40">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>120</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.25">
@@ -13290,40 +13290,40 @@
         <v>100</v>
       </c>
       <c r="C23" s="42">
+        <v>18</v>
+      </c>
+      <c r="D23" s="42">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="42">
+        <v>0</v>
+      </c>
+      <c r="G23" s="42">
+        <v>2</v>
+      </c>
+      <c r="H23" s="42">
+        <v>2</v>
+      </c>
+      <c r="I23" s="42">
+        <v>6</v>
+      </c>
+      <c r="J23" s="42">
+        <v>0</v>
+      </c>
+      <c r="K23" s="42">
+        <v>2</v>
+      </c>
+      <c r="L23" s="42">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23">
         <v>30</v>
-      </c>
-      <c r="D23" s="42">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="42">
-        <v>2</v>
-      </c>
-      <c r="G23" s="42">
-        <v>30</v>
-      </c>
-      <c r="H23" s="42">
-        <v>6</v>
-      </c>
-      <c r="I23" s="42">
-        <v>30</v>
-      </c>
-      <c r="J23" s="42">
-        <v>12</v>
-      </c>
-      <c r="K23" s="42">
-        <v>4</v>
-      </c>
-      <c r="L23" s="42">
-        <v>2</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>116</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.25">
@@ -13331,40 +13331,40 @@
         <v>101</v>
       </c>
       <c r="C24" s="42">
-        <v>330</v>
+        <v>184</v>
       </c>
       <c r="D24" s="42">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E24" s="42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="42">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G24" s="42">
-        <v>442</v>
+        <v>112</v>
       </c>
       <c r="H24" s="42">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="I24" s="42">
-        <v>328</v>
+        <v>88</v>
       </c>
       <c r="J24" s="42">
-        <v>310</v>
+        <v>96</v>
       </c>
       <c r="K24" s="42">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="L24" s="42">
         <v>10</v>
       </c>
       <c r="M24" s="42">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="N24">
-        <v>1892</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.25">
@@ -13372,7 +13372,7 @@
         <v>102</v>
       </c>
       <c r="C25" s="42">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -13381,31 +13381,31 @@
         <v>0</v>
       </c>
       <c r="F25" s="42">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G25" s="42">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="H25" s="42">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="I25" s="42">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="J25" s="42">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="K25" s="42">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L25" s="42">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M25" s="42">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>834</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.25">
@@ -13413,7 +13413,7 @@
         <v>103</v>
       </c>
       <c r="C26" s="42">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
@@ -13425,28 +13425,28 @@
         <v>0</v>
       </c>
       <c r="G26" s="42">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="H26" s="42">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I26" s="42">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J26" s="42">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="K26" s="42">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L26" s="42">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M26" s="42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>318</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.25">
@@ -13454,7 +13454,7 @@
         <v>104</v>
       </c>
       <c r="C27" s="42">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D27" s="42">
         <v>2</v>
@@ -13466,28 +13466,28 @@
         <v>0</v>
       </c>
       <c r="G27" s="42">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H27" s="42">
+        <v>0</v>
+      </c>
+      <c r="I27" s="42">
         <v>8</v>
       </c>
-      <c r="I27" s="42">
-        <v>32</v>
-      </c>
       <c r="J27" s="42">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K27" s="42">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L27" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>134</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.25">
@@ -13495,7 +13495,7 @@
         <v>105</v>
       </c>
       <c r="C28" s="42">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -13507,28 +13507,28 @@
         <v>0</v>
       </c>
       <c r="G28" s="42">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H28" s="42">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I28" s="42">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J28" s="42">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K28" s="42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L28" s="42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="42">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>168</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
